--- a/research/traditional_assets/database/data/colombia/colombia_diversified.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_diversified.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.131</v>
+        <v>0.07685</v>
       </c>
       <c r="E2">
-        <v>0.314</v>
+        <v>0.005000000000000004</v>
       </c>
       <c r="G2">
-        <v>0.1377720870678617</v>
+        <v>0.1093634862152204</v>
       </c>
       <c r="H2">
-        <v>0.1377720870678617</v>
+        <v>0.1093634862152204</v>
       </c>
       <c r="I2">
-        <v>0.2430110968843363</v>
+        <v>0.192902214881633</v>
       </c>
       <c r="J2">
-        <v>0.2041515637778319</v>
+        <v>0.1318035517059098</v>
       </c>
       <c r="K2">
-        <v>1459.3</v>
+        <v>1532.8</v>
       </c>
       <c r="L2">
-        <v>0.1557084933845497</v>
+        <v>0.1298267903273621</v>
       </c>
       <c r="M2">
         <v>130.9</v>
       </c>
       <c r="N2">
-        <v>0.03889697798116067</v>
+        <v>0.02856768730494751</v>
       </c>
       <c r="O2">
-        <v>0.0897005413554444</v>
+        <v>0.08539926931106473</v>
       </c>
       <c r="P2">
         <v>130.9</v>
       </c>
       <c r="Q2">
-        <v>0.03889697798116067</v>
+        <v>0.02856768730494751</v>
       </c>
       <c r="R2">
-        <v>0.0897005413554444</v>
+        <v>0.08539926931106473</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -641,52 +641,52 @@
         <v>764.8</v>
       </c>
       <c r="V2">
-        <v>0.2272605711229311</v>
+        <v>0.16691036860828</v>
       </c>
       <c r="W2">
-        <v>0.1897980152691612</v>
+        <v>0.1075928696773425</v>
       </c>
       <c r="X2">
-        <v>0.124187302709569</v>
+        <v>0.1703891880301411</v>
       </c>
       <c r="Y2">
-        <v>0.06561071255959219</v>
+        <v>-0.06279631835279856</v>
       </c>
       <c r="Z2">
-        <v>1.148276115562744</v>
+        <v>0.7867171309962485</v>
       </c>
       <c r="AA2">
-        <v>0.2344223646408685</v>
+        <v>0.1172111823204343</v>
       </c>
       <c r="AB2">
-        <v>0.0906346088718598</v>
+        <v>0.08728171903358717</v>
       </c>
       <c r="AC2">
-        <v>0.1437877557690088</v>
+        <v>0.0299294632868471</v>
       </c>
       <c r="AD2">
-        <v>2930.4</v>
+        <v>7447.799999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2930.4</v>
+        <v>7447.799999999999</v>
       </c>
       <c r="AG2">
-        <v>2165.6</v>
+        <v>6682.999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.4654605524405546</v>
+        <v>0.6191073907513778</v>
       </c>
       <c r="AI2">
-        <v>0.2917707970329069</v>
+        <v>0.4050975784870439</v>
       </c>
       <c r="AJ2">
-        <v>0.3915456797266268</v>
+        <v>0.593248173562596</v>
       </c>
       <c r="AK2">
-        <v>0.233394764352765</v>
+        <v>0.3792762933872102</v>
       </c>
       <c r="AL2">
         <v>335.4</v>
@@ -695,13 +695,13 @@
         <v>335.4</v>
       </c>
       <c r="AN2">
-        <v>1.25113141490906</v>
+        <v>3.179830928187174</v>
       </c>
       <c r="AO2">
         <v>6.790399522957663</v>
       </c>
       <c r="AP2">
-        <v>0.9246008026641621</v>
+        <v>2.853300315942276</v>
       </c>
       <c r="AQ2">
         <v>6.790399522957663</v>
@@ -781,10 +781,10 @@
         <v>0.1897980152691612</v>
       </c>
       <c r="X3">
-        <v>0.124187302709569</v>
+        <v>0.1241696113550712</v>
       </c>
       <c r="Y3">
-        <v>0.06561071255959219</v>
+        <v>0.06562840391409</v>
       </c>
       <c r="Z3">
         <v>1.148276115562744</v>
@@ -793,10 +793,10 @@
         <v>0.2344223646408685</v>
       </c>
       <c r="AB3">
-        <v>0.0906346088718598</v>
+        <v>0.09062515214499997</v>
       </c>
       <c r="AC3">
-        <v>0.1437877557690088</v>
+        <v>0.1437972124958686</v>
       </c>
       <c r="AD3">
         <v>2930.4</v>
@@ -839,6 +839,125 @@
       </c>
       <c r="AQ3">
         <v>6.790399522957663</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Corporación Financiera Colombiana S.A. (BVC:CORFICOLCF)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Diversified</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0227</v>
+      </c>
+      <c r="E4">
+        <v>-0.304</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>73.5</v>
+      </c>
+      <c r="L4">
+        <v>0.03019100431300062</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.02538772408552382</v>
+      </c>
+      <c r="X4">
+        <v>0.216608764705211</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1912210406196871</v>
+      </c>
+      <c r="Z4">
+        <v>0.3556350887444306</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.08393828592217437</v>
+      </c>
+      <c r="AC4">
+        <v>-0.08393828592217437</v>
+      </c>
+      <c r="AD4">
+        <v>4517.4</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>4517.4</v>
+      </c>
+      <c r="AG4">
+        <v>4517.4</v>
+      </c>
+      <c r="AH4">
+        <v>0.7877995186774092</v>
+      </c>
+      <c r="AI4">
+        <v>0.5415442895333085</v>
+      </c>
+      <c r="AJ4">
+        <v>0.7877995186774092</v>
+      </c>
+      <c r="AK4">
+        <v>0.5415442895333085</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1252,7 @@
         <v>6.57543231961837</v>
       </c>
       <c r="F2">
-        <v>4.60985638861363</v>
+        <v>4.7714803445719</v>
       </c>
       <c r="G2">
         <v>1.25113141490906</v>
@@ -1151,13 +1270,13 @@
         <v>3365.3</v>
       </c>
       <c r="L2">
-        <v>258.576180089917</v>
+        <v>300.81739602842</v>
       </c>
       <c r="M2">
         <v>5530.9</v>
       </c>
       <c r="N2">
-        <v>5726.51918008992</v>
+        <v>5768.76039602842</v>
       </c>
       <c r="O2">
         <v>2930.4</v>
@@ -1166,16 +1285,16 @@
         <v>6232.743</v>
       </c>
       <c r="Q2">
-        <v>0.0906346088718598</v>
+        <v>0.090625152145</v>
       </c>
       <c r="R2">
-        <v>0.0825628743074019</v>
+        <v>0.0808823916128134</v>
       </c>
       <c r="S2">
         <v>0.0521023673444086</v>
       </c>
       <c r="T2">
-        <v>0.0498923673444086</v>
+        <v>0.0482023673444086</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1307,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.124187302709569</v>
+        <v>0.124169611355071</v>
       </c>
       <c r="X2">
-        <v>3.31694306364373</v>
+        <v>3.31620479418488</v>
       </c>
       <c r="Y2">
         <v>1.14037333568347</v>
@@ -1230,7 +1349,7 @@
         <v>3365.3</v>
       </c>
       <c r="AK2">
-        <v>0.06873828092673559</v>
+        <v>0.06872276727524601</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1537,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09585574695705792</v>
+        <v>0.09584444979624923</v>
       </c>
       <c r="C2">
-        <v>6176.129781220159</v>
+        <v>6176.170004431605</v>
       </c>
       <c r="D2">
-        <v>5411.329781220159</v>
+        <v>5411.370004431605</v>
       </c>
       <c r="E2">
         <v>-2930.4</v>
@@ -1469,19 +1588,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09585574695705792</v>
+        <v>0.09584444979624923</v>
       </c>
       <c r="T2">
         <v>0.7282077218429368</v>
       </c>
       <c r="U2">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V2">
         <v>0.35</v>
       </c>
       <c r="W2">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1619,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09568117551615231</v>
+        <v>0.09566081789540645</v>
       </c>
       <c r="C3">
-        <v>6117.087073673564</v>
+        <v>6117.330704750482</v>
       </c>
       <c r="D3">
-        <v>5415.244073673564</v>
+        <v>5415.487704750482</v>
       </c>
       <c r="E3">
         <v>-2867.443</v>
@@ -1533,37 +1652,37 @@
         <v>2205.4</v>
       </c>
       <c r="M3">
-        <v>4.442087786002975</v>
+        <v>4.353947986002976</v>
       </c>
       <c r="N3">
-        <v>2200.957912213997</v>
+        <v>2201.046052013997</v>
       </c>
       <c r="O3">
-        <v>770.3352692748988</v>
+        <v>770.3661182048988</v>
       </c>
       <c r="P3">
-        <v>1430.622642939098</v>
+        <v>1430.679933809098</v>
       </c>
       <c r="Q3">
-        <v>1567.422642939098</v>
+        <v>1567.479933809098</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09618439580071537</v>
+        <v>0.09617302446662865</v>
       </c>
       <c r="T3">
         <v>0.7329888836530167</v>
       </c>
       <c r="U3">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V3">
         <v>0.35</v>
       </c>
       <c r="W3">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>496.4782566767856</v>
+        <v>506.5287888348449</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1701,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09550660407524669</v>
+        <v>0.09547718599456365</v>
       </c>
       <c r="C4">
-        <v>6058.050033043241</v>
+        <v>6058.497676445269</v>
       </c>
       <c r="D4">
-        <v>5419.16403304324</v>
+        <v>5419.611676445268</v>
       </c>
       <c r="E4">
         <v>-2804.486</v>
@@ -1615,37 +1734,37 @@
         <v>2205.4</v>
       </c>
       <c r="M4">
-        <v>8.884175572005951</v>
+        <v>8.707895972005952</v>
       </c>
       <c r="N4">
-        <v>2196.515824427994</v>
+        <v>2196.692104027994</v>
       </c>
       <c r="O4">
-        <v>768.7805385497977</v>
+        <v>768.8422364097977</v>
       </c>
       <c r="P4">
-        <v>1427.735285878196</v>
+        <v>1427.849867618196</v>
       </c>
       <c r="Q4">
-        <v>1564.535285878196</v>
+        <v>1564.649867618196</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09651975176363115</v>
+        <v>0.096508304742526</v>
       </c>
       <c r="T4">
         <v>0.7378676201939146</v>
       </c>
       <c r="U4">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V4">
         <v>0.35</v>
       </c>
       <c r="W4">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>248.2391283383928</v>
+        <v>253.2643944174224</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1783,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09533203263434106</v>
+        <v>0.09529355409372087</v>
       </c>
       <c r="C5">
-        <v>5999.01867164452</v>
+        <v>5999.67093385411</v>
       </c>
       <c r="D5">
-        <v>5423.08967164452</v>
+        <v>5423.741933854109</v>
       </c>
       <c r="E5">
         <v>-2741.529</v>
@@ -1697,37 +1816,37 @@
         <v>2205.4</v>
       </c>
       <c r="M5">
-        <v>13.32626335800893</v>
+        <v>13.06184395800893</v>
       </c>
       <c r="N5">
-        <v>2192.073736641991</v>
+        <v>2192.338156041991</v>
       </c>
       <c r="O5">
-        <v>767.2258078246967</v>
+        <v>767.3183546146967</v>
       </c>
       <c r="P5">
-        <v>1424.847928817294</v>
+        <v>1425.019801427294</v>
       </c>
       <c r="Q5">
-        <v>1561.647928817294</v>
+        <v>1561.819801427294</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09686202228248331</v>
+        <v>0.09685049801380269</v>
       </c>
       <c r="T5">
         <v>0.7428469492408102</v>
       </c>
       <c r="U5">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V5">
         <v>0.35</v>
       </c>
       <c r="W5">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>165.4927522255952</v>
+        <v>168.842929611615</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1865,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09515746119343545</v>
+        <v>0.09510992219287807</v>
       </c>
       <c r="C6">
-        <v>5939.993001828441</v>
+        <v>5940.850491358897</v>
       </c>
       <c r="D6">
-        <v>5427.021001828442</v>
+        <v>5427.878491358897</v>
       </c>
       <c r="E6">
         <v>-2678.572</v>
@@ -1779,37 +1898,37 @@
         <v>2205.4</v>
       </c>
       <c r="M6">
-        <v>17.7683511440119</v>
+        <v>17.4157919440119</v>
       </c>
       <c r="N6">
-        <v>2187.631648855988</v>
+        <v>2187.984208055988</v>
       </c>
       <c r="O6">
-        <v>765.6710770995957</v>
+        <v>765.7944728195957</v>
       </c>
       <c r="P6">
-        <v>1421.960571756392</v>
+        <v>1422.189735236392</v>
       </c>
       <c r="Q6">
-        <v>1558.760571756392</v>
+        <v>1558.989735236392</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09721142343714489</v>
+        <v>0.09719982031156431</v>
       </c>
       <c r="T6">
         <v>0.7479300143095163</v>
       </c>
       <c r="U6">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V6">
         <v>0.35</v>
       </c>
       <c r="W6">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>124.1195641691964</v>
+        <v>126.6321972087112</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1947,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09498288975252983</v>
+        <v>0.0949262902920353</v>
       </c>
       <c r="C7">
-        <v>5880.973035981889</v>
+        <v>5882.036363385425</v>
       </c>
       <c r="D7">
-        <v>5430.958035981888</v>
+        <v>5432.021363385425</v>
       </c>
       <c r="E7">
         <v>-2615.615</v>
@@ -1861,37 +1980,37 @@
         <v>2205.4</v>
       </c>
       <c r="M7">
-        <v>22.21043893001488</v>
+        <v>21.76973993001488</v>
       </c>
       <c r="N7">
-        <v>2183.189561069985</v>
+        <v>2183.630260069985</v>
       </c>
       <c r="O7">
-        <v>764.1163463744947</v>
+        <v>764.2705910244946</v>
       </c>
       <c r="P7">
-        <v>1419.07321469549</v>
+        <v>1419.35966904549</v>
       </c>
       <c r="Q7">
-        <v>1555.87321469549</v>
+        <v>1556.15966904549</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09756818040558884</v>
+        <v>0.09755649676296302</v>
       </c>
       <c r="T7">
         <v>0.7531200912744057</v>
       </c>
       <c r="U7">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V7">
         <v>0.35</v>
       </c>
       <c r="W7">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>99.29565133535711</v>
+        <v>101.305757766969</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2029,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09480831831162422</v>
+        <v>0.0947426583911925</v>
       </c>
       <c r="C8">
-        <v>5821.958786527713</v>
+        <v>5823.228564403568</v>
       </c>
       <c r="D8">
-        <v>5434.900786527713</v>
+        <v>5436.170564403568</v>
       </c>
       <c r="E8">
         <v>-2552.658</v>
@@ -1943,37 +2062,37 @@
         <v>2205.4</v>
       </c>
       <c r="M8">
-        <v>26.65252671601785</v>
+        <v>26.12368791601785</v>
       </c>
       <c r="N8">
-        <v>2178.747473283982</v>
+        <v>2179.276312083982</v>
       </c>
       <c r="O8">
-        <v>762.5616156493936</v>
+        <v>762.7467092293936</v>
       </c>
       <c r="P8">
-        <v>1416.185857634588</v>
+        <v>1416.529602854588</v>
       </c>
       <c r="Q8">
-        <v>1552.985857634588</v>
+        <v>1553.329602854588</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09793252794782947</v>
+        <v>0.09792076207502978</v>
       </c>
       <c r="T8">
         <v>0.7584205954087608</v>
       </c>
       <c r="U8">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V8">
         <v>0.35</v>
       </c>
       <c r="W8">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>82.74637611279761</v>
+        <v>84.42146480580749</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2111,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09463374687071859</v>
+        <v>0.09455902649034971</v>
       </c>
       <c r="C9">
-        <v>5762.950265924866</v>
+        <v>5764.427108927444</v>
       </c>
       <c r="D9">
-        <v>5438.849265924866</v>
+        <v>5440.326108927444</v>
       </c>
       <c r="E9">
         <v>-2489.701</v>
@@ -2025,37 +2144,37 @@
         <v>2205.4</v>
       </c>
       <c r="M9">
-        <v>31.09461450202083</v>
+        <v>30.47763590202083</v>
       </c>
       <c r="N9">
-        <v>2174.305385497979</v>
+        <v>2174.922364097979</v>
       </c>
       <c r="O9">
-        <v>761.0068849242925</v>
+        <v>761.2228274342926</v>
       </c>
       <c r="P9">
-        <v>1413.298500573686</v>
+        <v>1413.699536663686</v>
       </c>
       <c r="Q9">
-        <v>1550.098500573686</v>
+        <v>1550.499536663686</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09830471092108602</v>
+        <v>0.09829286104972162</v>
       </c>
       <c r="T9">
         <v>0.7638350888793385</v>
       </c>
       <c r="U9">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V9">
         <v>0.35</v>
       </c>
       <c r="W9">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>70.9254652395408</v>
+        <v>72.36125554783499</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2193,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09445917542981298</v>
+        <v>0.09437539458950692</v>
       </c>
       <c r="C10">
-        <v>5703.947486668533</v>
+        <v>5705.632011515584</v>
       </c>
       <c r="D10">
-        <v>5442.803486668533</v>
+        <v>5444.488011515584</v>
       </c>
       <c r="E10">
         <v>-2426.744</v>
@@ -2107,37 +2226,37 @@
         <v>2205.4</v>
       </c>
       <c r="M10">
-        <v>35.5367022880238</v>
+        <v>34.83158388802381</v>
       </c>
       <c r="N10">
-        <v>2169.863297711976</v>
+        <v>2170.568416111976</v>
       </c>
       <c r="O10">
-        <v>759.4521541991916</v>
+        <v>759.6989456391915</v>
       </c>
       <c r="P10">
-        <v>1410.411143512784</v>
+        <v>1410.869470472784</v>
       </c>
       <c r="Q10">
-        <v>1547.211143512784</v>
+        <v>1547.669470472784</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09868498482854379</v>
+        <v>0.09867304913255895</v>
       </c>
       <c r="T10">
         <v>0.7693672887297114</v>
       </c>
       <c r="U10">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V10">
         <v>0.35</v>
       </c>
       <c r="W10">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>62.0597820845982</v>
+        <v>63.31609860435561</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2275,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09428460398890737</v>
+        <v>0.09419176268866417</v>
       </c>
       <c r="C11">
-        <v>5644.950461290265</v>
+        <v>5646.843286771103</v>
       </c>
       <c r="D11">
-        <v>5446.763461290265</v>
+        <v>5448.656286771103</v>
       </c>
       <c r="E11">
         <v>-2363.787</v>
@@ -2189,37 +2308,37 @@
         <v>2205.4</v>
       </c>
       <c r="M11">
-        <v>39.97879007402678</v>
+        <v>39.18553187402679</v>
       </c>
       <c r="N11">
-        <v>2165.421209925973</v>
+        <v>2166.214468125973</v>
       </c>
       <c r="O11">
-        <v>757.8974234740905</v>
+        <v>758.1750638440905</v>
       </c>
       <c r="P11">
-        <v>1407.523786451883</v>
+        <v>1408.039404281883</v>
       </c>
       <c r="Q11">
-        <v>1544.323786451883</v>
+        <v>1544.839404281882</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09907361640429735</v>
+        <v>0.09906159299743668</v>
       </c>
       <c r="T11">
         <v>0.7750210753899828</v>
       </c>
       <c r="U11">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V11">
         <v>0.35</v>
       </c>
       <c r="W11">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>55.16425074186507</v>
+        <v>56.28097653720499</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2357,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09411003254800175</v>
+        <v>0.09400813078782139</v>
       </c>
       <c r="C12">
-        <v>5585.959202358106</v>
+        <v>5588.060949341871</v>
       </c>
       <c r="D12">
-        <v>5450.729202358106</v>
+        <v>5452.830949341871</v>
       </c>
       <c r="E12">
         <v>-2300.83</v>
@@ -2271,37 +2390,37 @@
         <v>2205.4</v>
       </c>
       <c r="M12">
-        <v>44.42087786002976</v>
+        <v>43.53947986002976</v>
       </c>
       <c r="N12">
-        <v>2160.97912213997</v>
+        <v>2161.86052013997</v>
       </c>
       <c r="O12">
-        <v>756.3426927489895</v>
+        <v>756.6511820489894</v>
       </c>
       <c r="P12">
-        <v>1404.636429390981</v>
+        <v>1405.209338090981</v>
       </c>
       <c r="Q12">
-        <v>1541.43642939098</v>
+        <v>1542.00933809098</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09947088423728988</v>
+        <v>0.09945877117042279</v>
       </c>
       <c r="T12">
         <v>0.7808005017538155</v>
       </c>
       <c r="U12">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V12">
         <v>0.35</v>
       </c>
       <c r="W12">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>49.64782566767856</v>
+        <v>50.65287888348449</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2439,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09393546110709614</v>
+        <v>0.09382449888697861</v>
       </c>
       <c r="C13">
-        <v>5526.973722476731</v>
+        <v>5529.285013920684</v>
       </c>
       <c r="D13">
-        <v>5454.700722476731</v>
+        <v>5457.012013920684</v>
       </c>
       <c r="E13">
         <v>-2237.873</v>
@@ -2353,37 +2472,37 @@
         <v>2205.4</v>
       </c>
       <c r="M13">
-        <v>48.86296564603273</v>
+        <v>47.89342784603274</v>
       </c>
       <c r="N13">
-        <v>2156.537034353967</v>
+        <v>2157.506572153967</v>
       </c>
       <c r="O13">
-        <v>754.7879620238884</v>
+        <v>755.1273002538883</v>
       </c>
       <c r="P13">
-        <v>1401.749072330079</v>
+        <v>1402.379271900078</v>
       </c>
       <c r="Q13">
-        <v>1538.549072330079</v>
+        <v>1539.179271900078</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09987707943731594</v>
+        <v>0.09986487469561084</v>
       </c>
       <c r="T13">
         <v>0.7867098028673976</v>
       </c>
       <c r="U13">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>45.13438697061687</v>
+        <v>46.04807171225863</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2521,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09376088966619051</v>
+        <v>0.0936408669861358</v>
       </c>
       <c r="C14">
-        <v>5467.994034287579</v>
+        <v>5470.515495245437</v>
       </c>
       <c r="D14">
-        <v>5458.678034287579</v>
+        <v>5461.199495245437</v>
       </c>
       <c r="E14">
         <v>-2174.916</v>
@@ -2435,37 +2554,37 @@
         <v>2205.4</v>
       </c>
       <c r="M14">
-        <v>53.30505343203571</v>
+        <v>52.24737583203571</v>
       </c>
       <c r="N14">
-        <v>2152.094946567964</v>
+        <v>2153.152624167964</v>
       </c>
       <c r="O14">
-        <v>753.2332312987874</v>
+        <v>753.6034184587874</v>
       </c>
       <c r="P14">
-        <v>1398.861715269177</v>
+        <v>1399.549205709176</v>
       </c>
       <c r="Q14">
-        <v>1535.661715269177</v>
+        <v>1536.349205709176</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1002925063464335</v>
+        <v>0.1002802078463713</v>
       </c>
       <c r="T14">
         <v>0.7927534062790152</v>
       </c>
       <c r="U14">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V14">
         <v>0.35</v>
       </c>
       <c r="W14">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>41.3731880563988</v>
+        <v>42.21073240290374</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2603,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.0935863182252849</v>
+        <v>0.09345723508529302</v>
       </c>
       <c r="C15">
-        <v>5409.020150468984</v>
+        <v>5411.752408099297</v>
       </c>
       <c r="D15">
-        <v>5462.661150468984</v>
+        <v>5465.393408099297</v>
       </c>
       <c r="E15">
         <v>-2111.959</v>
@@ -2517,37 +2636,37 @@
         <v>2205.4</v>
       </c>
       <c r="M15">
-        <v>57.74714121803869</v>
+        <v>56.60132381803869</v>
       </c>
       <c r="N15">
-        <v>2147.652858781961</v>
+        <v>2148.798676181961</v>
       </c>
       <c r="O15">
-        <v>751.6785005736862</v>
+        <v>752.0795366636863</v>
       </c>
       <c r="P15">
-        <v>1395.974358208275</v>
+        <v>1396.719139518275</v>
       </c>
       <c r="Q15">
-        <v>1532.774358208275</v>
+        <v>1533.519139518275</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1007174832994388</v>
+        <v>0.100705088885655</v>
       </c>
       <c r="T15">
         <v>0.7989359431023945</v>
       </c>
       <c r="U15">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.1906351289835</v>
+        <v>38.96375298729576</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2685,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0934117467843793</v>
+        <v>0.09327360318445023</v>
       </c>
       <c r="C16">
-        <v>5350.052083736313</v>
+        <v>5352.995767310873</v>
       </c>
       <c r="D16">
-        <v>5466.650083736313</v>
+        <v>5469.593767310873</v>
       </c>
       <c r="E16">
         <v>-2049.002</v>
@@ -2599,37 +2718,37 @@
         <v>2205.4</v>
       </c>
       <c r="M16">
-        <v>62.18922900404166</v>
+        <v>60.95527180404167</v>
       </c>
       <c r="N16">
-        <v>2143.210770995958</v>
+        <v>2144.444728195958</v>
       </c>
       <c r="O16">
-        <v>750.1237698485852</v>
+        <v>750.5556548685852</v>
       </c>
       <c r="P16">
-        <v>1393.087001147373</v>
+        <v>1393.889073327373</v>
       </c>
       <c r="Q16">
-        <v>1529.887001147373</v>
+        <v>1530.689073327373</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1011523434373978</v>
+        <v>0.1011398508793407</v>
       </c>
       <c r="T16">
         <v>0.8052622598518988</v>
       </c>
       <c r="U16">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V16">
         <v>0.35</v>
       </c>
       <c r="W16">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>35.46273261977039</v>
+        <v>36.18062777391749</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2767,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09323717534347367</v>
+        <v>0.09308997128360744</v>
       </c>
       <c r="C17">
-        <v>5291.0898468421</v>
+        <v>5294.2455877544</v>
       </c>
       <c r="D17">
-        <v>5470.6448468421</v>
+        <v>5473.8005877544</v>
       </c>
       <c r="E17">
         <v>-1986.045</v>
@@ -2681,37 +2800,37 @@
         <v>2205.4</v>
       </c>
       <c r="M17">
-        <v>66.63131679004464</v>
+        <v>65.30921979004464</v>
       </c>
       <c r="N17">
-        <v>2138.768683209955</v>
+        <v>2140.090780209955</v>
       </c>
       <c r="O17">
-        <v>748.5690391234841</v>
+        <v>749.0317730734843</v>
       </c>
       <c r="P17">
-        <v>1390.199644086471</v>
+        <v>1391.059007136471</v>
       </c>
       <c r="Q17">
-        <v>1526.999644086471</v>
+        <v>1527.859007136471</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1015974355786028</v>
+        <v>0.1015848425669955</v>
       </c>
       <c r="T17">
         <v>0.8117374311131561</v>
       </c>
       <c r="U17">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V17">
         <v>0.35</v>
       </c>
       <c r="W17">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.09855044511904</v>
+        <v>33.768585922323</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2849,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09306260390256806</v>
+        <v>0.09290633938276464</v>
       </c>
       <c r="C18">
-        <v>5232.133452576183</v>
+        <v>5235.501884349906</v>
       </c>
       <c r="D18">
-        <v>5474.645452576183</v>
+        <v>5478.013884349905</v>
       </c>
       <c r="E18">
         <v>-1923.088</v>
@@ -2763,37 +2882,37 @@
         <v>2205.4</v>
       </c>
       <c r="M18">
-        <v>71.07340457604761</v>
+        <v>69.66316777604762</v>
       </c>
       <c r="N18">
-        <v>2134.326595423952</v>
+        <v>2135.736832223952</v>
       </c>
       <c r="O18">
-        <v>747.0143083983832</v>
+        <v>747.5078912783832</v>
       </c>
       <c r="P18">
-        <v>1387.312287025569</v>
+        <v>1388.228940945569</v>
       </c>
       <c r="Q18">
-        <v>1524.112287025569</v>
+        <v>1525.028940945569</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1020531251517413</v>
+        <v>0.1020404292948325</v>
       </c>
       <c r="T18">
         <v>0.818366773118729</v>
       </c>
       <c r="U18">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V18">
         <v>0.35</v>
       </c>
       <c r="W18">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.0298910422991</v>
+        <v>31.65804930217781</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2931,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09288803246166243</v>
+        <v>0.09272270748192186</v>
       </c>
       <c r="C19">
-        <v>5173.182913765837</v>
+        <v>5176.764672063388</v>
       </c>
       <c r="D19">
-        <v>5478.651913765837</v>
+        <v>5482.233672063388</v>
       </c>
       <c r="E19">
         <v>-1860.131</v>
@@ -2845,37 +2964,37 @@
         <v>2205.4</v>
       </c>
       <c r="M19">
-        <v>75.51549236205059</v>
+        <v>74.01711576205059</v>
       </c>
       <c r="N19">
-        <v>2129.884507637949</v>
+        <v>2131.382884237949</v>
       </c>
       <c r="O19">
-        <v>745.4595776732821</v>
+        <v>745.9840094832821</v>
       </c>
       <c r="P19">
-        <v>1384.424929964667</v>
+        <v>1385.398874754667</v>
       </c>
       <c r="Q19">
-        <v>1521.224929964667</v>
+        <v>1522.198874754667</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1025197951965217</v>
+        <v>0.1025069940161113</v>
       </c>
       <c r="T19">
         <v>0.8251558583051591</v>
       </c>
       <c r="U19">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.20460333392856</v>
+        <v>29.79581110793205</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +3013,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.09271346102075684</v>
+        <v>0.09253907558107907</v>
       </c>
       <c r="C20">
-        <v>5114.238243275915</v>
+        <v>5118.033965907001</v>
       </c>
       <c r="D20">
-        <v>5482.664243275915</v>
+        <v>5486.459965907002</v>
       </c>
       <c r="E20">
         <v>-1797.174</v>
@@ -2927,37 +3046,37 @@
         <v>2205.4</v>
       </c>
       <c r="M20">
-        <v>79.95758014805357</v>
+        <v>78.37106374805357</v>
       </c>
       <c r="N20">
-        <v>2125.442419851946</v>
+        <v>2127.028936251946</v>
       </c>
       <c r="O20">
-        <v>743.904846948181</v>
+        <v>744.460127688181</v>
       </c>
       <c r="P20">
-        <v>1381.537572903765</v>
+        <v>1382.568808563765</v>
       </c>
       <c r="Q20">
-        <v>1518.337572903765</v>
+        <v>1519.368808563765</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1029978474375162</v>
+        <v>0.1029849383647384</v>
       </c>
       <c r="T20">
         <v>0.8321105309351606</v>
       </c>
       <c r="U20">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V20">
         <v>0.35</v>
       </c>
       <c r="W20">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.58212537093253</v>
+        <v>28.14048826860249</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3095,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09253888957985122</v>
+        <v>0.09235544368023631</v>
       </c>
       <c r="C21">
-        <v>5055.299454008986</v>
+        <v>5059.309780939222</v>
       </c>
       <c r="D21">
-        <v>5486.682454008986</v>
+        <v>5490.692780939222</v>
       </c>
       <c r="E21">
         <v>-1734.217</v>
@@ -3009,37 +3128,37 @@
         <v>2205.4</v>
       </c>
       <c r="M21">
-        <v>84.39966793405655</v>
+        <v>82.72501173405655</v>
       </c>
       <c r="N21">
-        <v>2121.000332065943</v>
+        <v>2122.674988265943</v>
       </c>
       <c r="O21">
-        <v>742.35011622308</v>
+        <v>742.9362458930801</v>
       </c>
       <c r="P21">
-        <v>1378.650215842863</v>
+        <v>1379.738742372863</v>
       </c>
       <c r="Q21">
-        <v>1515.450215842863</v>
+        <v>1516.538742372863</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1034877034375476</v>
+        <v>0.1034746838083934</v>
       </c>
       <c r="T21">
         <v>0.8392369238770143</v>
       </c>
       <c r="U21">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V21">
         <v>0.35</v>
       </c>
       <c r="W21">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.13043456193608</v>
+        <v>26.65940993867605</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3177,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09236431813894559</v>
+        <v>0.0921718117793935</v>
       </c>
       <c r="C22">
-        <v>4996.366558905468</v>
+        <v>5000.592132265034</v>
       </c>
       <c r="D22">
-        <v>5490.706558905468</v>
+        <v>5494.932132265034</v>
       </c>
       <c r="E22">
         <v>-1671.26</v>
@@ -3091,37 +3210,37 @@
         <v>2205.4</v>
       </c>
       <c r="M22">
-        <v>88.84175572005952</v>
+        <v>87.07895972005953</v>
       </c>
       <c r="N22">
-        <v>2116.55824427994</v>
+        <v>2118.32104027994</v>
       </c>
       <c r="O22">
-        <v>740.7953854979789</v>
+        <v>741.412364097979</v>
       </c>
       <c r="P22">
-        <v>1375.762858781961</v>
+        <v>1376.908676181961</v>
       </c>
       <c r="Q22">
-        <v>1512.562858781961</v>
+        <v>1513.708676181961</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1039898058375798</v>
+        <v>0.1039766728881397</v>
       </c>
       <c r="T22">
         <v>0.8465414766424141</v>
       </c>
       <c r="U22">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.82391283383928</v>
+        <v>25.32643944174224</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3259,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09218974669803998</v>
+        <v>0.09198817987855074</v>
       </c>
       <c r="C23">
-        <v>4937.439570943774</v>
+        <v>4941.881035036107</v>
       </c>
       <c r="D23">
-        <v>5494.736570943774</v>
+        <v>5499.178035036108</v>
       </c>
       <c r="E23">
         <v>-1608.303</v>
@@ -3173,37 +3292,37 @@
         <v>2205.4</v>
       </c>
       <c r="M23">
-        <v>93.2838435060625</v>
+        <v>91.43290770606249</v>
       </c>
       <c r="N23">
-        <v>2112.116156493937</v>
+        <v>2113.967092293937</v>
       </c>
       <c r="O23">
-        <v>739.240654772878</v>
+        <v>739.8884823028779</v>
       </c>
       <c r="P23">
-        <v>1372.875501721059</v>
+        <v>1374.078609991059</v>
       </c>
       <c r="Q23">
-        <v>1509.675501721059</v>
+        <v>1510.878609991059</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1045046196907774</v>
+        <v>0.1044913705521834</v>
       </c>
       <c r="T23">
         <v>0.8540309547942797</v>
       </c>
       <c r="U23">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V23">
         <v>0.35</v>
       </c>
       <c r="W23">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3330,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.6418217465136</v>
+        <v>24.12041851594499</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3341,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09201517525713436</v>
+        <v>0.09180454797770793</v>
       </c>
       <c r="C24">
-        <v>4878.518503140445</v>
+        <v>4883.176504450982</v>
       </c>
       <c r="D24">
-        <v>5498.772503140445</v>
+        <v>5503.430504450982</v>
       </c>
       <c r="E24">
         <v>-1545.346</v>
@@ -3255,37 +3374,37 @@
         <v>2205.4</v>
       </c>
       <c r="M24">
-        <v>97.72593129206547</v>
+        <v>95.78685569206547</v>
       </c>
       <c r="N24">
-        <v>2107.674068707934</v>
+        <v>2109.613144307934</v>
       </c>
       <c r="O24">
-        <v>737.6859240477769</v>
+        <v>738.364600507777</v>
       </c>
       <c r="P24">
-        <v>1369.988144660157</v>
+        <v>1371.248543800157</v>
       </c>
       <c r="Q24">
-        <v>1506.788144660157</v>
+        <v>1508.048543800157</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1050326338991852</v>
+        <v>0.1050192655922283</v>
       </c>
       <c r="T24">
         <v>0.8617124708474753</v>
       </c>
       <c r="U24">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.56719348530844</v>
+        <v>23.02403585612932</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3423,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09184060381622874</v>
+        <v>0.09162091607686515</v>
       </c>
       <c r="C25">
-        <v>4819.603368550294</v>
+        <v>4824.47855575524</v>
       </c>
       <c r="D25">
-        <v>5502.814368550295</v>
+        <v>5507.68955575524</v>
       </c>
       <c r="E25">
         <v>-1482.389</v>
@@ -3337,37 +3456,37 @@
         <v>2205.4</v>
       </c>
       <c r="M25">
-        <v>102.1680190780684</v>
+        <v>100.1408036780685</v>
       </c>
       <c r="N25">
-        <v>2103.231980921931</v>
+        <v>2105.259196321931</v>
       </c>
       <c r="O25">
-        <v>736.1311933226758</v>
+        <v>736.8407187126759</v>
       </c>
       <c r="P25">
-        <v>1367.100787599255</v>
+        <v>1368.418477609255</v>
       </c>
       <c r="Q25">
-        <v>1503.900787599255</v>
+        <v>1505.218477609255</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1055743627623568</v>
+        <v>0.1055608721917548</v>
       </c>
       <c r="T25">
         <v>0.8695935067981564</v>
       </c>
       <c r="U25">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V25">
         <v>0.35</v>
       </c>
       <c r="W25">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.58601115986025</v>
+        <v>22.0229908189063</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3505,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09166603237532313</v>
+        <v>0.09143728417602236</v>
       </c>
       <c r="C26">
-        <v>4760.69418026655</v>
+        <v>4765.787204241698</v>
       </c>
       <c r="D26">
-        <v>5506.862180266549</v>
+        <v>5511.955204241697</v>
       </c>
       <c r="E26">
         <v>-1419.432</v>
@@ -3419,37 +3538,37 @@
         <v>2205.4</v>
       </c>
       <c r="M26">
-        <v>106.6101068640714</v>
+        <v>104.4947516640714</v>
       </c>
       <c r="N26">
-        <v>2098.789893135928</v>
+        <v>2100.905248335928</v>
       </c>
       <c r="O26">
-        <v>734.5764625975748</v>
+        <v>735.3168369175748</v>
       </c>
       <c r="P26">
-        <v>1364.213430538353</v>
+        <v>1365.588411418353</v>
       </c>
       <c r="Q26">
-        <v>1501.013430538353</v>
+        <v>1502.388411418353</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1061303476482435</v>
+        <v>0.106116731596532</v>
       </c>
       <c r="T26">
         <v>0.8776819384317501</v>
       </c>
       <c r="U26">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V26">
         <v>0.35</v>
       </c>
       <c r="W26">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.6865940281994</v>
+        <v>21.10536620145187</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3587,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09149146093441751</v>
+        <v>0.09125365227517959</v>
       </c>
       <c r="C27">
-        <v>4701.790951420987</v>
+        <v>4707.102465250584</v>
       </c>
       <c r="D27">
-        <v>5510.915951420987</v>
+        <v>5516.227465250584</v>
       </c>
       <c r="E27">
         <v>-1356.475</v>
@@ -3501,37 +3620,37 @@
         <v>2205.4</v>
       </c>
       <c r="M27">
-        <v>111.0521946500744</v>
+        <v>108.8486996500744</v>
       </c>
       <c r="N27">
-        <v>2094.347805349925</v>
+        <v>2096.551300349925</v>
       </c>
       <c r="O27">
-        <v>733.0217318724738</v>
+        <v>733.7929551224738</v>
       </c>
       <c r="P27">
-        <v>1361.326073477451</v>
+        <v>1362.758345227452</v>
       </c>
       <c r="Q27">
-        <v>1498.126073477451</v>
+        <v>1499.558345227452</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1067011587977538</v>
+        <v>0.1066874139187699</v>
       </c>
       <c r="T27">
         <v>0.8859860615755732</v>
       </c>
       <c r="U27">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V27">
         <v>0.35</v>
       </c>
       <c r="W27">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.85913026707142</v>
+        <v>20.2611515533938</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3669,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.09131688949351188</v>
+        <v>0.0910700203743368</v>
       </c>
       <c r="C28">
-        <v>4642.893695184082</v>
+        <v>4648.424354169723</v>
       </c>
       <c r="D28">
-        <v>5514.975695184083</v>
+        <v>5520.506354169724</v>
       </c>
       <c r="E28">
         <v>-1293.518</v>
@@ -3583,37 +3702,37 @@
         <v>2205.4</v>
       </c>
       <c r="M28">
-        <v>115.4942824360774</v>
+        <v>113.2026476360774</v>
       </c>
       <c r="N28">
-        <v>2089.905717563922</v>
+        <v>2092.197352363922</v>
       </c>
       <c r="O28">
-        <v>731.4670011473728</v>
+        <v>732.2690733273727</v>
       </c>
       <c r="P28">
-        <v>1358.43871641655</v>
+        <v>1359.92827903655</v>
       </c>
       <c r="Q28">
-        <v>1495.23871641655</v>
+        <v>1496.72827903655</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1072873972756292</v>
+        <v>0.1072735200875548</v>
       </c>
       <c r="T28">
         <v>0.8945146204800399</v>
       </c>
       <c r="U28">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.09531756449175</v>
+        <v>19.48187649364788</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3751,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09114231805260628</v>
+        <v>0.09088638847349402</v>
       </c>
       <c r="C29">
-        <v>4584.002424765147</v>
+        <v>4589.752886434726</v>
       </c>
       <c r="D29">
-        <v>5519.041424765147</v>
+        <v>5524.791886434726</v>
       </c>
       <c r="E29">
         <v>-1230.561</v>
@@ -3665,37 +3784,37 @@
         <v>2205.4</v>
       </c>
       <c r="M29">
-        <v>119.9363702220804</v>
+        <v>117.5565956220804</v>
       </c>
       <c r="N29">
-        <v>2085.463629777919</v>
+        <v>2087.843404377919</v>
       </c>
       <c r="O29">
-        <v>729.9122704222717</v>
+        <v>730.7451915322717</v>
       </c>
       <c r="P29">
-        <v>1355.551359355647</v>
+        <v>1357.098212845648</v>
       </c>
       <c r="Q29">
-        <v>1492.351359355647</v>
+        <v>1493.898212845648</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1078896970816657</v>
+        <v>0.1078756839595941</v>
       </c>
       <c r="T29">
         <v>0.9032768385325745</v>
       </c>
       <c r="U29">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.38808358062169</v>
+        <v>18.76032551240166</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3833,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09096774661170066</v>
+        <v>0.09070275657265123</v>
       </c>
       <c r="C30">
-        <v>4525.117153412475</v>
+        <v>4531.088077529165</v>
       </c>
       <c r="D30">
-        <v>5523.113153412475</v>
+        <v>5529.084077529165</v>
       </c>
       <c r="E30">
         <v>-1167.604</v>
@@ -3747,37 +3866,37 @@
         <v>2205.4</v>
       </c>
       <c r="M30">
-        <v>124.3784580080833</v>
+        <v>121.9105436080833</v>
       </c>
       <c r="N30">
-        <v>2081.021541991916</v>
+        <v>2083.489456391917</v>
       </c>
       <c r="O30">
-        <v>728.3575396971706</v>
+        <v>729.2213097371707</v>
       </c>
       <c r="P30">
-        <v>1352.664002294746</v>
+        <v>1354.268146654746</v>
       </c>
       <c r="Q30">
-        <v>1489.464002294746</v>
+        <v>1491.068146654746</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1085087274378698</v>
+        <v>0.1084945746058567</v>
       </c>
       <c r="T30">
         <v>0.9122824515310125</v>
       </c>
       <c r="U30">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V30">
         <v>0.35</v>
       </c>
       <c r="W30">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.7313663098852</v>
+        <v>18.09031388695875</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3915,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09079317517079505</v>
+        <v>0.09051912467180843</v>
       </c>
       <c r="C31">
-        <v>4466.237894413485</v>
+        <v>4472.429942984771</v>
       </c>
       <c r="D31">
-        <v>5527.190894413485</v>
+        <v>5533.38294298477</v>
       </c>
       <c r="E31">
         <v>-1104.647</v>
@@ -3829,37 +3948,37 @@
         <v>2205.4</v>
       </c>
       <c r="M31">
-        <v>128.8205457940863</v>
+        <v>126.2644915940863</v>
       </c>
       <c r="N31">
-        <v>2076.579454205913</v>
+        <v>2079.135508405913</v>
       </c>
       <c r="O31">
-        <v>726.8028089720697</v>
+        <v>727.6974279420696</v>
       </c>
       <c r="P31">
-        <v>1349.776645233844</v>
+        <v>1351.438080463844</v>
       </c>
       <c r="Q31">
-        <v>1486.576645233844</v>
+        <v>1488.238080463844</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1091451952688965</v>
+        <v>0.1091308987914506</v>
       </c>
       <c r="T31">
         <v>0.9215417437688432</v>
       </c>
       <c r="U31">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V31">
         <v>0.35</v>
       </c>
       <c r="W31">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.1199398854064</v>
+        <v>17.46650995982224</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3997,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09061860372988942</v>
+        <v>0.09033549277096564</v>
       </c>
       <c r="C32">
-        <v>4407.364661094864</v>
+        <v>4413.778498381611</v>
       </c>
       <c r="D32">
-        <v>5531.274661094864</v>
+        <v>5537.688498381611</v>
       </c>
       <c r="E32">
         <v>-1041.69</v>
@@ -3911,37 +4030,37 @@
         <v>2205.4</v>
       </c>
       <c r="M32">
-        <v>133.2626335800893</v>
+        <v>130.6184395800893</v>
       </c>
       <c r="N32">
-        <v>2072.13736641991</v>
+        <v>2074.78156041991</v>
       </c>
       <c r="O32">
-        <v>725.2480782469686</v>
+        <v>726.1735461469686</v>
       </c>
       <c r="P32">
-        <v>1346.889288172942</v>
+        <v>1348.608014272942</v>
       </c>
       <c r="Q32">
-        <v>1483.689288172942</v>
+        <v>1485.408014272942</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1097998478950955</v>
+        <v>0.1097854036680615</v>
       </c>
       <c r="T32">
         <v>0.9310655872134691</v>
       </c>
       <c r="U32">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V32">
         <v>0.35</v>
       </c>
       <c r="W32">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.54927522255952</v>
+        <v>16.8842929611615</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4079,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.0904440322889838</v>
+        <v>0.09015186087012286</v>
       </c>
       <c r="C33">
-        <v>4348.497466822715</v>
+        <v>4355.133759348288</v>
       </c>
       <c r="D33">
-        <v>5535.364466822715</v>
+        <v>5542.000759348288</v>
       </c>
       <c r="E33">
         <v>-978.7329999999999</v>
@@ -3993,37 +4112,37 @@
         <v>2205.4</v>
       </c>
       <c r="M33">
-        <v>137.7047213660923</v>
+        <v>134.9723875660922</v>
       </c>
       <c r="N33">
-        <v>2067.695278633907</v>
+        <v>2070.427612433908</v>
       </c>
       <c r="O33">
-        <v>723.6933475218676</v>
+        <v>724.6496643518676</v>
       </c>
       <c r="P33">
-        <v>1344.00193111204</v>
+        <v>1345.77794808204</v>
       </c>
       <c r="Q33">
-        <v>1480.80193111204</v>
+        <v>1482.57794808204</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.110473475959735</v>
+        <v>0.1104588797005162</v>
       </c>
       <c r="T33">
         <v>0.9408654840912727</v>
       </c>
       <c r="U33">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.01542763473502</v>
+        <v>16.33963834951113</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4161,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09026946084807819</v>
+        <v>0.08996822896928008</v>
       </c>
       <c r="C34">
-        <v>4289.636325002703</v>
+        <v>4296.495741562117</v>
       </c>
       <c r="D34">
-        <v>5539.460325002702</v>
+        <v>5546.319741562118</v>
       </c>
       <c r="E34">
         <v>-915.7759999999998</v>
@@ -4075,37 +4194,37 @@
         <v>2205.4</v>
       </c>
       <c r="M34">
-        <v>142.1468091520952</v>
+        <v>139.3263355520952</v>
       </c>
       <c r="N34">
-        <v>2063.253190847905</v>
+        <v>2066.073664447904</v>
       </c>
       <c r="O34">
-        <v>722.1386167967665</v>
+        <v>723.1257825567665</v>
       </c>
       <c r="P34">
-        <v>1341.114574051138</v>
+        <v>1342.947881891138</v>
       </c>
       <c r="Q34">
-        <v>1477.914574051138</v>
+        <v>1479.747881891138</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1111669166145109</v>
+        <v>0.1111521638515725</v>
       </c>
       <c r="T34">
         <v>0.9509536132301881</v>
       </c>
       <c r="U34">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V34">
         <v>0.35</v>
       </c>
       <c r="W34">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.51494552114955</v>
+        <v>15.8290246510889</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4243,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09009488940717257</v>
+        <v>0.08978459706843728</v>
       </c>
       <c r="C35">
-        <v>4230.781249080195</v>
+        <v>4237.864460749332</v>
       </c>
       <c r="D35">
-        <v>5543.562249080195</v>
+        <v>5550.645460749332</v>
       </c>
       <c r="E35">
         <v>-852.819</v>
@@ -4157,37 +4276,37 @@
         <v>2205.4</v>
       </c>
       <c r="M35">
-        <v>146.5888969380982</v>
+        <v>143.6802835380982</v>
       </c>
       <c r="N35">
-        <v>2058.811103061902</v>
+        <v>2061.719716461901</v>
       </c>
       <c r="O35">
-        <v>720.5838860716655</v>
+        <v>721.6019007616654</v>
       </c>
       <c r="P35">
-        <v>1338.227216990236</v>
+        <v>1340.117815700236</v>
       </c>
       <c r="Q35">
-        <v>1475.027216990236</v>
+        <v>1476.917815700236</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.111881056990325</v>
+        <v>0.1118661430519141</v>
       </c>
       <c r="T35">
         <v>0.9613428805523546</v>
       </c>
       <c r="U35">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V35">
         <v>0.35</v>
       </c>
       <c r="W35">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.04479565687229</v>
+        <v>15.34935723741954</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4325,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08992031796626695</v>
+        <v>0.0896009651675945</v>
       </c>
       <c r="C36">
-        <v>4171.93225254042</v>
+        <v>4179.239932685251</v>
       </c>
       <c r="D36">
-        <v>5547.67025254042</v>
+        <v>5554.977932685251</v>
       </c>
       <c r="E36">
         <v>-789.8619999999996</v>
@@ -4239,37 +4358,37 @@
         <v>2205.4</v>
       </c>
       <c r="M36">
-        <v>151.0309847241012</v>
+        <v>148.0342315241012</v>
       </c>
       <c r="N36">
-        <v>2054.369015275899</v>
+        <v>2057.365768475898</v>
       </c>
       <c r="O36">
-        <v>719.0291553465645</v>
+        <v>720.0780189665643</v>
       </c>
       <c r="P36">
-        <v>1335.339859929334</v>
+        <v>1337.287749509334</v>
       </c>
       <c r="Q36">
-        <v>1472.139859929334</v>
+        <v>1474.087749509334</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1126168379835879</v>
+        <v>0.1126017579855993</v>
       </c>
       <c r="T36">
         <v>0.9720469741570111</v>
       </c>
       <c r="U36">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V36">
         <v>0.35</v>
       </c>
       <c r="W36">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.60230166696428</v>
+        <v>14.89790555396602</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4407,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08974574652536134</v>
+        <v>0.08941733326675172</v>
       </c>
       <c r="C37">
-        <v>4113.089348908603</v>
+        <v>4120.622173194497</v>
       </c>
       <c r="D37">
-        <v>5551.784348908604</v>
+        <v>5559.317173194497</v>
       </c>
       <c r="E37">
         <v>-726.9049999999997</v>
@@ -4321,37 +4440,37 @@
         <v>2205.4</v>
       </c>
       <c r="M37">
-        <v>155.4730725101042</v>
+        <v>152.3881795101042</v>
       </c>
       <c r="N37">
-        <v>2049.926927489896</v>
+        <v>2053.011820489895</v>
       </c>
       <c r="O37">
-        <v>717.4744246214634</v>
+        <v>718.5541371714634</v>
       </c>
       <c r="P37">
-        <v>1332.452502868432</v>
+        <v>1334.457683318432</v>
       </c>
       <c r="Q37">
-        <v>1469.252502868432</v>
+        <v>1471.257683318432</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1133752583920282</v>
+        <v>0.1133600072249365</v>
       </c>
       <c r="T37">
         <v>0.9830804244879647</v>
       </c>
       <c r="U37">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.18509304790816</v>
+        <v>14.472251109567</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4489,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08957117508445574</v>
+        <v>0.08923370136590893</v>
       </c>
       <c r="C38">
-        <v>4054.252551750123</v>
+        <v>4062.01119815117</v>
       </c>
       <c r="D38">
-        <v>5555.904551750123</v>
+        <v>5563.66319815117</v>
       </c>
       <c r="E38">
         <v>-663.9479999999999</v>
@@ -4403,37 +4522,37 @@
         <v>2205.4</v>
       </c>
       <c r="M38">
-        <v>159.9151602961071</v>
+        <v>156.7421274961071</v>
       </c>
       <c r="N38">
-        <v>2045.484839703892</v>
+        <v>2048.657872503893</v>
       </c>
       <c r="O38">
-        <v>715.9196938963623</v>
+        <v>717.0302553763623</v>
       </c>
       <c r="P38">
-        <v>1329.56514580753</v>
+        <v>1331.62761712753</v>
       </c>
       <c r="Q38">
-        <v>1466.36514580753</v>
+        <v>1468.42761712753</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1141573794382322</v>
+        <v>0.1141419517530028</v>
       </c>
       <c r="T38">
         <v>0.9944586701417606</v>
       </c>
       <c r="U38">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V38">
         <v>0.35</v>
       </c>
       <c r="W38">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.79106268546627</v>
+        <v>14.07024413430125</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4571,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08939660364355012</v>
+        <v>0.08905006946506615</v>
       </c>
       <c r="C39">
-        <v>3995.421874670654</v>
+        <v>4003.407023479047</v>
       </c>
       <c r="D39">
-        <v>5560.030874670654</v>
+        <v>5568.016023479047</v>
       </c>
       <c r="E39">
         <v>-600.991</v>
@@ -4485,37 +4604,37 @@
         <v>2205.4</v>
       </c>
       <c r="M39">
-        <v>164.3572480821101</v>
+        <v>161.0960754821101</v>
       </c>
       <c r="N39">
-        <v>2041.04275191789</v>
+        <v>2044.30392451789</v>
       </c>
       <c r="O39">
-        <v>714.3649631712613</v>
+        <v>715.5063735812613</v>
       </c>
       <c r="P39">
-        <v>1326.677788746628</v>
+        <v>1328.797550936628</v>
       </c>
       <c r="Q39">
-        <v>1463.477788746628</v>
+        <v>1465.597550936628</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1149643297239983</v>
+        <v>0.1149487199168809</v>
       </c>
       <c r="T39">
         <v>1.006198129943296</v>
       </c>
       <c r="U39">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V39">
         <v>0.35</v>
       </c>
       <c r="W39">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.41833126153475</v>
+        <v>13.68996726580662</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4653,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08922203220264449</v>
+        <v>0.08886643756422337</v>
       </c>
       <c r="C40">
-        <v>3936.597331316325</v>
+        <v>3944.809665151784</v>
       </c>
       <c r="D40">
-        <v>5564.163331316326</v>
+        <v>5572.375665151784</v>
       </c>
       <c r="E40">
         <v>-538.0339999999997</v>
@@ -4567,37 +4686,37 @@
         <v>2205.4</v>
       </c>
       <c r="M40">
-        <v>168.7993358681131</v>
+        <v>165.4500234681131</v>
       </c>
       <c r="N40">
-        <v>2036.600664131887</v>
+        <v>2039.949976531886</v>
       </c>
       <c r="O40">
-        <v>712.8102324461603</v>
+        <v>713.9824917861603</v>
       </c>
       <c r="P40">
-        <v>1323.790431685726</v>
+        <v>1325.967484745726</v>
       </c>
       <c r="Q40">
-        <v>1460.590431685726</v>
+        <v>1462.767484745726</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1157973106641439</v>
+        <v>0.1157815128602389</v>
       </c>
       <c r="T40">
         <v>1.018316281996494</v>
       </c>
       <c r="U40">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V40">
         <v>0.35</v>
       </c>
       <c r="W40">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.06521728096804</v>
+        <v>13.32970496933802</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4735,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08904746076173889</v>
+        <v>0.08868280566338058</v>
       </c>
       <c r="C41">
-        <v>3877.778935373861</v>
+        <v>3886.219139193096</v>
       </c>
       <c r="D41">
-        <v>5568.301935373861</v>
+        <v>5576.742139193097</v>
       </c>
       <c r="E41">
         <v>-475.0769999999998</v>
@@ -4649,37 +4768,37 @@
         <v>2205.4</v>
       </c>
       <c r="M41">
-        <v>173.2414236541161</v>
+        <v>169.8039714541161</v>
       </c>
       <c r="N41">
-        <v>2032.158576345884</v>
+        <v>2035.596028545884</v>
       </c>
       <c r="O41">
-        <v>711.2555017210592</v>
+        <v>712.4586099910592</v>
       </c>
       <c r="P41">
-        <v>1320.903074624825</v>
+        <v>1323.137418554824</v>
       </c>
       <c r="Q41">
-        <v>1457.703074624824</v>
+        <v>1459.937418554824</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1166576024547861</v>
+        <v>0.1166416104902643</v>
       </c>
       <c r="T41">
         <v>1.030831750510453</v>
       </c>
       <c r="U41">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V41">
         <v>0.35</v>
       </c>
       <c r="W41">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>12.73021170966117</v>
+        <v>12.98791766243192</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4817,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08915888932083327</v>
+        <v>0.08888917376253778</v>
       </c>
       <c r="C42">
-        <v>3812.179563332174</v>
+        <v>3818.355510246231</v>
       </c>
       <c r="D42">
-        <v>5565.659563332175</v>
+        <v>5571.835510246232</v>
       </c>
       <c r="E42">
         <v>-412.1199999999994</v>
@@ -4731,37 +4850,37 @@
         <v>2205.4</v>
       </c>
       <c r="M42">
-        <v>180.453619440119</v>
+        <v>177.935339440119</v>
       </c>
       <c r="N42">
-        <v>2024.946380559881</v>
+        <v>2027.46466055988</v>
       </c>
       <c r="O42">
-        <v>708.7312331959582</v>
+        <v>709.6126311959581</v>
       </c>
       <c r="P42">
-        <v>1316.215147363922</v>
+        <v>1317.852029363922</v>
       </c>
       <c r="Q42">
-        <v>1453.015147363922</v>
+        <v>1454.652029363922</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1175465706384497</v>
+        <v>0.1175303780412906</v>
       </c>
       <c r="T42">
         <v>1.043764401308209</v>
       </c>
       <c r="U42">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V42">
         <v>0.35</v>
       </c>
       <c r="W42">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.22142291655076</v>
+        <v>12.39439004606607</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4899,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08899146787992764</v>
+        <v>0.08871529186169499</v>
       </c>
       <c r="C43">
-        <v>3753.193675440183</v>
+        <v>3759.532171004503</v>
       </c>
       <c r="D43">
-        <v>5569.630675440183</v>
+        <v>5575.969171004504</v>
       </c>
       <c r="E43">
         <v>-349.1629999999996</v>
@@ -4813,37 +4932,37 @@
         <v>2205.4</v>
       </c>
       <c r="M43">
-        <v>184.964959926122</v>
+        <v>182.383722926122</v>
       </c>
       <c r="N43">
-        <v>2020.435040073878</v>
+        <v>2023.016277073878</v>
       </c>
       <c r="O43">
-        <v>707.1522640258571</v>
+        <v>708.0556969758571</v>
       </c>
       <c r="P43">
-        <v>1313.28277604802</v>
+        <v>1314.96058009802</v>
       </c>
       <c r="Q43">
-        <v>1450.08277604802</v>
+        <v>1451.76058009802</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1184656733368137</v>
+        <v>0.118449273305911</v>
       </c>
       <c r="T43">
         <v>1.057135447048263</v>
       </c>
       <c r="U43">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V43">
         <v>0.35</v>
       </c>
       <c r="W43">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.92333943078123</v>
+        <v>12.09208784982056</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4981,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08882404643902204</v>
+        <v>0.08854140996085223</v>
       </c>
       <c r="C44">
-        <v>3694.21345839132</v>
+        <v>3700.714969717616</v>
       </c>
       <c r="D44">
-        <v>5573.607458391321</v>
+        <v>5580.108969717616</v>
       </c>
       <c r="E44">
         <v>-286.2059999999997</v>
@@ -4895,37 +5014,37 @@
         <v>2205.4</v>
       </c>
       <c r="M44">
-        <v>189.476300412125</v>
+        <v>186.832106412125</v>
       </c>
       <c r="N44">
-        <v>2015.923699587875</v>
+        <v>2018.567893587875</v>
       </c>
       <c r="O44">
-        <v>705.5732948557561</v>
+        <v>706.498762755756</v>
       </c>
       <c r="P44">
-        <v>1310.350404732118</v>
+        <v>1312.069130832118</v>
       </c>
       <c r="Q44">
-        <v>1447.150404732118</v>
+        <v>1448.869130832118</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1194164692316731</v>
+        <v>0.119399854614139</v>
       </c>
       <c r="T44">
         <v>1.070967563331078</v>
       </c>
       <c r="U44">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V44">
         <v>0.35</v>
       </c>
       <c r="W44">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.63945039671501</v>
+        <v>11.80418099625341</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5063,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08865662499811641</v>
+        <v>0.08836752806000941</v>
       </c>
       <c r="C45">
-        <v>3635.238924341419</v>
+        <v>3641.90392006684</v>
       </c>
       <c r="D45">
-        <v>5577.589924341419</v>
+        <v>5584.25492006684</v>
       </c>
       <c r="E45">
         <v>-223.2489999999998</v>
@@ -4977,37 +5096,37 @@
         <v>2205.4</v>
       </c>
       <c r="M45">
-        <v>193.9876408981279</v>
+        <v>191.2804898981279</v>
       </c>
       <c r="N45">
-        <v>2011.412359101872</v>
+        <v>2014.119510101872</v>
       </c>
       <c r="O45">
-        <v>703.9943256856551</v>
+        <v>704.941828535655</v>
       </c>
       <c r="P45">
-        <v>1307.418033416217</v>
+        <v>1309.177681566217</v>
       </c>
       <c r="Q45">
-        <v>1444.218033416216</v>
+        <v>1445.977681566216</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1204006263860012</v>
+        <v>0.1203837896524802</v>
       </c>
       <c r="T45">
         <v>1.085285017027324</v>
       </c>
       <c r="U45">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V45">
         <v>0.35</v>
       </c>
       <c r="W45">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.36876550376815</v>
+        <v>11.52966515913123</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5145,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08848920355721079</v>
+        <v>0.08819364615916664</v>
       </c>
       <c r="C46">
-        <v>3576.270085481074</v>
+        <v>3583.099035774133</v>
       </c>
       <c r="D46">
-        <v>5581.578085481074</v>
+        <v>5588.407035774133</v>
       </c>
       <c r="E46">
         <v>-160.2919999999999</v>
@@ -5059,37 +5178,37 @@
         <v>2205.4</v>
       </c>
       <c r="M46">
-        <v>198.4989813841309</v>
+        <v>195.7288733841309</v>
       </c>
       <c r="N46">
-        <v>2006.901018615869</v>
+        <v>2009.671126615869</v>
       </c>
       <c r="O46">
-        <v>702.415356515554</v>
+        <v>703.384894315554</v>
       </c>
       <c r="P46">
-        <v>1304.485662100315</v>
+        <v>1306.286232300315</v>
       </c>
       <c r="Q46">
-        <v>1441.285662100315</v>
+        <v>1443.086232300315</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1214199320101268</v>
+        <v>0.1214028652279051</v>
       </c>
       <c r="T46">
         <v>1.100113808355579</v>
       </c>
       <c r="U46">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V46">
         <v>0.35</v>
       </c>
       <c r="W46">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5216,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.1103844695916</v>
+        <v>11.26762731460552</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5227,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08832178211630518</v>
+        <v>0.08801976425832385</v>
       </c>
       <c r="C47">
-        <v>3517.306954035771</v>
+        <v>3524.300330602297</v>
       </c>
       <c r="D47">
-        <v>5585.571954035771</v>
+        <v>5592.565330602297</v>
       </c>
       <c r="E47">
         <v>-97.33499999999958</v>
@@ -5141,37 +5260,37 @@
         <v>2205.4</v>
       </c>
       <c r="M47">
-        <v>203.0103218701339</v>
+        <v>200.1772568701339</v>
       </c>
       <c r="N47">
-        <v>2002.389678129866</v>
+        <v>2005.222743129866</v>
       </c>
       <c r="O47">
-        <v>700.836387345453</v>
+        <v>701.8279600954529</v>
       </c>
       <c r="P47">
-        <v>1301.553290784413</v>
+        <v>1303.394783034413</v>
       </c>
       <c r="Q47">
-        <v>1438.353290784413</v>
+        <v>1440.194783034413</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1224763032933114</v>
+        <v>0.1224589980969818</v>
       </c>
       <c r="T47">
         <v>1.115481828459408</v>
       </c>
       <c r="U47">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.86348703693401</v>
+        <v>11.01723559650318</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5309,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08815436067539956</v>
+        <v>0.08784588235748107</v>
       </c>
       <c r="C48">
-        <v>3458.349542266018</v>
+        <v>3465.507818355123</v>
       </c>
       <c r="D48">
-        <v>5589.571542266018</v>
+        <v>5596.729818355123</v>
       </c>
       <c r="E48">
         <v>-34.3779999999997</v>
@@ -5223,37 +5342,37 @@
         <v>2205.4</v>
       </c>
       <c r="M48">
-        <v>207.5216623561369</v>
+        <v>204.6256403561369</v>
       </c>
       <c r="N48">
-        <v>1997.878337643863</v>
+        <v>2000.774359643863</v>
       </c>
       <c r="O48">
-        <v>699.257418175352</v>
+        <v>700.2710258753519</v>
       </c>
       <c r="P48">
-        <v>1298.620919468511</v>
+        <v>1300.503333768511</v>
       </c>
       <c r="Q48">
-        <v>1435.420919468511</v>
+        <v>1437.303333768511</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1235717994388363</v>
+        <v>0.1235542469982465</v>
       </c>
       <c r="T48">
         <v>1.131419034493008</v>
       </c>
       <c r="U48">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V48">
         <v>0.35</v>
       </c>
       <c r="W48">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.62732427526153</v>
+        <v>10.77773047484007</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5391,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08798693923449395</v>
+        <v>0.08767200045663828</v>
       </c>
       <c r="C49">
-        <v>3399.397862467458</v>
+        <v>3406.721512877552</v>
       </c>
       <c r="D49">
-        <v>5593.576862467458</v>
+        <v>5600.900512877553</v>
       </c>
       <c r="E49">
         <v>28.57900000000063</v>
@@ -5305,37 +5424,37 @@
         <v>2205.4</v>
       </c>
       <c r="M49">
-        <v>212.0330028421399</v>
+        <v>209.0740238421399</v>
       </c>
       <c r="N49">
-        <v>1993.36699715786</v>
+        <v>1996.32597615786</v>
       </c>
       <c r="O49">
-        <v>697.6784490052509</v>
+        <v>698.7140916552509</v>
       </c>
       <c r="P49">
-        <v>1295.688548152609</v>
+        <v>1297.611884502609</v>
       </c>
       <c r="Q49">
-        <v>1432.488548152609</v>
+        <v>1434.411884502609</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1247086350615507</v>
+        <v>0.1246908260467287</v>
       </c>
       <c r="T49">
         <v>1.147957644527875</v>
       </c>
       <c r="U49">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V49">
         <v>0.35</v>
       </c>
       <c r="W49">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.40121099280915</v>
+        <v>10.54841706048177</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5473,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08781951779358833</v>
+        <v>0.08749811855579551</v>
       </c>
       <c r="C50">
-        <v>3340.45192697101</v>
+        <v>3347.941428055827</v>
       </c>
       <c r="D50">
-        <v>5597.58792697101</v>
+        <v>5605.077428055827</v>
       </c>
       <c r="E50">
         <v>91.53600000000006</v>
@@ -5387,37 +5506,37 @@
         <v>2205.4</v>
       </c>
       <c r="M50">
-        <v>216.5443433281428</v>
+        <v>213.5224073281428</v>
       </c>
       <c r="N50">
-        <v>1988.855656671857</v>
+        <v>1991.877592671857</v>
       </c>
       <c r="O50">
-        <v>696.0994798351499</v>
+        <v>697.1571574351498</v>
       </c>
       <c r="P50">
-        <v>1292.756176836707</v>
+        <v>1294.720435236707</v>
       </c>
       <c r="Q50">
-        <v>1429.556176836707</v>
+        <v>1431.520435236707</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1258891951312927</v>
+        <v>0.1258711196739988</v>
       </c>
       <c r="T50">
         <v>1.165132354948699</v>
       </c>
       <c r="U50">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V50">
         <v>0.35</v>
       </c>
       <c r="W50">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.18451909712563</v>
+        <v>10.32865837172173</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5555,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.0876520963526827</v>
+        <v>0.0873242366549527</v>
       </c>
       <c r="C51">
-        <v>3281.511748142979</v>
+        <v>3289.167577817642</v>
       </c>
       <c r="D51">
-        <v>5601.60474814298</v>
+        <v>5609.260577817642</v>
       </c>
       <c r="E51">
         <v>154.4930000000004</v>
@@ -5469,37 +5588,37 @@
         <v>2205.4</v>
       </c>
       <c r="M51">
-        <v>221.0556838141458</v>
+        <v>217.9707908141458</v>
       </c>
       <c r="N51">
-        <v>1984.344316185854</v>
+        <v>1987.429209185854</v>
       </c>
       <c r="O51">
-        <v>694.5205106650488</v>
+        <v>695.6002232150488</v>
       </c>
       <c r="P51">
-        <v>1289.823805520805</v>
+        <v>1291.828985970805</v>
       </c>
       <c r="Q51">
-        <v>1426.623805520805</v>
+        <v>1428.628985970805</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1271160516743578</v>
+        <v>0.1270976993258676</v>
       </c>
       <c r="T51">
         <v>1.182980583425241</v>
       </c>
       <c r="U51">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V51">
         <v>0.35</v>
       </c>
       <c r="W51">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>9.976671768612862</v>
+        <v>10.11786942536006</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5637,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.0881996749117771</v>
+        <v>0.08715035475410993</v>
       </c>
       <c r="C52">
-        <v>3205.43844969006</v>
+        <v>3230.399976132297</v>
       </c>
       <c r="D52">
-        <v>5588.48844969006</v>
+        <v>5613.449976132297</v>
       </c>
       <c r="E52">
         <v>217.4500000000003</v>
@@ -5551,45 +5670,45 @@
         <v>2205.4</v>
       </c>
       <c r="M52">
-        <v>232.4922943001488</v>
+        <v>222.4191743001488</v>
       </c>
       <c r="N52">
-        <v>1972.907705699851</v>
+        <v>1982.980825699851</v>
       </c>
       <c r="O52">
-        <v>690.5176969949478</v>
+        <v>694.0432889949477</v>
       </c>
       <c r="P52">
-        <v>1282.390008704903</v>
+        <v>1288.937536704903</v>
       </c>
       <c r="Q52">
-        <v>1419.190008704903</v>
+        <v>1425.737536704903</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1283919824791456</v>
+        <v>0.1283733421638112</v>
       </c>
       <c r="T52">
         <v>1.201542741040846</v>
       </c>
       <c r="U52">
-        <v>0.07385748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V52">
         <v>0.35</v>
       </c>
       <c r="W52">
-        <v>0.04800736734440863</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y52">
-        <v>9.485905787280917</v>
+        <v>9.91551203685286</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5719,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08804655347087148</v>
+        <v>0.08754002285326715</v>
       </c>
       <c r="C53">
-        <v>3146.143018625008</v>
+        <v>3158.063251627013</v>
       </c>
       <c r="D53">
-        <v>5592.150018625008</v>
+        <v>5604.070251627013</v>
       </c>
       <c r="E53">
         <v>280.4070000000002</v>
@@ -5633,37 +5752,37 @@
         <v>2205.4</v>
       </c>
       <c r="M53">
-        <v>237.1421401861517</v>
+        <v>232.3259296861517</v>
       </c>
       <c r="N53">
-        <v>1968.257859813848</v>
+        <v>1973.074070313848</v>
       </c>
       <c r="O53">
-        <v>688.8902509348468</v>
+        <v>690.5759246098468</v>
       </c>
       <c r="P53">
-        <v>1279.367608879001</v>
+        <v>1282.498145704001</v>
       </c>
       <c r="Q53">
-        <v>1416.167608879001</v>
+        <v>1419.298145704001</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.129719992092292</v>
+        <v>0.1297010520563648</v>
       </c>
       <c r="T53">
         <v>1.220862537742801</v>
       </c>
       <c r="U53">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V53">
         <v>0.35</v>
       </c>
       <c r="W53">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.299907634589136</v>
+        <v>9.492698481737559</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5801,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08789343202996586</v>
+        <v>0.08737719095242436</v>
       </c>
       <c r="C54">
-        <v>3086.852388814265</v>
+        <v>3099.021973025047</v>
       </c>
       <c r="D54">
-        <v>5595.816388814265</v>
+        <v>5607.985973025047</v>
       </c>
       <c r="E54">
         <v>343.3640000000005</v>
@@ -5715,37 +5834,37 @@
         <v>2205.4</v>
       </c>
       <c r="M54">
-        <v>241.7919860721547</v>
+        <v>236.8813400721548</v>
       </c>
       <c r="N54">
-        <v>1963.608013927845</v>
+        <v>1968.518659927845</v>
       </c>
       <c r="O54">
-        <v>687.2628048747457</v>
+        <v>688.9815309747457</v>
       </c>
       <c r="P54">
-        <v>1276.345209053099</v>
+        <v>1279.537128953099</v>
       </c>
       <c r="Q54">
-        <v>1413.145209053099</v>
+        <v>1416.337128953099</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1311033354393195</v>
+        <v>0.1310840831944414</v>
       </c>
       <c r="T54">
         <v>1.240987325974005</v>
       </c>
       <c r="U54">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V54">
         <v>0.35</v>
       </c>
       <c r="W54">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.121063257000882</v>
+        <v>9.310146587857989</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5883,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08774031058906025</v>
+        <v>0.08721435905158158</v>
       </c>
       <c r="C55">
-        <v>3027.566569707538</v>
+        <v>3039.986170298426</v>
       </c>
       <c r="D55">
-        <v>5599.487569707539</v>
+        <v>5611.907170298427</v>
       </c>
       <c r="E55">
         <v>406.3210000000004</v>
@@ -5797,37 +5916,37 @@
         <v>2205.4</v>
       </c>
       <c r="M55">
-        <v>246.4418319581577</v>
+        <v>241.4367504581577</v>
       </c>
       <c r="N55">
-        <v>1958.958168041842</v>
+        <v>1963.963249541842</v>
       </c>
       <c r="O55">
-        <v>685.6353588146446</v>
+        <v>687.3871373396446</v>
       </c>
       <c r="P55">
-        <v>1273.322809227197</v>
+        <v>1276.576112202197</v>
       </c>
       <c r="Q55">
-        <v>1410.122809227197</v>
+        <v>1413.376112202197</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1325455444606887</v>
+        <v>0.1325259667213723</v>
       </c>
       <c r="T55">
         <v>1.261968488172494</v>
       </c>
       <c r="U55">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V55">
         <v>0.35</v>
       </c>
       <c r="W55">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.948967723849922</v>
+        <v>9.134483444690858</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5965,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08758718914815464</v>
+        <v>0.08705152715073879</v>
       </c>
       <c r="C56">
-        <v>2968.285570779346</v>
+        <v>2980.955854941662</v>
       </c>
       <c r="D56">
-        <v>5603.163570779347</v>
+        <v>5615.833854941662</v>
       </c>
       <c r="E56">
         <v>469.2780000000007</v>
@@ -5879,37 +5998,37 @@
         <v>2205.4</v>
       </c>
       <c r="M56">
-        <v>251.0916778441607</v>
+        <v>245.9921608441607</v>
       </c>
       <c r="N56">
-        <v>1954.308322155839</v>
+        <v>1959.407839155839</v>
       </c>
       <c r="O56">
-        <v>684.0079127545436</v>
+        <v>685.7927437045436</v>
       </c>
       <c r="P56">
-        <v>1270.300409401295</v>
+        <v>1273.615095451295</v>
       </c>
       <c r="Q56">
-        <v>1407.100409401295</v>
+        <v>1410.415095451295</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1340504582221173</v>
+        <v>0.1340305408364307</v>
       </c>
       <c r="T56">
         <v>1.283861874814395</v>
       </c>
       <c r="U56">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V56">
         <v>0.35</v>
       </c>
       <c r="W56">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.783246099334182</v>
+        <v>8.96532634386325</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6047,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08743406770724903</v>
+        <v>0.08688869524989601</v>
       </c>
       <c r="C57">
-        <v>2909.009401529107</v>
+        <v>2921.931038481451</v>
       </c>
       <c r="D57">
-        <v>5606.844401529108</v>
+        <v>5619.766038481452</v>
       </c>
       <c r="E57">
         <v>532.2350000000006</v>
@@ -5961,37 +6080,37 @@
         <v>2205.4</v>
       </c>
       <c r="M57">
-        <v>255.7415237301637</v>
+        <v>250.5475712301637</v>
       </c>
       <c r="N57">
-        <v>1949.658476269836</v>
+        <v>1954.852428769836</v>
       </c>
       <c r="O57">
-        <v>682.3804666944426</v>
+        <v>684.1983500694425</v>
       </c>
       <c r="P57">
-        <v>1267.278009575393</v>
+        <v>1270.654078700393</v>
       </c>
       <c r="Q57">
-        <v>1404.078009575393</v>
+        <v>1407.454078700393</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1356222570396095</v>
+        <v>0.1356019849121584</v>
       </c>
       <c r="T57">
         <v>1.306728300862603</v>
       </c>
       <c r="U57">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V57">
         <v>0.35</v>
       </c>
       <c r="W57">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.623550715709925</v>
+        <v>8.802320410338464</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6129,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08728094626634339</v>
+        <v>0.0867258633490532</v>
       </c>
       <c r="C58">
-        <v>2849.738071481216</v>
+        <v>2862.911732476804</v>
       </c>
       <c r="D58">
-        <v>5610.530071481217</v>
+        <v>5623.703732476804</v>
       </c>
       <c r="E58">
         <v>595.1920000000005</v>
@@ -6043,37 +6162,37 @@
         <v>2205.4</v>
       </c>
       <c r="M58">
-        <v>260.3913696161666</v>
+        <v>255.1029816161667</v>
       </c>
       <c r="N58">
-        <v>1945.008630383833</v>
+        <v>1950.297018383833</v>
       </c>
       <c r="O58">
-        <v>680.7530206343415</v>
+        <v>682.6039564343415</v>
       </c>
       <c r="P58">
-        <v>1264.255609749491</v>
+        <v>1267.693061949491</v>
       </c>
       <c r="Q58">
-        <v>1401.055609749491</v>
+        <v>1404.493061949491</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1372655012578967</v>
+        <v>0.1372448582640554</v>
       </c>
       <c r="T58">
         <v>1.330634109913003</v>
       </c>
       <c r="U58">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V58">
         <v>0.35</v>
       </c>
       <c r="W58">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.469558738643677</v>
+        <v>8.645136117296705</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6211,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08712782482543778</v>
+        <v>0.08656303144821043</v>
       </c>
       <c r="C59">
-        <v>2790.471590185126</v>
+        <v>2803.897948519146</v>
       </c>
       <c r="D59">
-        <v>5614.220590185127</v>
+        <v>5627.646948519146</v>
       </c>
       <c r="E59">
         <v>658.1490000000008</v>
@@ -6125,37 +6244,37 @@
         <v>2205.4</v>
       </c>
       <c r="M59">
-        <v>265.0412155021697</v>
+        <v>259.6583920021696</v>
       </c>
       <c r="N59">
-        <v>1940.35878449783</v>
+        <v>1945.74160799783</v>
       </c>
       <c r="O59">
-        <v>679.1255745742404</v>
+        <v>681.0095627992405</v>
       </c>
       <c r="P59">
-        <v>1261.23320992359</v>
+        <v>1264.73204519859</v>
       </c>
       <c r="Q59">
-        <v>1398.03320992359</v>
+        <v>1401.532045198589</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1389851754398253</v>
+        <v>0.1389641443299942</v>
       </c>
       <c r="T59">
         <v>1.35565181705877</v>
       </c>
       <c r="U59">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V59">
         <v>0.35</v>
       </c>
       <c r="W59">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.320969988842908</v>
+        <v>8.493467062607287</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6293,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08697470338453217</v>
+        <v>0.08640019954736763</v>
       </c>
       <c r="C60">
-        <v>2731.209967215434</v>
+        <v>2744.889698232439</v>
       </c>
       <c r="D60">
-        <v>5617.915967215434</v>
+        <v>5631.595698232439</v>
       </c>
       <c r="E60">
         <v>721.1060000000002</v>
@@ -6207,37 +6326,37 @@
         <v>2205.4</v>
       </c>
       <c r="M60">
-        <v>269.6910613881726</v>
+        <v>264.2138023881726</v>
       </c>
       <c r="N60">
-        <v>1935.708938611827</v>
+        <v>1941.186197611827</v>
       </c>
       <c r="O60">
-        <v>677.4981285141395</v>
+        <v>679.4151691641395</v>
       </c>
       <c r="P60">
-        <v>1258.210810097687</v>
+        <v>1261.771028447688</v>
       </c>
       <c r="Q60">
-        <v>1395.010810097687</v>
+        <v>1398.571028447687</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1407867388685123</v>
+        <v>0.1407653011609777</v>
       </c>
       <c r="T60">
         <v>1.38186084359243</v>
       </c>
       <c r="U60">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V60">
         <v>0.35</v>
       </c>
       <c r="W60">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.177504989035274</v>
+        <v>8.347027975320959</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6375,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08682158194362655</v>
+        <v>0.08623736764652484</v>
       </c>
       <c r="C61">
-        <v>2671.953212171961</v>
+        <v>2685.886993273287</v>
       </c>
       <c r="D61">
-        <v>5621.616212171961</v>
+        <v>5635.549993273287</v>
       </c>
       <c r="E61">
         <v>784.0630000000001</v>
@@ -6289,37 +6408,37 @@
         <v>2205.4</v>
       </c>
       <c r="M61">
-        <v>274.3409072741755</v>
+        <v>268.7692127741756</v>
       </c>
       <c r="N61">
-        <v>1931.059092725824</v>
+        <v>1936.630787225824</v>
       </c>
       <c r="O61">
-        <v>675.8706824540384</v>
+        <v>677.8207755290383</v>
       </c>
       <c r="P61">
-        <v>1255.188410271786</v>
+        <v>1258.810011696786</v>
       </c>
       <c r="Q61">
-        <v>1391.988410271786</v>
+        <v>1395.610011696786</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1426761834400621</v>
+        <v>0.1426543193007896</v>
       </c>
       <c r="T61">
         <v>1.409348359225293</v>
       </c>
       <c r="U61">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V61">
         <v>0.35</v>
       </c>
       <c r="W61">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.0389032095601</v>
+        <v>8.205552924891787</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6457,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08666846050272094</v>
+        <v>0.08607453574568207</v>
       </c>
       <c r="C62">
-        <v>2612.701334679839</v>
+        <v>2626.889845331064</v>
       </c>
       <c r="D62">
-        <v>5625.321334679838</v>
+        <v>5639.509845331064</v>
       </c>
       <c r="E62">
         <v>847.02</v>
@@ -6371,37 +6490,37 @@
         <v>2205.4</v>
       </c>
       <c r="M62">
-        <v>278.9907531601785</v>
+        <v>273.3246231601785</v>
       </c>
       <c r="N62">
-        <v>1926.409246839821</v>
+        <v>1932.075376839821</v>
       </c>
       <c r="O62">
-        <v>674.2432363939374</v>
+        <v>676.2263818939373</v>
       </c>
       <c r="P62">
-        <v>1252.166010445884</v>
+        <v>1255.848994945884</v>
       </c>
       <c r="Q62">
-        <v>1388.966010445884</v>
+        <v>1392.648994945884</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1446601002401894</v>
+        <v>0.1446377883475922</v>
       </c>
       <c r="T62">
         <v>1.4382102506398</v>
       </c>
       <c r="U62">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V62">
         <v>0.35</v>
       </c>
       <c r="W62">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.904921489400765</v>
+        <v>8.068793709476925</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6539,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08651533906181533</v>
+        <v>0.08591170384483929</v>
       </c>
       <c r="C63">
-        <v>2553.454344389587</v>
+        <v>2567.898266128015</v>
       </c>
       <c r="D63">
-        <v>5629.031344389588</v>
+        <v>5643.475266128015</v>
       </c>
       <c r="E63">
         <v>909.9770000000003</v>
@@ -6453,37 +6572,37 @@
         <v>2205.4</v>
       </c>
       <c r="M63">
-        <v>283.6405990461815</v>
+        <v>277.8800335461815</v>
       </c>
       <c r="N63">
-        <v>1921.759400953818</v>
+        <v>1927.519966453818</v>
       </c>
       <c r="O63">
-        <v>672.6157903338363</v>
+        <v>674.6319882588363</v>
       </c>
       <c r="P63">
-        <v>1249.143610619982</v>
+        <v>1252.887978194982</v>
       </c>
       <c r="Q63">
-        <v>1385.943610619982</v>
+        <v>1389.687978194982</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1467457563634001</v>
+        <v>0.1467229737557693</v>
       </c>
       <c r="T63">
         <v>1.468552239049923</v>
       </c>
       <c r="U63">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V63">
         <v>0.35</v>
       </c>
       <c r="W63">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.775332612525342</v>
+        <v>7.93651840276419</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6621,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08696671762090971</v>
+        <v>0.0857488719439965</v>
       </c>
       <c r="C64">
-        <v>2479.574826199016</v>
+        <v>2508.912267419384</v>
       </c>
       <c r="D64">
-        <v>5618.108826199016</v>
+        <v>5647.446267419384</v>
       </c>
       <c r="E64">
         <v>972.9340000000002</v>
@@ -6535,45 +6654,45 @@
         <v>2205.4</v>
       </c>
       <c r="M64">
-        <v>294.1454459321845</v>
+        <v>282.4354439321845</v>
       </c>
       <c r="N64">
-        <v>1911.254554067815</v>
+        <v>1922.964556067815</v>
       </c>
       <c r="O64">
-        <v>668.9390939237353</v>
+        <v>673.0375946237353</v>
       </c>
       <c r="P64">
-        <v>1242.31546014408</v>
+        <v>1249.92696144408</v>
       </c>
       <c r="Q64">
-        <v>1379.11546014408</v>
+        <v>1386.72696144408</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1489411838615167</v>
+        <v>0.1489179057643767</v>
       </c>
       <c r="T64">
         <v>1.500491174218473</v>
       </c>
       <c r="U64">
-        <v>0.07535748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V64">
         <v>0.35</v>
       </c>
       <c r="W64">
-        <v>0.04898236734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>7.497651350714628</v>
+        <v>7.808510041429283</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6703,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08682334618000409</v>
+        <v>0.0855860400431537</v>
       </c>
       <c r="C65">
-        <v>2420.08255089024</v>
+        <v>2449.931860993518</v>
       </c>
       <c r="D65">
-        <v>5621.573550890241</v>
+        <v>5651.422860993518</v>
       </c>
       <c r="E65">
         <v>1035.891000000001</v>
@@ -6617,45 +6736,45 @@
         <v>2205.4</v>
       </c>
       <c r="M65">
-        <v>298.8897273181875</v>
+        <v>286.9908543181875</v>
       </c>
       <c r="N65">
-        <v>1906.510272681812</v>
+        <v>1918.409145681812</v>
       </c>
       <c r="O65">
-        <v>667.2785954386343</v>
+        <v>671.4432009886342</v>
       </c>
       <c r="P65">
-        <v>1239.231677243178</v>
+        <v>1246.965944693178</v>
       </c>
       <c r="Q65">
-        <v>1376.031677243178</v>
+        <v>1383.765944693178</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1512552831162882</v>
+        <v>0.1512314827464223</v>
       </c>
       <c r="T65">
         <v>1.534156538315052</v>
       </c>
       <c r="U65">
-        <v>0.07535748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V65">
         <v>0.35</v>
       </c>
       <c r="W65">
-        <v>0.04898236734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>7.378641011814395</v>
+        <v>7.684565437597071</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6785,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08667997473909847</v>
+        <v>0.08575600814231092</v>
       </c>
       <c r="C66">
-        <v>2360.59455165559</v>
+        <v>2382.82411900071</v>
       </c>
       <c r="D66">
-        <v>5625.042551655591</v>
+        <v>5647.272119000711</v>
       </c>
       <c r="E66">
         <v>1098.848</v>
@@ -6699,37 +6818,37 @@
         <v>2205.4</v>
       </c>
       <c r="M66">
-        <v>303.6340087041905</v>
+        <v>294.7696631041904</v>
       </c>
       <c r="N66">
-        <v>1901.765991295809</v>
+        <v>1910.630336895809</v>
       </c>
       <c r="O66">
-        <v>665.6180969535332</v>
+        <v>668.7206179135331</v>
       </c>
       <c r="P66">
-        <v>1236.147894342276</v>
+        <v>1241.909718982276</v>
       </c>
       <c r="Q66">
-        <v>1372.947894342276</v>
+        <v>1378.709718982276</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1536979434407693</v>
+        <v>0.1536735917830261</v>
       </c>
       <c r="T66">
         <v>1.569692200416997</v>
       </c>
       <c r="U66">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V66">
         <v>0.35</v>
       </c>
       <c r="W66">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.263349746004796</v>
+        <v>7.48177399524479</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6867,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08653660329819285</v>
+        <v>0.08559837624146814</v>
       </c>
       <c r="C67">
-        <v>2301.110836416085</v>
+        <v>2323.716396904586</v>
       </c>
       <c r="D67">
-        <v>5628.515836416086</v>
+        <v>5651.121396904587</v>
       </c>
       <c r="E67">
         <v>1161.805000000001</v>
@@ -6781,37 +6900,37 @@
         <v>2205.4</v>
       </c>
       <c r="M67">
-        <v>308.3782900901934</v>
+        <v>299.3754390901934</v>
       </c>
       <c r="N67">
-        <v>1897.021709909806</v>
+        <v>1906.024560909806</v>
       </c>
       <c r="O67">
-        <v>663.9575984684321</v>
+        <v>667.1085963184322</v>
       </c>
       <c r="P67">
-        <v>1233.064111441374</v>
+        <v>1238.915964591374</v>
       </c>
       <c r="Q67">
-        <v>1369.864111441374</v>
+        <v>1375.715964591374</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1562801843552207</v>
+        <v>0.1562552499074358</v>
       </c>
       <c r="T67">
         <v>1.607258471781911</v>
       </c>
       <c r="U67">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V67">
         <v>0.35</v>
       </c>
       <c r="W67">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.151605903758568</v>
+        <v>7.366669779933331</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6949,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08639323185728723</v>
+        <v>0.08544074434062535</v>
       </c>
       <c r="C68">
-        <v>2241.631413112323</v>
+        <v>2264.613925855851</v>
       </c>
       <c r="D68">
-        <v>5631.993413112323</v>
+        <v>5654.975925855851</v>
       </c>
       <c r="E68">
         <v>1224.762</v>
@@ -6863,37 +6982,37 @@
         <v>2205.4</v>
       </c>
       <c r="M68">
-        <v>313.1225714761964</v>
+        <v>303.9812150761963</v>
       </c>
       <c r="N68">
-        <v>1892.277428523803</v>
+        <v>1901.418784923803</v>
       </c>
       <c r="O68">
-        <v>662.2970999833311</v>
+        <v>665.4965747233312</v>
       </c>
       <c r="P68">
-        <v>1229.980328540472</v>
+        <v>1235.922210200472</v>
       </c>
       <c r="Q68">
-        <v>1366.780328540472</v>
+        <v>1372.722210200472</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1590143217940516</v>
+        <v>0.1589887702744578</v>
       </c>
       <c r="T68">
         <v>1.647034523815348</v>
       </c>
       <c r="U68">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V68">
         <v>0.35</v>
       </c>
       <c r="W68">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.043248238550105</v>
+        <v>7.255053571146464</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7031,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08624986041638164</v>
+        <v>0.08528311243978257</v>
       </c>
       <c r="C69">
-        <v>2182.156289704531</v>
+        <v>2205.51671660677</v>
       </c>
       <c r="D69">
-        <v>5635.475289704531</v>
+        <v>5658.835716606771</v>
       </c>
       <c r="E69">
         <v>1287.719000000001</v>
@@ -6945,37 +7064,37 @@
         <v>2205.4</v>
       </c>
       <c r="M69">
-        <v>317.8668528621994</v>
+        <v>308.5869910621993</v>
       </c>
       <c r="N69">
-        <v>1887.5331471378</v>
+        <v>1896.8130089378</v>
       </c>
       <c r="O69">
-        <v>660.6366014982301</v>
+        <v>663.8845531282301</v>
       </c>
       <c r="P69">
-        <v>1226.89654563957</v>
+        <v>1232.92845580957</v>
       </c>
       <c r="Q69">
-        <v>1363.69654563957</v>
+        <v>1369.72845580957</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1619141645322056</v>
+        <v>0.1618879585425115</v>
       </c>
       <c r="T69">
         <v>1.689221245668995</v>
       </c>
       <c r="U69">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V69">
         <v>0.35</v>
       </c>
       <c r="W69">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.938125130512044</v>
+        <v>7.146769189487562</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7113,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.086106488975476</v>
+        <v>0.08512548053893979</v>
       </c>
       <c r="C70">
-        <v>2122.68547417264</v>
+        <v>2146.424779938995</v>
       </c>
       <c r="D70">
-        <v>5638.961474172641</v>
+        <v>5662.700779938996</v>
       </c>
       <c r="E70">
         <v>1350.676000000001</v>
@@ -7027,37 +7146,37 @@
         <v>2205.4</v>
       </c>
       <c r="M70">
-        <v>322.6111342482024</v>
+        <v>313.1927670482024</v>
       </c>
       <c r="N70">
-        <v>1882.788865751797</v>
+        <v>1892.207232951797</v>
       </c>
       <c r="O70">
-        <v>658.976103013129</v>
+        <v>662.272531533129</v>
       </c>
       <c r="P70">
-        <v>1223.812762738668</v>
+        <v>1229.934701418668</v>
       </c>
       <c r="Q70">
-        <v>1360.612762738668</v>
+        <v>1366.734701418668</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1649952474414942</v>
+        <v>0.1649683460773185</v>
       </c>
       <c r="T70">
         <v>1.734044637638494</v>
       </c>
       <c r="U70">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V70">
         <v>0.35</v>
       </c>
       <c r="W70">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.836093878592748</v>
+        <v>7.041669642583331</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7195,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08596311753457038</v>
+        <v>0.08496784863809698</v>
       </c>
       <c r="C71">
-        <v>2063.218974516337</v>
+        <v>2087.338126663647</v>
       </c>
       <c r="D71">
-        <v>5642.451974516338</v>
+        <v>5666.571126663648</v>
       </c>
       <c r="E71">
         <v>1413.633000000001</v>
@@ -7109,37 +7228,37 @@
         <v>2205.4</v>
       </c>
       <c r="M71">
-        <v>327.3554156342054</v>
+        <v>317.7985430342054</v>
       </c>
       <c r="N71">
-        <v>1878.044584365794</v>
+        <v>1887.601456965794</v>
       </c>
       <c r="O71">
-        <v>657.315604528028</v>
+        <v>660.660509938028</v>
       </c>
       <c r="P71">
-        <v>1220.728979837766</v>
+        <v>1226.940947027766</v>
       </c>
       <c r="Q71">
-        <v>1357.528979837766</v>
+        <v>1363.740947027766</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1682751098933175</v>
+        <v>0.1682474682917905</v>
       </c>
       <c r="T71">
         <v>1.78175986134796</v>
       </c>
       <c r="U71">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V71">
         <v>0.35</v>
       </c>
       <c r="W71">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.737020054265317</v>
+        <v>6.939616459357485</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7277,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08581974609366477</v>
+        <v>0.08481021673725421</v>
       </c>
       <c r="C72">
-        <v>2003.756798755129</v>
+        <v>2028.256767621426</v>
       </c>
       <c r="D72">
-        <v>5645.94679875513</v>
+        <v>5670.446767621426</v>
       </c>
       <c r="E72">
         <v>1476.590000000001</v>
@@ -7191,37 +7310,37 @@
         <v>2205.4</v>
       </c>
       <c r="M72">
-        <v>332.0996970202083</v>
+        <v>322.4043190202083</v>
       </c>
       <c r="N72">
-        <v>1873.300302979791</v>
+        <v>1882.995680979791</v>
       </c>
       <c r="O72">
-        <v>655.6551060429269</v>
+        <v>659.0484883429269</v>
       </c>
       <c r="P72">
-        <v>1217.645196936864</v>
+        <v>1223.947192636864</v>
       </c>
       <c r="Q72">
-        <v>1354.445196936864</v>
+        <v>1360.747192636864</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1717736298419291</v>
+        <v>0.1717451986538939</v>
       </c>
       <c r="T72">
         <v>1.832656099971391</v>
       </c>
       <c r="U72">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V72">
         <v>0.35</v>
       </c>
       <c r="W72">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.640776910632955</v>
+        <v>6.840479081366666</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7359,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.08567637465275915</v>
+        <v>0.08465258483641142</v>
       </c>
       <c r="C73">
-        <v>1944.298954928403</v>
+        <v>1969.18071368271</v>
       </c>
       <c r="D73">
-        <v>5649.445954928403</v>
+        <v>5674.32771368271</v>
       </c>
       <c r="E73">
         <v>1539.547</v>
@@ -7273,37 +7392,37 @@
         <v>2205.4</v>
       </c>
       <c r="M73">
-        <v>336.8439784062112</v>
+        <v>327.0100950062112</v>
       </c>
       <c r="N73">
-        <v>1868.556021593789</v>
+        <v>1878.389904993788</v>
       </c>
       <c r="O73">
-        <v>653.9946075578259</v>
+        <v>657.4364667478259</v>
       </c>
       <c r="P73">
-        <v>1214.561414035963</v>
+        <v>1220.953438245962</v>
       </c>
       <c r="Q73">
-        <v>1351.361414035963</v>
+        <v>1357.753438245962</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.175513427028376</v>
+        <v>0.1754841517995907</v>
       </c>
       <c r="T73">
         <v>1.887062424017128</v>
       </c>
       <c r="U73">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V73">
         <v>0.35</v>
       </c>
       <c r="W73">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.547244841469112</v>
+        <v>6.74413430557277</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7441,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.08553300321185353</v>
+        <v>0.08449495293556863</v>
       </c>
       <c r="C74">
-        <v>1884.845451095488</v>
+        <v>1910.109975747656</v>
       </c>
       <c r="D74">
-        <v>5652.949451095488</v>
+        <v>5678.213975747656</v>
       </c>
       <c r="E74">
         <v>1602.504</v>
@@ -7355,37 +7474,37 @@
         <v>2205.4</v>
       </c>
       <c r="M74">
-        <v>341.5882597922143</v>
+        <v>331.6158709922142</v>
       </c>
       <c r="N74">
-        <v>1863.811740207785</v>
+        <v>1873.784129007785</v>
       </c>
       <c r="O74">
-        <v>652.3341090727248</v>
+        <v>655.8244451527248</v>
       </c>
       <c r="P74">
-        <v>1211.477631135061</v>
+        <v>1217.959683855061</v>
       </c>
       <c r="Q74">
-        <v>1348.277631135061</v>
+        <v>1354.759683855061</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1795203525852833</v>
+        <v>0.1794901730271229</v>
       </c>
       <c r="T74">
         <v>1.945354914066131</v>
       </c>
       <c r="U74">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V74">
         <v>0.35</v>
       </c>
       <c r="W74">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.456310885337595</v>
+        <v>6.650465773550924</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7523,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.08538963177094791</v>
+        <v>0.08433732103472584</v>
       </c>
       <c r="C75">
-        <v>1825.396295335718</v>
+        <v>1851.044564746304</v>
       </c>
       <c r="D75">
-        <v>5656.457295335718</v>
+        <v>5682.105564746304</v>
       </c>
       <c r="E75">
         <v>1665.461000000001</v>
@@ -7437,37 +7556,37 @@
         <v>2205.4</v>
       </c>
       <c r="M75">
-        <v>346.3325411782172</v>
+        <v>336.2216469782172</v>
       </c>
       <c r="N75">
-        <v>1859.067458821782</v>
+        <v>1869.178353021782</v>
       </c>
       <c r="O75">
-        <v>650.6736105876238</v>
+        <v>654.2124235576238</v>
       </c>
       <c r="P75">
-        <v>1208.393848234159</v>
+        <v>1214.965929464159</v>
       </c>
       <c r="Q75">
-        <v>1345.193848234159</v>
+        <v>1351.765929464159</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1838240874427023</v>
+        <v>0.1837929365678057</v>
       </c>
       <c r="T75">
         <v>2.007965366340986</v>
       </c>
       <c r="U75">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V75">
         <v>0.35</v>
       </c>
       <c r="W75">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.367868270469957</v>
+        <v>6.559363502680363</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7605,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.08524626033004229</v>
+        <v>0.08417968913388306</v>
       </c>
       <c r="C76">
-        <v>1765.951495748495</v>
+        <v>1791.984491638678</v>
       </c>
       <c r="D76">
-        <v>5659.969495748495</v>
+        <v>5686.002491638678</v>
       </c>
       <c r="E76">
         <v>1728.418</v>
@@ -7519,37 +7638,37 @@
         <v>2205.4</v>
       </c>
       <c r="M76">
-        <v>351.0768225642202</v>
+        <v>340.8274229642201</v>
       </c>
       <c r="N76">
-        <v>1854.323177435779</v>
+        <v>1864.572577035779</v>
       </c>
       <c r="O76">
-        <v>649.0131121025228</v>
+        <v>652.6004019625227</v>
       </c>
       <c r="P76">
-        <v>1205.310065333257</v>
+        <v>1211.972175073257</v>
       </c>
       <c r="Q76">
-        <v>1342.110065333257</v>
+        <v>1348.772175073257</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1884588788276151</v>
+        <v>0.1884266819193103</v>
       </c>
       <c r="T76">
         <v>2.07539200725237</v>
       </c>
       <c r="U76">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V76">
         <v>0.35</v>
       </c>
       <c r="W76">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.281815996544688</v>
+        <v>6.470723455346846</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7687,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.08510288888913668</v>
+        <v>0.08402205723304028</v>
       </c>
       <c r="C77">
-        <v>1706.511060453346</v>
+        <v>1732.92976741489</v>
       </c>
       <c r="D77">
-        <v>5663.486060453346</v>
+        <v>5689.904767414891</v>
       </c>
       <c r="E77">
         <v>1791.375</v>
@@ -7601,37 +7720,37 @@
         <v>2205.4</v>
       </c>
       <c r="M77">
-        <v>355.8211039502232</v>
+        <v>345.4331989502231</v>
       </c>
       <c r="N77">
-        <v>1849.578896049776</v>
+        <v>1859.966801049776</v>
       </c>
       <c r="O77">
-        <v>647.3526136174218</v>
+        <v>650.9883803674218</v>
       </c>
       <c r="P77">
-        <v>1202.226282432355</v>
+        <v>1208.978420682355</v>
       </c>
       <c r="Q77">
-        <v>1339.026282432355</v>
+        <v>1345.778420682355</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1934644535233209</v>
+        <v>0.1934311268989352</v>
       </c>
       <c r="T77">
         <v>2.148212779436664</v>
       </c>
       <c r="U77">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V77">
         <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.198058449924092</v>
+        <v>6.384447142608888</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7769,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.08495951744823108</v>
+        <v>0.08386442533219748</v>
       </c>
       <c r="C78">
-        <v>1647.074997589993</v>
+        <v>1673.880403095241</v>
       </c>
       <c r="D78">
-        <v>5667.006997589993</v>
+        <v>5693.812403095241</v>
       </c>
       <c r="E78">
         <v>1854.332000000001</v>
@@ -7683,37 +7802,37 @@
         <v>2205.4</v>
       </c>
       <c r="M78">
-        <v>360.5653853362262</v>
+        <v>350.0389749362262</v>
       </c>
       <c r="N78">
-        <v>1844.834614663773</v>
+        <v>1855.361025063773</v>
       </c>
       <c r="O78">
-        <v>645.6921151323206</v>
+        <v>649.3763587723207</v>
       </c>
       <c r="P78">
-        <v>1199.142499531453</v>
+        <v>1205.984666291453</v>
       </c>
       <c r="Q78">
-        <v>1335.942499531453</v>
+        <v>1342.784666291453</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1988871594436688</v>
+        <v>0.1988526089601956</v>
       </c>
       <c r="T78">
         <v>2.227101949302982</v>
       </c>
       <c r="U78">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V78">
         <v>0.35</v>
       </c>
       <c r="W78">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.116505049267196</v>
+        <v>6.300441259153507</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7851,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.08551684600732545</v>
+        <v>0.0837067934313547</v>
       </c>
       <c r="C79">
-        <v>1570.455549081369</v>
+        <v>1614.836409730327</v>
       </c>
       <c r="D79">
-        <v>5653.344549081369</v>
+        <v>5697.725409730328</v>
       </c>
       <c r="E79">
         <v>1917.289</v>
@@ -7765,45 +7884,45 @@
         <v>2205.4</v>
       </c>
       <c r="M79">
-        <v>372.0964313222291</v>
+        <v>354.6447509222291</v>
       </c>
       <c r="N79">
-        <v>1833.30356867777</v>
+        <v>1850.75524907777</v>
       </c>
       <c r="O79">
-        <v>641.6562490372196</v>
+        <v>647.7643371772197</v>
       </c>
       <c r="P79">
-        <v>1191.647319640551</v>
+        <v>1202.990911900551</v>
       </c>
       <c r="Q79">
-        <v>1328.447319640551</v>
+        <v>1339.790911900551</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2047814050092644</v>
+        <v>0.2047455242441742</v>
       </c>
       <c r="T79">
         <v>2.312851046983762</v>
       </c>
       <c r="U79">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V79">
         <v>0.35</v>
       </c>
       <c r="W79">
-        <v>0.04989236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y79">
-        <v>5.92695821393181</v>
+        <v>6.218617346696969</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7933,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.08538257456641983</v>
+        <v>0.08354916153051191</v>
       </c>
       <c r="C80">
-        <v>1510.784075161353</v>
+        <v>1555.797798401145</v>
       </c>
       <c r="D80">
-        <v>5656.630075161353</v>
+        <v>5701.643798401145</v>
       </c>
       <c r="E80">
         <v>1980.246000000001</v>
@@ -7847,45 +7966,45 @@
         <v>2205.4</v>
       </c>
       <c r="M80">
-        <v>376.9288525082321</v>
+        <v>359.2505269082321</v>
       </c>
       <c r="N80">
-        <v>1828.471147491768</v>
+        <v>1846.149473091768</v>
       </c>
       <c r="O80">
-        <v>639.9649016221186</v>
+        <v>646.1523155821186</v>
       </c>
       <c r="P80">
-        <v>1188.506245869649</v>
+        <v>1199.997157509649</v>
       </c>
       <c r="Q80">
-        <v>1325.306245869649</v>
+        <v>1336.797157509649</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2112114910808232</v>
+        <v>0.2111741590994236</v>
       </c>
       <c r="T80">
         <v>2.406395517180977</v>
       </c>
       <c r="U80">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V80">
         <v>0.35</v>
       </c>
       <c r="W80">
-        <v>0.04989236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y80">
-        <v>5.850971570163454</v>
+        <v>6.138891483277776</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8015,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.08524830312551422</v>
+        <v>0.08390502962966913</v>
       </c>
       <c r="C81">
-        <v>1451.116422327658</v>
+        <v>1484.002324675789</v>
       </c>
       <c r="D81">
-        <v>5659.919422327659</v>
+        <v>5692.80532467579</v>
       </c>
       <c r="E81">
         <v>2043.203000000001</v>
@@ -7929,37 +8048,37 @@
         <v>2205.4</v>
       </c>
       <c r="M81">
-        <v>381.7612736942351</v>
+        <v>368.8299058942351</v>
       </c>
       <c r="N81">
-        <v>1823.638726305765</v>
+        <v>1836.570094105765</v>
       </c>
       <c r="O81">
-        <v>638.2735542070176</v>
+        <v>642.7995329370176</v>
       </c>
       <c r="P81">
-        <v>1185.365172098747</v>
+        <v>1193.770561168747</v>
       </c>
       <c r="Q81">
-        <v>1322.165172098747</v>
+        <v>1330.570561168747</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2182539663020543</v>
+        <v>0.2182150448932682</v>
       </c>
       <c r="T81">
         <v>2.508848984539833</v>
       </c>
       <c r="U81">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V81">
         <v>0.35</v>
       </c>
       <c r="W81">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.776908638895561</v>
+        <v>5.979450052058457</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8097,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.0851140316846086</v>
+        <v>0.08375389772882634</v>
       </c>
       <c r="C82">
-        <v>1391.452597250082</v>
+        <v>1424.795543553599</v>
       </c>
       <c r="D82">
-        <v>5663.212597250083</v>
+        <v>5696.5555435536</v>
       </c>
       <c r="E82">
         <v>2106.160000000001</v>
@@ -8011,37 +8130,37 @@
         <v>2205.4</v>
       </c>
       <c r="M82">
-        <v>386.5936948802381</v>
+        <v>373.4986388802381</v>
       </c>
       <c r="N82">
-        <v>1818.806305119761</v>
+        <v>1831.901361119762</v>
       </c>
       <c r="O82">
-        <v>636.5822067919164</v>
+        <v>641.1654763919165</v>
       </c>
       <c r="P82">
-        <v>1182.224098327845</v>
+        <v>1190.735884727845</v>
       </c>
       <c r="Q82">
-        <v>1319.024098327845</v>
+        <v>1327.535884727845</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2260006890454085</v>
+        <v>0.2259600192664973</v>
       </c>
       <c r="T82">
         <v>2.621547798634573</v>
       </c>
       <c r="U82">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V82">
         <v>0.35</v>
       </c>
       <c r="W82">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.704697280909366</v>
+        <v>5.904706926407726</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8179,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08497976024370299</v>
+        <v>0.08360276582798357</v>
       </c>
       <c r="C83">
-        <v>1331.792606613954</v>
+        <v>1365.593706711738</v>
       </c>
       <c r="D83">
-        <v>5666.509606613955</v>
+        <v>5700.310706711739</v>
       </c>
       <c r="E83">
         <v>2169.117000000001</v>
@@ -8093,37 +8212,37 @@
         <v>2205.4</v>
       </c>
       <c r="M83">
-        <v>391.426116066241</v>
+        <v>378.167371866241</v>
       </c>
       <c r="N83">
-        <v>1813.973883933759</v>
+        <v>1827.232628133759</v>
       </c>
       <c r="O83">
-        <v>634.8908593768155</v>
+        <v>639.5314198468155</v>
       </c>
       <c r="P83">
-        <v>1179.083024556943</v>
+        <v>1187.701208286943</v>
       </c>
       <c r="Q83">
-        <v>1315.883024556943</v>
+        <v>1324.501208286943</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2345628562880632</v>
+        <v>0.2345202541000662</v>
       </c>
       <c r="T83">
         <v>2.746109645791918</v>
       </c>
       <c r="U83">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V83">
         <v>0.35</v>
       </c>
       <c r="W83">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.634268919416659</v>
+        <v>5.831809310032322</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8261,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08484548880279735</v>
+        <v>0.08345163392714076</v>
       </c>
       <c r="C84">
-        <v>1272.136457120182</v>
+        <v>1306.396823934452</v>
       </c>
       <c r="D84">
-        <v>5669.810457120183</v>
+        <v>5704.070823934453</v>
       </c>
       <c r="E84">
         <v>2232.074000000001</v>
@@ -8175,37 +8294,37 @@
         <v>2205.4</v>
       </c>
       <c r="M84">
-        <v>396.258537252244</v>
+        <v>382.836104852244</v>
       </c>
       <c r="N84">
-        <v>1809.141462747756</v>
+        <v>1822.563895147756</v>
       </c>
       <c r="O84">
-        <v>633.1995119617144</v>
+        <v>637.8973633017144</v>
       </c>
       <c r="P84">
-        <v>1175.941950786041</v>
+        <v>1184.666531846041</v>
       </c>
       <c r="Q84">
-        <v>1312.741950786041</v>
+        <v>1321.466531846041</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2440763754465683</v>
+        <v>0.244031626137365</v>
       </c>
       <c r="T84">
         <v>2.884511698188967</v>
       </c>
       <c r="U84">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V84">
         <v>0.35</v>
       </c>
       <c r="W84">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.565558322838407</v>
+        <v>5.76068968430022</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8343,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08471121736189176</v>
+        <v>0.08330050202629799</v>
       </c>
       <c r="C85">
-        <v>1212.484155485293</v>
+        <v>1247.204905031815</v>
       </c>
       <c r="D85">
-        <v>5673.115155485294</v>
+        <v>5707.835905031816</v>
       </c>
       <c r="E85">
         <v>2295.031000000001</v>
@@ -8257,37 +8376,37 @@
         <v>2205.4</v>
       </c>
       <c r="M85">
-        <v>401.0909584382471</v>
+        <v>387.504837838247</v>
       </c>
       <c r="N85">
-        <v>1804.309041561753</v>
+        <v>1817.895162161753</v>
       </c>
       <c r="O85">
-        <v>631.5081645466133</v>
+        <v>636.2633067566134</v>
       </c>
       <c r="P85">
-        <v>1172.800877015139</v>
+        <v>1181.631855405139</v>
       </c>
       <c r="Q85">
-        <v>1309.600877015139</v>
+        <v>1318.431855405139</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.254709132153133</v>
+        <v>0.2546619831202285</v>
       </c>
       <c r="T85">
         <v>3.03919634498567</v>
       </c>
       <c r="U85">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V85">
         <v>0.35</v>
       </c>
       <c r="W85">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.498503403286136</v>
+        <v>5.691283784489374</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8425,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.08457694592098614</v>
+        <v>0.0831493701254552</v>
       </c>
       <c r="C86">
-        <v>1152.835708441488</v>
+        <v>1188.01795983982</v>
       </c>
       <c r="D86">
-        <v>5676.423708441489</v>
+        <v>5711.605959839821</v>
       </c>
       <c r="E86">
         <v>2357.988000000001</v>
@@ -8339,37 +8458,37 @@
         <v>2205.4</v>
       </c>
       <c r="M86">
-        <v>405.92337962425</v>
+        <v>392.17357082425</v>
       </c>
       <c r="N86">
-        <v>1799.47662037575</v>
+        <v>1813.22642917575</v>
       </c>
       <c r="O86">
-        <v>629.8168171315124</v>
+        <v>634.6292502115124</v>
       </c>
       <c r="P86">
-        <v>1169.659803244237</v>
+        <v>1178.597178964237</v>
       </c>
       <c r="Q86">
-        <v>1306.459803244237</v>
+        <v>1315.397178964237</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.266670983448018</v>
+        <v>0.2666211347259497</v>
       </c>
       <c r="T86">
         <v>3.213216572631958</v>
       </c>
       <c r="U86">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V86">
         <v>0.35</v>
       </c>
       <c r="W86">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.433045029437492</v>
+        <v>5.623530406102596</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8507,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.08444267448008053</v>
+        <v>0.08299823822461241</v>
       </c>
       <c r="C87">
-        <v>1093.191122736678</v>
+        <v>1128.835998220467</v>
       </c>
       <c r="D87">
-        <v>5679.736122736678</v>
+        <v>5715.380998220467</v>
       </c>
       <c r="E87">
         <v>2420.945</v>
@@ -8421,37 +8540,37 @@
         <v>2205.4</v>
       </c>
       <c r="M87">
-        <v>410.7558008102529</v>
+        <v>396.8423038102529</v>
       </c>
       <c r="N87">
-        <v>1794.644199189747</v>
+        <v>1808.557696189747</v>
       </c>
       <c r="O87">
-        <v>628.1254697164113</v>
+        <v>632.9951936664113</v>
       </c>
       <c r="P87">
-        <v>1166.518729473335</v>
+        <v>1175.562502523336</v>
       </c>
       <c r="Q87">
-        <v>1303.318729473335</v>
+        <v>1312.362502523335</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2802277482488879</v>
+        <v>0.2801748398791006</v>
       </c>
       <c r="T87">
         <v>3.410439497297754</v>
       </c>
       <c r="U87">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V87">
         <v>0.35</v>
       </c>
       <c r="W87">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.369126852620581</v>
+        <v>5.557371224854331</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8589,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.0843084030391749</v>
+        <v>0.08284710632376963</v>
       </c>
       <c r="C88">
-        <v>1033.550405134534</v>
+        <v>1069.659030061839</v>
       </c>
       <c r="D88">
-        <v>5683.052405134535</v>
+        <v>5719.161030061839</v>
       </c>
       <c r="E88">
         <v>2483.902</v>
@@ -8503,37 +8622,37 @@
         <v>2205.4</v>
       </c>
       <c r="M88">
-        <v>415.5882219962559</v>
+        <v>401.5110367962559</v>
       </c>
       <c r="N88">
-        <v>1789.811778003744</v>
+        <v>1803.888963203744</v>
       </c>
       <c r="O88">
-        <v>626.4341223013103</v>
+        <v>631.3611371213103</v>
       </c>
       <c r="P88">
-        <v>1163.377655702433</v>
+        <v>1172.527826082433</v>
       </c>
       <c r="Q88">
-        <v>1300.177655702433</v>
+        <v>1309.327826082433</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2957211937355963</v>
+        <v>0.2956647886255586</v>
       </c>
       <c r="T88">
         <v>3.635837125487234</v>
       </c>
       <c r="U88">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V88">
         <v>0.35</v>
       </c>
       <c r="W88">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.306695145031969</v>
+        <v>5.49275062921649</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8671,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.08417413159826928</v>
+        <v>0.08269597442292684</v>
       </c>
       <c r="C89">
-        <v>973.9135624145356</v>
+        <v>1010.487065278206</v>
       </c>
       <c r="D89">
-        <v>5686.372562414536</v>
+        <v>5722.946065278206</v>
       </c>
       <c r="E89">
         <v>2546.859000000001</v>
@@ -8585,37 +8704,37 @@
         <v>2205.4</v>
       </c>
       <c r="M89">
-        <v>420.4206431822589</v>
+        <v>406.1797697822589</v>
       </c>
       <c r="N89">
-        <v>1784.979356817741</v>
+        <v>1799.220230217741</v>
       </c>
       <c r="O89">
-        <v>624.7427748862092</v>
+        <v>629.7270805762092</v>
       </c>
       <c r="P89">
-        <v>1160.236581931531</v>
+        <v>1169.493149641532</v>
       </c>
       <c r="Q89">
-        <v>1297.036581931531</v>
+        <v>1306.293149641531</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3135982462202598</v>
+        <v>0.3135378064099333</v>
       </c>
       <c r="T89">
         <v>3.895911311859712</v>
       </c>
       <c r="U89">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V89">
         <v>0.35</v>
       </c>
       <c r="W89">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.245698649112061</v>
+        <v>5.429615564512852</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8753,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.08403986015736367</v>
+        <v>0.08254484252208405</v>
       </c>
       <c r="C90">
-        <v>914.280601372011</v>
+        <v>951.320113810094</v>
       </c>
       <c r="D90">
-        <v>5689.696601372011</v>
+        <v>5726.736113810094</v>
       </c>
       <c r="E90">
         <v>2609.816</v>
@@ -8667,37 +8786,37 @@
         <v>2205.4</v>
       </c>
       <c r="M90">
-        <v>425.2530643682618</v>
+        <v>410.8485027682618</v>
       </c>
       <c r="N90">
-        <v>1780.146935631738</v>
+        <v>1794.551497231738</v>
       </c>
       <c r="O90">
-        <v>623.0514274711081</v>
+        <v>628.0930240311081</v>
       </c>
       <c r="P90">
-        <v>1157.09550816063</v>
+        <v>1166.45847320063</v>
       </c>
       <c r="Q90">
-        <v>1293.89550816063</v>
+        <v>1303.25847320063</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3344548074523674</v>
+        <v>0.3343896604917039</v>
       </c>
       <c r="T90">
         <v>4.199331195960936</v>
       </c>
       <c r="U90">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V90">
         <v>0.35</v>
       </c>
       <c r="W90">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.186088437190334</v>
+        <v>5.367915387643388</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8835,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.08390558871645806</v>
+        <v>0.08239371062124126</v>
       </c>
       <c r="C91">
-        <v>854.651528818189</v>
+        <v>892.1581856243774</v>
       </c>
       <c r="D91">
-        <v>5693.02452881819</v>
+        <v>5730.531185624378</v>
       </c>
       <c r="E91">
         <v>2672.773000000001</v>
@@ -8749,37 +8868,37 @@
         <v>2205.4</v>
       </c>
       <c r="M91">
-        <v>430.0854855542648</v>
+        <v>415.5172357542648</v>
       </c>
       <c r="N91">
-        <v>1775.314514445735</v>
+        <v>1789.882764245735</v>
       </c>
       <c r="O91">
-        <v>621.3600800560072</v>
+        <v>626.4589674860072</v>
       </c>
       <c r="P91">
-        <v>1153.954434389728</v>
+        <v>1163.423796759728</v>
       </c>
       <c r="Q91">
-        <v>1290.754434389728</v>
+        <v>1300.223796759728</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3591034707266762</v>
+        <v>0.35903276077016</v>
       </c>
       <c r="T91">
         <v>4.557918331716928</v>
       </c>
       <c r="U91">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V91">
         <v>0.35</v>
       </c>
       <c r="W91">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.127817780592689</v>
+        <v>5.307601731602452</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8917,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.08377131727555243</v>
+        <v>0.08224257872039847</v>
       </c>
       <c r="C92">
-        <v>795.0263515802444</v>
+        <v>833.0012907143746</v>
       </c>
       <c r="D92">
-        <v>5696.356351580245</v>
+        <v>5734.331290714375</v>
       </c>
       <c r="E92">
         <v>2735.730000000001</v>
@@ -8831,37 +8950,37 @@
         <v>2205.4</v>
       </c>
       <c r="M92">
-        <v>434.9179067402678</v>
+        <v>420.1859687402678</v>
       </c>
       <c r="N92">
-        <v>1770.482093259732</v>
+        <v>1785.214031259732</v>
       </c>
       <c r="O92">
-        <v>619.6687326409061</v>
+        <v>624.8249109409061</v>
       </c>
       <c r="P92">
-        <v>1150.813360618826</v>
+        <v>1160.389120318826</v>
       </c>
       <c r="Q92">
-        <v>1287.613360618826</v>
+        <v>1297.189120318826</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3886818666558468</v>
+        <v>0.3886044811043073</v>
       </c>
       <c r="T92">
         <v>4.988222894624118</v>
       </c>
       <c r="U92">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V92">
         <v>0.35</v>
       </c>
       <c r="W92">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.070842027474993</v>
+        <v>5.24862837902909</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8999,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.08363704583464682</v>
+        <v>0.08209144681955569</v>
       </c>
       <c r="C93">
-        <v>735.4050765013417</v>
+        <v>773.849439099924</v>
       </c>
       <c r="D93">
-        <v>5699.692076501342</v>
+        <v>5738.136439099924</v>
       </c>
       <c r="E93">
         <v>2798.687</v>
@@ -8913,37 +9032,37 @@
         <v>2205.4</v>
       </c>
       <c r="M93">
-        <v>439.7503279262708</v>
+        <v>424.8547017262707</v>
       </c>
       <c r="N93">
-        <v>1765.649672073729</v>
+        <v>1780.545298273729</v>
       </c>
       <c r="O93">
-        <v>617.9773852258051</v>
+        <v>623.190854395805</v>
       </c>
       <c r="P93">
-        <v>1147.672286847924</v>
+        <v>1157.354443877924</v>
       </c>
       <c r="Q93">
-        <v>1284.472286847924</v>
+        <v>1294.154443877924</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4248332394581665</v>
+        <v>0.4247476948460429</v>
       </c>
       <c r="T93">
         <v>5.514150693732907</v>
       </c>
       <c r="U93">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V93">
         <v>0.35</v>
       </c>
       <c r="W93">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.015118488711532</v>
+        <v>5.190951144094705</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9081,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.08350277439374121</v>
+        <v>0.08194031491871291</v>
       </c>
       <c r="C94">
-        <v>675.7877104406816</v>
+        <v>714.7026408274796</v>
       </c>
       <c r="D94">
-        <v>5703.031710440682</v>
+        <v>5741.94664082748</v>
       </c>
       <c r="E94">
         <v>2861.644000000001</v>
@@ -8995,37 +9114,37 @@
         <v>2205.4</v>
       </c>
       <c r="M94">
-        <v>444.5827491122738</v>
+        <v>429.5234347122737</v>
       </c>
       <c r="N94">
-        <v>1760.817250887726</v>
+        <v>1775.876565287726</v>
       </c>
       <c r="O94">
-        <v>616.286037810704</v>
+        <v>621.556797850704</v>
       </c>
       <c r="P94">
-        <v>1144.531213077022</v>
+        <v>1154.319767437022</v>
       </c>
       <c r="Q94">
-        <v>1281.331213077022</v>
+        <v>1291.119767437022</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4700224554610661</v>
+        <v>0.4699267120232125</v>
       </c>
       <c r="T94">
         <v>6.171560442618893</v>
       </c>
       <c r="U94">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V94">
         <v>0.35</v>
       </c>
       <c r="W94">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.960606331225536</v>
+        <v>5.134527762093676</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9163,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.08336850295283559</v>
+        <v>0.08178918301787011</v>
       </c>
       <c r="C95">
-        <v>616.1742602735567</v>
+        <v>655.5609059701965</v>
       </c>
       <c r="D95">
-        <v>5706.375260273558</v>
+        <v>5745.761905970197</v>
       </c>
       <c r="E95">
         <v>2924.601000000001</v>
@@ -9077,37 +9196,37 @@
         <v>2205.4</v>
       </c>
       <c r="M95">
-        <v>449.4151702982768</v>
+        <v>434.1921676982768</v>
       </c>
       <c r="N95">
-        <v>1755.984829701723</v>
+        <v>1771.207832301723</v>
       </c>
       <c r="O95">
-        <v>614.5946903956029</v>
+        <v>619.9227413056029</v>
       </c>
       <c r="P95">
-        <v>1141.39013930612</v>
+        <v>1151.28509099612</v>
       </c>
       <c r="Q95">
-        <v>1278.19013930612</v>
+        <v>1288.08509099612</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5281228760362227</v>
+        <v>0.5280140198224303</v>
       </c>
       <c r="T95">
         <v>7.016801548329445</v>
       </c>
       <c r="U95">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V95">
         <v>0.35</v>
       </c>
       <c r="W95">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.907266478201606</v>
+        <v>5.079317786157183</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9245,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08323423151192996</v>
+        <v>0.08163805111702734</v>
       </c>
       <c r="C96">
-        <v>556.5647328913865</v>
+        <v>596.4242446280196</v>
       </c>
       <c r="D96">
-        <v>5709.722732891388</v>
+        <v>5749.582244628021</v>
       </c>
       <c r="E96">
         <v>2987.558000000001</v>
@@ -9159,37 +9278,37 @@
         <v>2205.4</v>
       </c>
       <c r="M96">
-        <v>454.2475914842798</v>
+        <v>438.8609006842797</v>
       </c>
       <c r="N96">
-        <v>1751.15240851572</v>
+        <v>1766.53909931572</v>
       </c>
       <c r="O96">
-        <v>612.9033429805019</v>
+        <v>618.2886847605018</v>
       </c>
       <c r="P96">
-        <v>1138.249065535218</v>
+        <v>1148.250414555218</v>
       </c>
       <c r="Q96">
-        <v>1275.049065535218</v>
+        <v>1285.050414555218</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6055901034697648</v>
+        <v>0.605463763554721</v>
       </c>
       <c r="T96">
         <v>8.143789689276851</v>
       </c>
       <c r="U96">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V96">
         <v>0.35</v>
       </c>
       <c r="W96">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.855061515667545</v>
+        <v>5.025282490559767</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9327,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08309996007102435</v>
+        <v>0.08148691921618455</v>
       </c>
       <c r="C97">
-        <v>496.9591352017769</v>
+        <v>537.2926669277758</v>
       </c>
       <c r="D97">
-        <v>5713.074135201778</v>
+        <v>5753.407666927777</v>
       </c>
       <c r="E97">
         <v>3050.515000000001</v>
@@ -9241,37 +9360,37 @@
         <v>2205.4</v>
       </c>
       <c r="M97">
-        <v>459.0800126702827</v>
+        <v>443.5296336702827</v>
       </c>
       <c r="N97">
-        <v>1746.319987329717</v>
+        <v>1761.870366329717</v>
       </c>
       <c r="O97">
-        <v>611.2119955654009</v>
+        <v>616.6546282154009</v>
       </c>
       <c r="P97">
-        <v>1135.107991764316</v>
+        <v>1145.215738114316</v>
       </c>
       <c r="Q97">
-        <v>1271.907991764316</v>
+        <v>1282.015738114316</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7140442218767241</v>
+        <v>0.713893404779928</v>
       </c>
       <c r="T97">
         <v>9.72157308660322</v>
       </c>
       <c r="U97">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V97">
         <v>0.35</v>
       </c>
       <c r="W97">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.803955604976309</v>
+        <v>4.972384780132822</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9409,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.08296568863011874</v>
+        <v>0.08133578731534177</v>
       </c>
       <c r="C98">
-        <v>437.3574741285538</v>
+        <v>478.1661830232579</v>
       </c>
       <c r="D98">
-        <v>5716.429474128554</v>
+        <v>5757.238183023258</v>
       </c>
       <c r="E98">
         <v>3113.472</v>
@@ -9323,37 +9442,37 @@
         <v>2205.4</v>
       </c>
       <c r="M98">
-        <v>463.9124338562856</v>
+        <v>448.1983666562856</v>
       </c>
       <c r="N98">
-        <v>1741.487566143714</v>
+        <v>1757.201633343714</v>
       </c>
       <c r="O98">
-        <v>609.5206481502998</v>
+        <v>615.0205716702999</v>
       </c>
       <c r="P98">
-        <v>1131.966917993414</v>
+        <v>1142.181061673414</v>
       </c>
       <c r="Q98">
-        <v>1268.766917993414</v>
+        <v>1278.981061673414</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8767253994871608</v>
+        <v>0.8765378666177365</v>
       </c>
       <c r="T98">
         <v>12.08824818259274</v>
       </c>
       <c r="U98">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V98">
         <v>0.35</v>
       </c>
       <c r="W98">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.753914400757806</v>
+        <v>4.920589105339772</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9491,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.08283141718921314</v>
+        <v>0.08118465541449899</v>
       </c>
       <c r="C99">
-        <v>377.7597566118211</v>
+        <v>419.0448030953157</v>
       </c>
       <c r="D99">
-        <v>5719.788756611822</v>
+        <v>5761.073803095316</v>
       </c>
       <c r="E99">
         <v>3176.429000000001</v>
@@ -9405,37 +9524,37 @@
         <v>2205.4</v>
       </c>
       <c r="M99">
-        <v>468.7448550422886</v>
+        <v>452.8670996422886</v>
       </c>
       <c r="N99">
-        <v>1736.655144957711</v>
+        <v>1752.532900357711</v>
       </c>
       <c r="O99">
-        <v>607.8293007351988</v>
+        <v>613.3865151251988</v>
       </c>
       <c r="P99">
-        <v>1128.825844222512</v>
+        <v>1139.146385232512</v>
       </c>
       <c r="Q99">
-        <v>1265.625844222512</v>
+        <v>1275.946385232512</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.147860695504558</v>
+        <v>1.147611969680753</v>
       </c>
       <c r="T99">
         <v>16.03270667590865</v>
       </c>
       <c r="U99">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V99">
         <v>0.35</v>
       </c>
       <c r="W99">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.70490497394587</v>
+        <v>4.86986138260431</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9573,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.0826971457483075</v>
+        <v>0.0810335235136562</v>
       </c>
       <c r="C100">
-        <v>318.16598960801</v>
+        <v>359.9285373519569</v>
       </c>
       <c r="D100">
-        <v>5723.151989608011</v>
+        <v>5764.914537351958</v>
       </c>
       <c r="E100">
         <v>3239.386000000001</v>
@@ -9487,37 +9606,37 @@
         <v>2205.4</v>
       </c>
       <c r="M100">
-        <v>473.5772762282916</v>
+        <v>457.5358326282916</v>
       </c>
       <c r="N100">
-        <v>1731.822723771708</v>
+        <v>1747.864167371708</v>
       </c>
       <c r="O100">
-        <v>606.1379533200978</v>
+        <v>611.7524585800977</v>
       </c>
       <c r="P100">
-        <v>1125.68477045161</v>
+        <v>1136.11170879161</v>
       </c>
       <c r="Q100">
-        <v>1262.48477045161</v>
+        <v>1272.91170879161</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.690131287539351</v>
+        <v>1.689760175806786</v>
       </c>
       <c r="T100">
         <v>23.92162366254045</v>
       </c>
       <c r="U100">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V100">
         <v>0.35</v>
       </c>
       <c r="W100">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9644,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.656895739517851</v>
+        <v>4.820168919516512</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9655,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.08256287430740189</v>
+        <v>0.08088239161281341</v>
       </c>
       <c r="C101">
-        <v>258.5761800899172</v>
+        <v>300.8173960284203</v>
       </c>
       <c r="D101">
-        <v>5726.519180089917</v>
+        <v>5768.76039602842</v>
       </c>
       <c r="E101">
         <v>3302.343</v>
@@ -9569,37 +9688,37 @@
         <v>2205.4</v>
       </c>
       <c r="M101">
-        <v>478.4096974142946</v>
+        <v>462.2045656142946</v>
       </c>
       <c r="N101">
-        <v>1726.990302585705</v>
+        <v>1743.195434385705</v>
       </c>
       <c r="O101">
-        <v>604.4466059049968</v>
+        <v>610.1184020349967</v>
       </c>
       <c r="P101">
-        <v>1122.543696680708</v>
+        <v>1133.077032350708</v>
       </c>
       <c r="Q101">
-        <v>1259.343696680708</v>
+        <v>1269.877032350708</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.316943063643732</v>
+        <v>3.316204794184884</v>
       </c>
       <c r="T101">
         <v>47.58837462243589</v>
       </c>
       <c r="U101">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V101">
         <v>0.35</v>
       </c>
       <c r="W101">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9726,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>4.609856388613631</v>
+        <v>4.7714803445719</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/colombia/colombia_diversified.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_diversified.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09584444979624923</v>
+        <v>0.09566081789540645</v>
       </c>
       <c r="C2">
-        <v>6176.170004431605</v>
+        <v>6117.330704750482</v>
       </c>
       <c r="D2">
-        <v>5411.370004431605</v>
+        <v>5415.487704750482</v>
       </c>
       <c r="E2">
-        <v>-2930.4</v>
+        <v>-2867.443</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>62.95700000000001</v>
       </c>
       <c r="G2">
         <v>764.8</v>
@@ -1570,28 +1570,28 @@
         <v>2205.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.353947986002976</v>
       </c>
       <c r="N2">
-        <v>2205.4</v>
+        <v>2201.046052013997</v>
       </c>
       <c r="O2">
-        <v>771.8899999999999</v>
+        <v>770.3661182048988</v>
       </c>
       <c r="P2">
-        <v>1433.51</v>
+        <v>1430.679933809098</v>
       </c>
       <c r="Q2">
-        <v>1570.31</v>
+        <v>1567.479933809098</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09584444979624923</v>
+        <v>0.09617302446662865</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7329888836530167</v>
       </c>
       <c r="U2">
         <v>0.06915748822216712</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>506.5287888348449</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09566081789540645</v>
+        <v>0.09547718599456365</v>
       </c>
       <c r="C3">
-        <v>6117.330704750482</v>
+        <v>6058.497676445269</v>
       </c>
       <c r="D3">
-        <v>5415.487704750482</v>
+        <v>5419.611676445268</v>
       </c>
       <c r="E3">
-        <v>-2867.443</v>
+        <v>-2804.486</v>
       </c>
       <c r="F3">
-        <v>62.95700000000001</v>
+        <v>125.914</v>
       </c>
       <c r="G3">
         <v>764.8</v>
@@ -1652,28 +1652,28 @@
         <v>2205.4</v>
       </c>
       <c r="M3">
-        <v>4.353947986002976</v>
+        <v>8.707895972005952</v>
       </c>
       <c r="N3">
-        <v>2201.046052013997</v>
+        <v>2196.692104027994</v>
       </c>
       <c r="O3">
-        <v>770.3661182048988</v>
+        <v>768.8422364097977</v>
       </c>
       <c r="P3">
-        <v>1430.679933809098</v>
+        <v>1427.849867618196</v>
       </c>
       <c r="Q3">
-        <v>1567.479933809098</v>
+        <v>1564.649867618196</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09617302446662865</v>
+        <v>0.096508304742526</v>
       </c>
       <c r="T3">
-        <v>0.7329888836530167</v>
+        <v>0.7378676201939146</v>
       </c>
       <c r="U3">
         <v>0.06915748822216712</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>506.5287888348449</v>
+        <v>253.2643944174224</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09547718599456365</v>
+        <v>0.09529355409372087</v>
       </c>
       <c r="C4">
-        <v>6058.497676445269</v>
+        <v>5999.67093385411</v>
       </c>
       <c r="D4">
-        <v>5419.611676445268</v>
+        <v>5423.741933854109</v>
       </c>
       <c r="E4">
-        <v>-2804.486</v>
+        <v>-2741.529</v>
       </c>
       <c r="F4">
-        <v>125.914</v>
+        <v>188.871</v>
       </c>
       <c r="G4">
         <v>764.8</v>
@@ -1734,28 +1734,28 @@
         <v>2205.4</v>
       </c>
       <c r="M4">
-        <v>8.707895972005952</v>
+        <v>13.06184395800893</v>
       </c>
       <c r="N4">
-        <v>2196.692104027994</v>
+        <v>2192.338156041991</v>
       </c>
       <c r="O4">
-        <v>768.8422364097977</v>
+        <v>767.3183546146967</v>
       </c>
       <c r="P4">
-        <v>1427.849867618196</v>
+        <v>1425.019801427294</v>
       </c>
       <c r="Q4">
-        <v>1564.649867618196</v>
+        <v>1561.819801427294</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.096508304742526</v>
+        <v>0.09685049801380269</v>
       </c>
       <c r="T4">
-        <v>0.7378676201939146</v>
+        <v>0.7428469492408102</v>
       </c>
       <c r="U4">
         <v>0.06915748822216712</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>253.2643944174224</v>
+        <v>168.842929611615</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09529355409372087</v>
+        <v>0.09510992219287807</v>
       </c>
       <c r="C5">
-        <v>5999.67093385411</v>
+        <v>5940.850491358897</v>
       </c>
       <c r="D5">
-        <v>5423.741933854109</v>
+        <v>5427.878491358897</v>
       </c>
       <c r="E5">
-        <v>-2741.529</v>
+        <v>-2678.572</v>
       </c>
       <c r="F5">
-        <v>188.871</v>
+        <v>251.828</v>
       </c>
       <c r="G5">
         <v>764.8</v>
@@ -1816,28 +1816,28 @@
         <v>2205.4</v>
       </c>
       <c r="M5">
-        <v>13.06184395800893</v>
+        <v>17.4157919440119</v>
       </c>
       <c r="N5">
-        <v>2192.338156041991</v>
+        <v>2187.984208055988</v>
       </c>
       <c r="O5">
-        <v>767.3183546146967</v>
+        <v>765.7944728195957</v>
       </c>
       <c r="P5">
-        <v>1425.019801427294</v>
+        <v>1422.189735236392</v>
       </c>
       <c r="Q5">
-        <v>1561.819801427294</v>
+        <v>1558.989735236392</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09685049801380269</v>
+        <v>0.09719982031156431</v>
       </c>
       <c r="T5">
-        <v>0.7428469492408102</v>
+        <v>0.7479300143095163</v>
       </c>
       <c r="U5">
         <v>0.06915748822216712</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>168.842929611615</v>
+        <v>126.6321972087112</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09510992219287807</v>
+        <v>0.0949262902920353</v>
       </c>
       <c r="C6">
-        <v>5940.850491358897</v>
+        <v>5882.036363385425</v>
       </c>
       <c r="D6">
-        <v>5427.878491358897</v>
+        <v>5432.021363385425</v>
       </c>
       <c r="E6">
-        <v>-2678.572</v>
+        <v>-2615.615</v>
       </c>
       <c r="F6">
-        <v>251.828</v>
+        <v>314.7850000000001</v>
       </c>
       <c r="G6">
         <v>764.8</v>
@@ -1898,28 +1898,28 @@
         <v>2205.4</v>
       </c>
       <c r="M6">
-        <v>17.4157919440119</v>
+        <v>21.76973993001488</v>
       </c>
       <c r="N6">
-        <v>2187.984208055988</v>
+        <v>2183.630260069985</v>
       </c>
       <c r="O6">
-        <v>765.7944728195957</v>
+        <v>764.2705910244946</v>
       </c>
       <c r="P6">
-        <v>1422.189735236392</v>
+        <v>1419.35966904549</v>
       </c>
       <c r="Q6">
-        <v>1558.989735236392</v>
+        <v>1556.15966904549</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09719982031156431</v>
+        <v>0.09755649676296302</v>
       </c>
       <c r="T6">
-        <v>0.7479300143095163</v>
+        <v>0.7531200912744057</v>
       </c>
       <c r="U6">
         <v>0.06915748822216712</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>126.6321972087112</v>
+        <v>101.305757766969</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0949262902920353</v>
+        <v>0.0947426583911925</v>
       </c>
       <c r="C7">
-        <v>5882.036363385425</v>
+        <v>5823.228564403568</v>
       </c>
       <c r="D7">
-        <v>5432.021363385425</v>
+        <v>5436.170564403568</v>
       </c>
       <c r="E7">
-        <v>-2615.615</v>
+        <v>-2552.658</v>
       </c>
       <c r="F7">
-        <v>314.7850000000001</v>
+        <v>377.7420000000001</v>
       </c>
       <c r="G7">
         <v>764.8</v>
@@ -1980,28 +1980,28 @@
         <v>2205.4</v>
       </c>
       <c r="M7">
-        <v>21.76973993001488</v>
+        <v>26.12368791601786</v>
       </c>
       <c r="N7">
-        <v>2183.630260069985</v>
+        <v>2179.276312083982</v>
       </c>
       <c r="O7">
-        <v>764.2705910244946</v>
+        <v>762.7467092293936</v>
       </c>
       <c r="P7">
-        <v>1419.35966904549</v>
+        <v>1416.529602854588</v>
       </c>
       <c r="Q7">
-        <v>1556.15966904549</v>
+        <v>1553.329602854588</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09755649676296302</v>
+        <v>0.09792076207502978</v>
       </c>
       <c r="T7">
-        <v>0.7531200912744057</v>
+        <v>0.7584205954087608</v>
       </c>
       <c r="U7">
         <v>0.06915748822216712</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>101.305757766969</v>
+        <v>84.42146480580747</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0947426583911925</v>
+        <v>0.09455902649034971</v>
       </c>
       <c r="C8">
-        <v>5823.228564403568</v>
+        <v>5764.427108927444</v>
       </c>
       <c r="D8">
-        <v>5436.170564403568</v>
+        <v>5440.326108927444</v>
       </c>
       <c r="E8">
-        <v>-2552.658</v>
+        <v>-2489.701</v>
       </c>
       <c r="F8">
-        <v>377.742</v>
+        <v>440.699</v>
       </c>
       <c r="G8">
         <v>764.8</v>
@@ -2062,28 +2062,28 @@
         <v>2205.4</v>
       </c>
       <c r="M8">
-        <v>26.12368791601785</v>
+        <v>30.47763590202083</v>
       </c>
       <c r="N8">
-        <v>2179.276312083982</v>
+        <v>2174.922364097979</v>
       </c>
       <c r="O8">
-        <v>762.7467092293936</v>
+        <v>761.2228274342926</v>
       </c>
       <c r="P8">
-        <v>1416.529602854588</v>
+        <v>1413.699536663686</v>
       </c>
       <c r="Q8">
-        <v>1553.329602854588</v>
+        <v>1550.499536663686</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09792076207502978</v>
+        <v>0.09829286104972162</v>
       </c>
       <c r="T8">
-        <v>0.7584205954087608</v>
+        <v>0.7638350888793385</v>
       </c>
       <c r="U8">
         <v>0.06915748822216712</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>84.42146480580749</v>
+        <v>72.361255547835</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09455902649034971</v>
+        <v>0.09437539458950692</v>
       </c>
       <c r="C9">
-        <v>5764.427108927444</v>
+        <v>5705.632011515584</v>
       </c>
       <c r="D9">
-        <v>5440.326108927444</v>
+        <v>5444.488011515584</v>
       </c>
       <c r="E9">
-        <v>-2489.701</v>
+        <v>-2426.744</v>
       </c>
       <c r="F9">
-        <v>440.6990000000001</v>
+        <v>503.6560000000001</v>
       </c>
       <c r="G9">
         <v>764.8</v>
@@ -2144,28 +2144,28 @@
         <v>2205.4</v>
       </c>
       <c r="M9">
-        <v>30.47763590202083</v>
+        <v>34.83158388802381</v>
       </c>
       <c r="N9">
-        <v>2174.922364097979</v>
+        <v>2170.568416111976</v>
       </c>
       <c r="O9">
-        <v>761.2228274342926</v>
+        <v>759.6989456391915</v>
       </c>
       <c r="P9">
-        <v>1413.699536663686</v>
+        <v>1410.869470472784</v>
       </c>
       <c r="Q9">
-        <v>1550.499536663686</v>
+        <v>1547.669470472784</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09829286104972162</v>
+        <v>0.09867304913255895</v>
       </c>
       <c r="T9">
-        <v>0.7638350888793385</v>
+        <v>0.7693672887297114</v>
       </c>
       <c r="U9">
         <v>0.06915748822216712</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>72.36125554783499</v>
+        <v>63.31609860435561</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09437539458950692</v>
+        <v>0.09419176268866417</v>
       </c>
       <c r="C10">
-        <v>5705.632011515584</v>
+        <v>5646.843286771103</v>
       </c>
       <c r="D10">
-        <v>5444.488011515584</v>
+        <v>5448.656286771103</v>
       </c>
       <c r="E10">
-        <v>-2426.744</v>
+        <v>-2363.787</v>
       </c>
       <c r="F10">
-        <v>503.6560000000001</v>
+        <v>566.6130000000001</v>
       </c>
       <c r="G10">
         <v>764.8</v>
@@ -2226,28 +2226,28 @@
         <v>2205.4</v>
       </c>
       <c r="M10">
-        <v>34.83158388802381</v>
+        <v>39.18553187402679</v>
       </c>
       <c r="N10">
-        <v>2170.568416111976</v>
+        <v>2166.214468125973</v>
       </c>
       <c r="O10">
-        <v>759.6989456391915</v>
+        <v>758.1750638440905</v>
       </c>
       <c r="P10">
-        <v>1410.869470472784</v>
+        <v>1408.039404281883</v>
       </c>
       <c r="Q10">
-        <v>1547.669470472784</v>
+        <v>1544.839404281882</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09867304913255895</v>
+        <v>0.09906159299743668</v>
       </c>
       <c r="T10">
-        <v>0.7693672887297114</v>
+        <v>0.7750210753899828</v>
       </c>
       <c r="U10">
         <v>0.06915748822216712</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>63.31609860435561</v>
+        <v>56.28097653720499</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09419176268866417</v>
+        <v>0.09400813078782139</v>
       </c>
       <c r="C11">
-        <v>5646.843286771103</v>
+        <v>5588.060949341871</v>
       </c>
       <c r="D11">
-        <v>5448.656286771103</v>
+        <v>5452.830949341871</v>
       </c>
       <c r="E11">
-        <v>-2363.787</v>
+        <v>-2300.83</v>
       </c>
       <c r="F11">
-        <v>566.6130000000001</v>
+        <v>629.5700000000001</v>
       </c>
       <c r="G11">
         <v>764.8</v>
@@ -2308,28 +2308,28 @@
         <v>2205.4</v>
       </c>
       <c r="M11">
-        <v>39.18553187402679</v>
+        <v>43.53947986002976</v>
       </c>
       <c r="N11">
-        <v>2166.214468125973</v>
+        <v>2161.86052013997</v>
       </c>
       <c r="O11">
-        <v>758.1750638440905</v>
+        <v>756.6511820489894</v>
       </c>
       <c r="P11">
-        <v>1408.039404281883</v>
+        <v>1405.209338090981</v>
       </c>
       <c r="Q11">
-        <v>1544.839404281882</v>
+        <v>1542.00933809098</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09906159299743668</v>
+        <v>0.09945877117042279</v>
       </c>
       <c r="T11">
-        <v>0.7750210753899828</v>
+        <v>0.7808005017538155</v>
       </c>
       <c r="U11">
         <v>0.06915748822216712</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>56.28097653720499</v>
+        <v>50.6528788834845</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09400813078782139</v>
+        <v>0.09382449888697861</v>
       </c>
       <c r="C12">
-        <v>5588.060949341871</v>
+        <v>5529.285013920684</v>
       </c>
       <c r="D12">
-        <v>5452.830949341871</v>
+        <v>5457.012013920684</v>
       </c>
       <c r="E12">
-        <v>-2300.83</v>
+        <v>-2237.873</v>
       </c>
       <c r="F12">
-        <v>629.5700000000002</v>
+        <v>692.527</v>
       </c>
       <c r="G12">
         <v>764.8</v>
@@ -2390,28 +2390,28 @@
         <v>2205.4</v>
       </c>
       <c r="M12">
-        <v>43.53947986002976</v>
+        <v>47.89342784603274</v>
       </c>
       <c r="N12">
-        <v>2161.86052013997</v>
+        <v>2157.506572153967</v>
       </c>
       <c r="O12">
-        <v>756.6511820489894</v>
+        <v>755.1273002538883</v>
       </c>
       <c r="P12">
-        <v>1405.209338090981</v>
+        <v>1402.379271900078</v>
       </c>
       <c r="Q12">
-        <v>1542.00933809098</v>
+        <v>1539.179271900078</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09945877117042279</v>
+        <v>0.09986487469561084</v>
       </c>
       <c r="T12">
-        <v>0.7808005017538155</v>
+        <v>0.7867098028673976</v>
       </c>
       <c r="U12">
         <v>0.06915748822216712</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>50.65287888348449</v>
+        <v>46.04807171225863</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09382449888697861</v>
+        <v>0.0936408669861358</v>
       </c>
       <c r="C13">
-        <v>5529.285013920684</v>
+        <v>5470.515495245437</v>
       </c>
       <c r="D13">
-        <v>5457.012013920684</v>
+        <v>5461.199495245437</v>
       </c>
       <c r="E13">
-        <v>-2237.873</v>
+        <v>-2174.916</v>
       </c>
       <c r="F13">
-        <v>692.527</v>
+        <v>755.484</v>
       </c>
       <c r="G13">
         <v>764.8</v>
@@ -2472,28 +2472,28 @@
         <v>2205.4</v>
       </c>
       <c r="M13">
-        <v>47.89342784603274</v>
+        <v>52.24737583203571</v>
       </c>
       <c r="N13">
-        <v>2157.506572153967</v>
+        <v>2153.152624167964</v>
       </c>
       <c r="O13">
-        <v>755.1273002538883</v>
+        <v>753.6034184587874</v>
       </c>
       <c r="P13">
-        <v>1402.379271900078</v>
+        <v>1399.549205709176</v>
       </c>
       <c r="Q13">
-        <v>1539.179271900078</v>
+        <v>1536.349205709176</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09986487469561084</v>
+        <v>0.1002802078463713</v>
       </c>
       <c r="T13">
-        <v>0.7867098028673976</v>
+        <v>0.7927534062790152</v>
       </c>
       <c r="U13">
         <v>0.06915748822216712</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>46.04807171225863</v>
+        <v>42.21073240290374</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0936408669861358</v>
+        <v>0.09345723508529302</v>
       </c>
       <c r="C14">
-        <v>5470.515495245437</v>
+        <v>5411.752408099297</v>
       </c>
       <c r="D14">
-        <v>5461.199495245437</v>
+        <v>5465.393408099297</v>
       </c>
       <c r="E14">
-        <v>-2174.916</v>
+        <v>-2111.959</v>
       </c>
       <c r="F14">
-        <v>755.484</v>
+        <v>818.4410000000001</v>
       </c>
       <c r="G14">
         <v>764.8</v>
@@ -2554,28 +2554,28 @@
         <v>2205.4</v>
       </c>
       <c r="M14">
-        <v>52.24737583203571</v>
+        <v>56.60132381803869</v>
       </c>
       <c r="N14">
-        <v>2153.152624167964</v>
+        <v>2148.798676181961</v>
       </c>
       <c r="O14">
-        <v>753.6034184587874</v>
+        <v>752.0795366636863</v>
       </c>
       <c r="P14">
-        <v>1399.549205709176</v>
+        <v>1396.719139518275</v>
       </c>
       <c r="Q14">
-        <v>1536.349205709176</v>
+        <v>1533.519139518275</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1002802078463713</v>
+        <v>0.100705088885655</v>
       </c>
       <c r="T14">
-        <v>0.7927534062790152</v>
+        <v>0.7989359431023945</v>
       </c>
       <c r="U14">
         <v>0.06915748822216712</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>42.21073240290374</v>
+        <v>38.96375298729576</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09345723508529302</v>
+        <v>0.09327360318445023</v>
       </c>
       <c r="C15">
-        <v>5411.752408099297</v>
+        <v>5352.995767310873</v>
       </c>
       <c r="D15">
-        <v>5465.393408099297</v>
+        <v>5469.593767310873</v>
       </c>
       <c r="E15">
-        <v>-2111.959</v>
+        <v>-2049.002</v>
       </c>
       <c r="F15">
-        <v>818.4410000000001</v>
+        <v>881.3980000000001</v>
       </c>
       <c r="G15">
         <v>764.8</v>
@@ -2636,28 +2636,28 @@
         <v>2205.4</v>
       </c>
       <c r="M15">
-        <v>56.60132381803869</v>
+        <v>60.95527180404167</v>
       </c>
       <c r="N15">
-        <v>2148.798676181961</v>
+        <v>2144.444728195958</v>
       </c>
       <c r="O15">
-        <v>752.0795366636863</v>
+        <v>750.5556548685852</v>
       </c>
       <c r="P15">
-        <v>1396.719139518275</v>
+        <v>1393.889073327373</v>
       </c>
       <c r="Q15">
-        <v>1533.519139518275</v>
+        <v>1530.689073327373</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.100705088885655</v>
+        <v>0.1011398508793407</v>
       </c>
       <c r="T15">
-        <v>0.7989359431023945</v>
+        <v>0.8052622598518988</v>
       </c>
       <c r="U15">
         <v>0.06915748822216712</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.96375298729576</v>
+        <v>36.18062777391749</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09327360318445023</v>
+        <v>0.09308997128360744</v>
       </c>
       <c r="C16">
-        <v>5352.995767310873</v>
+        <v>5294.2455877544</v>
       </c>
       <c r="D16">
-        <v>5469.593767310873</v>
+        <v>5473.8005877544</v>
       </c>
       <c r="E16">
-        <v>-2049.002</v>
+        <v>-1986.045</v>
       </c>
       <c r="F16">
-        <v>881.3980000000001</v>
+        <v>944.3550000000002</v>
       </c>
       <c r="G16">
         <v>764.8</v>
@@ -2718,28 +2718,28 @@
         <v>2205.4</v>
       </c>
       <c r="M16">
-        <v>60.95527180404167</v>
+        <v>65.30921979004465</v>
       </c>
       <c r="N16">
-        <v>2144.444728195958</v>
+        <v>2140.090780209955</v>
       </c>
       <c r="O16">
-        <v>750.5556548685852</v>
+        <v>749.0317730734843</v>
       </c>
       <c r="P16">
-        <v>1393.889073327373</v>
+        <v>1391.059007136471</v>
       </c>
       <c r="Q16">
-        <v>1530.689073327373</v>
+        <v>1527.859007136471</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1011398508793407</v>
+        <v>0.1015848425669955</v>
       </c>
       <c r="T16">
-        <v>0.8052622598518988</v>
+        <v>0.8117374311131561</v>
       </c>
       <c r="U16">
         <v>0.06915748822216712</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>36.18062777391749</v>
+        <v>33.76858592232299</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09308997128360744</v>
+        <v>0.09290633938276464</v>
       </c>
       <c r="C17">
-        <v>5294.2455877544</v>
+        <v>5235.501884349906</v>
       </c>
       <c r="D17">
-        <v>5473.8005877544</v>
+        <v>5478.013884349905</v>
       </c>
       <c r="E17">
-        <v>-1986.045</v>
+        <v>-1923.088</v>
       </c>
       <c r="F17">
-        <v>944.355</v>
+        <v>1007.312</v>
       </c>
       <c r="G17">
         <v>764.8</v>
@@ -2800,28 +2800,28 @@
         <v>2205.4</v>
       </c>
       <c r="M17">
-        <v>65.30921979004464</v>
+        <v>69.66316777604762</v>
       </c>
       <c r="N17">
-        <v>2140.090780209955</v>
+        <v>2135.736832223952</v>
       </c>
       <c r="O17">
-        <v>749.0317730734843</v>
+        <v>747.5078912783832</v>
       </c>
       <c r="P17">
-        <v>1391.059007136471</v>
+        <v>1388.228940945569</v>
       </c>
       <c r="Q17">
-        <v>1527.859007136471</v>
+        <v>1525.028940945569</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1015848425669955</v>
+        <v>0.1020404292948325</v>
       </c>
       <c r="T17">
-        <v>0.8117374311131561</v>
+        <v>0.818366773118729</v>
       </c>
       <c r="U17">
         <v>0.06915748822216712</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.768585922323</v>
+        <v>31.65804930217781</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09290633938276464</v>
+        <v>0.09272270748192186</v>
       </c>
       <c r="C18">
-        <v>5235.501884349906</v>
+        <v>5176.764672063388</v>
       </c>
       <c r="D18">
-        <v>5478.013884349905</v>
+        <v>5482.233672063388</v>
       </c>
       <c r="E18">
-        <v>-1923.088</v>
+        <v>-1860.131</v>
       </c>
       <c r="F18">
-        <v>1007.312</v>
+        <v>1070.269</v>
       </c>
       <c r="G18">
         <v>764.8</v>
@@ -2882,28 +2882,28 @@
         <v>2205.4</v>
       </c>
       <c r="M18">
-        <v>69.66316777604762</v>
+        <v>74.01711576205059</v>
       </c>
       <c r="N18">
-        <v>2135.736832223952</v>
+        <v>2131.382884237949</v>
       </c>
       <c r="O18">
-        <v>747.5078912783832</v>
+        <v>745.9840094832821</v>
       </c>
       <c r="P18">
-        <v>1388.228940945569</v>
+        <v>1385.398874754667</v>
       </c>
       <c r="Q18">
-        <v>1525.028940945569</v>
+        <v>1522.198874754667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1020404292948325</v>
+        <v>0.1025069940161113</v>
       </c>
       <c r="T18">
-        <v>0.818366773118729</v>
+        <v>0.8251558583051591</v>
       </c>
       <c r="U18">
         <v>0.06915748822216712</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.65804930217781</v>
+        <v>29.79581110793205</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09272270748192186</v>
+        <v>0.09253907558107906</v>
       </c>
       <c r="C19">
-        <v>5176.764672063388</v>
+        <v>5118.033965907001</v>
       </c>
       <c r="D19">
-        <v>5482.233672063388</v>
+        <v>5486.459965907002</v>
       </c>
       <c r="E19">
-        <v>-1860.131</v>
+        <v>-1797.174</v>
       </c>
       <c r="F19">
-        <v>1070.269</v>
+        <v>1133.226</v>
       </c>
       <c r="G19">
         <v>764.8</v>
@@ -2964,28 +2964,28 @@
         <v>2205.4</v>
       </c>
       <c r="M19">
-        <v>74.01711576205059</v>
+        <v>78.37106374805359</v>
       </c>
       <c r="N19">
-        <v>2131.382884237949</v>
+        <v>2127.028936251946</v>
       </c>
       <c r="O19">
-        <v>745.9840094832821</v>
+        <v>744.460127688181</v>
       </c>
       <c r="P19">
-        <v>1385.398874754667</v>
+        <v>1382.568808563765</v>
       </c>
       <c r="Q19">
-        <v>1522.198874754667</v>
+        <v>1519.368808563765</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1025069940161113</v>
+        <v>0.1029849383647384</v>
       </c>
       <c r="T19">
-        <v>0.8251558583051591</v>
+        <v>0.8321105309351606</v>
       </c>
       <c r="U19">
         <v>0.06915748822216712</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.79581110793205</v>
+        <v>28.14048826860249</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09253907558107907</v>
+        <v>0.09235544368023631</v>
       </c>
       <c r="C20">
-        <v>5118.033965907001</v>
+        <v>5059.309780939222</v>
       </c>
       <c r="D20">
-        <v>5486.459965907002</v>
+        <v>5490.692780939222</v>
       </c>
       <c r="E20">
-        <v>-1797.174</v>
+        <v>-1734.217</v>
       </c>
       <c r="F20">
-        <v>1133.226</v>
+        <v>1196.183</v>
       </c>
       <c r="G20">
         <v>764.8</v>
@@ -3046,28 +3046,28 @@
         <v>2205.4</v>
       </c>
       <c r="M20">
-        <v>78.37106374805357</v>
+        <v>82.72501173405655</v>
       </c>
       <c r="N20">
-        <v>2127.028936251946</v>
+        <v>2122.674988265943</v>
       </c>
       <c r="O20">
-        <v>744.460127688181</v>
+        <v>742.9362458930801</v>
       </c>
       <c r="P20">
-        <v>1382.568808563765</v>
+        <v>1379.738742372863</v>
       </c>
       <c r="Q20">
-        <v>1519.368808563765</v>
+        <v>1516.538742372863</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1029849383647384</v>
+        <v>0.1034746838083934</v>
       </c>
       <c r="T20">
-        <v>0.8321105309351606</v>
+        <v>0.8392369238770143</v>
       </c>
       <c r="U20">
         <v>0.06915748822216712</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>28.14048826860249</v>
+        <v>26.65940993867605</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09235544368023631</v>
+        <v>0.0921718117793935</v>
       </c>
       <c r="C21">
-        <v>5059.309780939222</v>
+        <v>5000.592132265034</v>
       </c>
       <c r="D21">
-        <v>5490.692780939222</v>
+        <v>5494.932132265034</v>
       </c>
       <c r="E21">
-        <v>-1734.217</v>
+        <v>-1671.26</v>
       </c>
       <c r="F21">
-        <v>1196.183</v>
+        <v>1259.14</v>
       </c>
       <c r="G21">
         <v>764.8</v>
@@ -3128,28 +3128,28 @@
         <v>2205.4</v>
       </c>
       <c r="M21">
-        <v>82.72501173405655</v>
+        <v>87.07895972005953</v>
       </c>
       <c r="N21">
-        <v>2122.674988265943</v>
+        <v>2118.32104027994</v>
       </c>
       <c r="O21">
-        <v>742.9362458930801</v>
+        <v>741.412364097979</v>
       </c>
       <c r="P21">
-        <v>1379.738742372863</v>
+        <v>1376.908676181961</v>
       </c>
       <c r="Q21">
-        <v>1516.538742372863</v>
+        <v>1513.708676181961</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1034746838083934</v>
+        <v>0.1039766728881397</v>
       </c>
       <c r="T21">
-        <v>0.8392369238770143</v>
+        <v>0.8465414766424141</v>
       </c>
       <c r="U21">
         <v>0.06915748822216712</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.65940993867605</v>
+        <v>25.32643944174224</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0921718117793935</v>
+        <v>0.09198817987855074</v>
       </c>
       <c r="C22">
-        <v>5000.592132265034</v>
+        <v>4941.881035036107</v>
       </c>
       <c r="D22">
-        <v>5494.932132265034</v>
+        <v>5499.178035036108</v>
       </c>
       <c r="E22">
-        <v>-1671.26</v>
+        <v>-1608.303</v>
       </c>
       <c r="F22">
-        <v>1259.14</v>
+        <v>1322.097</v>
       </c>
       <c r="G22">
         <v>764.8</v>
@@ -3210,28 +3210,28 @@
         <v>2205.4</v>
       </c>
       <c r="M22">
-        <v>87.07895972005953</v>
+        <v>91.43290770606249</v>
       </c>
       <c r="N22">
-        <v>2118.32104027994</v>
+        <v>2113.967092293937</v>
       </c>
       <c r="O22">
-        <v>741.412364097979</v>
+        <v>739.8884823028779</v>
       </c>
       <c r="P22">
-        <v>1376.908676181961</v>
+        <v>1374.078609991059</v>
       </c>
       <c r="Q22">
-        <v>1513.708676181961</v>
+        <v>1510.878609991059</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1039766728881397</v>
+        <v>0.1044913705521834</v>
       </c>
       <c r="T22">
-        <v>0.8465414766424141</v>
+        <v>0.8540309547942797</v>
       </c>
       <c r="U22">
         <v>0.06915748822216712</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>25.32643944174224</v>
+        <v>24.12041851594499</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09198817987855074</v>
+        <v>0.09180454797770793</v>
       </c>
       <c r="C23">
-        <v>4941.881035036107</v>
+        <v>4883.176504450982</v>
       </c>
       <c r="D23">
-        <v>5499.178035036108</v>
+        <v>5503.430504450982</v>
       </c>
       <c r="E23">
-        <v>-1608.303</v>
+        <v>-1545.346</v>
       </c>
       <c r="F23">
-        <v>1322.097</v>
+        <v>1385.054</v>
       </c>
       <c r="G23">
         <v>764.8</v>
@@ -3292,28 +3292,28 @@
         <v>2205.4</v>
       </c>
       <c r="M23">
-        <v>91.43290770606249</v>
+        <v>95.78685569206547</v>
       </c>
       <c r="N23">
-        <v>2113.967092293937</v>
+        <v>2109.613144307934</v>
       </c>
       <c r="O23">
-        <v>739.8884823028779</v>
+        <v>738.364600507777</v>
       </c>
       <c r="P23">
-        <v>1374.078609991059</v>
+        <v>1371.248543800157</v>
       </c>
       <c r="Q23">
-        <v>1510.878609991059</v>
+        <v>1508.048543800157</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1044913705521834</v>
+        <v>0.1050192655922283</v>
       </c>
       <c r="T23">
-        <v>0.8540309547942797</v>
+        <v>0.8617124708474753</v>
       </c>
       <c r="U23">
         <v>0.06915748822216712</v>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>24.12041851594499</v>
+        <v>23.02403585612932</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09180454797770793</v>
+        <v>0.09162091607686515</v>
       </c>
       <c r="C24">
-        <v>4883.176504450982</v>
+        <v>4824.47855575524</v>
       </c>
       <c r="D24">
-        <v>5503.430504450982</v>
+        <v>5507.68955575524</v>
       </c>
       <c r="E24">
-        <v>-1545.346</v>
+        <v>-1482.389</v>
       </c>
       <c r="F24">
-        <v>1385.054</v>
+        <v>1448.011</v>
       </c>
       <c r="G24">
         <v>764.8</v>
@@ -3374,28 +3374,28 @@
         <v>2205.4</v>
       </c>
       <c r="M24">
-        <v>95.78685569206547</v>
+        <v>100.1408036780685</v>
       </c>
       <c r="N24">
-        <v>2109.613144307934</v>
+        <v>2105.259196321931</v>
       </c>
       <c r="O24">
-        <v>738.364600507777</v>
+        <v>736.8407187126759</v>
       </c>
       <c r="P24">
-        <v>1371.248543800157</v>
+        <v>1368.418477609255</v>
       </c>
       <c r="Q24">
-        <v>1508.048543800157</v>
+        <v>1505.218477609255</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1050192655922283</v>
+        <v>0.1055608721917548</v>
       </c>
       <c r="T24">
-        <v>0.8617124708474753</v>
+        <v>0.8695935067981564</v>
       </c>
       <c r="U24">
         <v>0.06915748822216712</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>23.02403585612932</v>
+        <v>22.0229908189063</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09162091607686515</v>
+        <v>0.09143728417602237</v>
       </c>
       <c r="C25">
-        <v>4824.47855575524</v>
+        <v>4765.787204241697</v>
       </c>
       <c r="D25">
-        <v>5507.68955575524</v>
+        <v>5511.955204241697</v>
       </c>
       <c r="E25">
-        <v>-1482.389</v>
+        <v>-1419.432</v>
       </c>
       <c r="F25">
-        <v>1448.011</v>
+        <v>1510.968</v>
       </c>
       <c r="G25">
         <v>764.8</v>
@@ -3456,28 +3456,28 @@
         <v>2205.4</v>
       </c>
       <c r="M25">
-        <v>100.1408036780685</v>
+        <v>104.4947516640714</v>
       </c>
       <c r="N25">
-        <v>2105.259196321931</v>
+        <v>2100.905248335928</v>
       </c>
       <c r="O25">
-        <v>736.8407187126759</v>
+        <v>735.3168369175748</v>
       </c>
       <c r="P25">
-        <v>1368.418477609255</v>
+        <v>1365.588411418353</v>
       </c>
       <c r="Q25">
-        <v>1505.218477609255</v>
+        <v>1502.388411418353</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1055608721917548</v>
+        <v>0.106116731596532</v>
       </c>
       <c r="T25">
-        <v>0.8695935067981564</v>
+        <v>0.8776819384317501</v>
       </c>
       <c r="U25">
         <v>0.06915748822216712</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>22.0229908189063</v>
+        <v>21.10536620145187</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09143728417602236</v>
+        <v>0.09125365227517959</v>
       </c>
       <c r="C26">
-        <v>4765.787204241698</v>
+        <v>4707.102465250584</v>
       </c>
       <c r="D26">
-        <v>5511.955204241697</v>
+        <v>5516.227465250584</v>
       </c>
       <c r="E26">
-        <v>-1419.432</v>
+        <v>-1356.475</v>
       </c>
       <c r="F26">
-        <v>1510.968</v>
+        <v>1573.925</v>
       </c>
       <c r="G26">
         <v>764.8</v>
@@ -3538,28 +3538,28 @@
         <v>2205.4</v>
       </c>
       <c r="M26">
-        <v>104.4947516640714</v>
+        <v>108.8486996500744</v>
       </c>
       <c r="N26">
-        <v>2100.905248335928</v>
+        <v>2096.551300349925</v>
       </c>
       <c r="O26">
-        <v>735.3168369175748</v>
+        <v>733.7929551224738</v>
       </c>
       <c r="P26">
-        <v>1365.588411418353</v>
+        <v>1362.758345227452</v>
       </c>
       <c r="Q26">
-        <v>1502.388411418353</v>
+        <v>1499.558345227452</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.106116731596532</v>
+        <v>0.1066874139187699</v>
       </c>
       <c r="T26">
-        <v>0.8776819384317501</v>
+        <v>0.8859860615755732</v>
       </c>
       <c r="U26">
         <v>0.06915748822216712</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>21.10536620145187</v>
+        <v>20.2611515533938</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09125365227517959</v>
+        <v>0.0910700203743368</v>
       </c>
       <c r="C27">
-        <v>4707.102465250584</v>
+        <v>4648.424354169723</v>
       </c>
       <c r="D27">
-        <v>5516.227465250584</v>
+        <v>5520.506354169724</v>
       </c>
       <c r="E27">
-        <v>-1356.475</v>
+        <v>-1293.518</v>
       </c>
       <c r="F27">
-        <v>1573.925</v>
+        <v>1636.882</v>
       </c>
       <c r="G27">
         <v>764.8</v>
@@ -3620,28 +3620,28 @@
         <v>2205.4</v>
       </c>
       <c r="M27">
-        <v>108.8486996500744</v>
+        <v>113.2026476360774</v>
       </c>
       <c r="N27">
-        <v>2096.551300349925</v>
+        <v>2092.197352363922</v>
       </c>
       <c r="O27">
-        <v>733.7929551224738</v>
+        <v>732.2690733273727</v>
       </c>
       <c r="P27">
-        <v>1362.758345227452</v>
+        <v>1359.92827903655</v>
       </c>
       <c r="Q27">
-        <v>1499.558345227452</v>
+        <v>1496.72827903655</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1066874139187699</v>
+        <v>0.1072735200875548</v>
       </c>
       <c r="T27">
-        <v>0.8859860615755732</v>
+        <v>0.8945146204800399</v>
       </c>
       <c r="U27">
         <v>0.06915748822216712</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>20.2611515533938</v>
+        <v>19.48187649364788</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0910700203743368</v>
+        <v>0.09088638847349402</v>
       </c>
       <c r="C28">
-        <v>4648.424354169723</v>
+        <v>4589.752886434726</v>
       </c>
       <c r="D28">
-        <v>5520.506354169724</v>
+        <v>5524.791886434726</v>
       </c>
       <c r="E28">
-        <v>-1293.518</v>
+        <v>-1230.561</v>
       </c>
       <c r="F28">
-        <v>1636.882</v>
+        <v>1699.839</v>
       </c>
       <c r="G28">
         <v>764.8</v>
@@ -3702,28 +3702,28 @@
         <v>2205.4</v>
       </c>
       <c r="M28">
-        <v>113.2026476360774</v>
+        <v>117.5565956220804</v>
       </c>
       <c r="N28">
-        <v>2092.197352363922</v>
+        <v>2087.843404377919</v>
       </c>
       <c r="O28">
-        <v>732.2690733273727</v>
+        <v>730.7451915322717</v>
       </c>
       <c r="P28">
-        <v>1359.92827903655</v>
+        <v>1357.098212845648</v>
       </c>
       <c r="Q28">
-        <v>1496.72827903655</v>
+        <v>1493.898212845648</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1072735200875548</v>
+        <v>0.1078756839595941</v>
       </c>
       <c r="T28">
-        <v>0.8945146204800399</v>
+        <v>0.9032768385325745</v>
       </c>
       <c r="U28">
         <v>0.06915748822216712</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.48187649364788</v>
+        <v>18.76032551240166</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09088638847349402</v>
+        <v>0.09070275657265123</v>
       </c>
       <c r="C29">
-        <v>4589.752886434726</v>
+        <v>4531.088077529165</v>
       </c>
       <c r="D29">
-        <v>5524.791886434726</v>
+        <v>5529.084077529165</v>
       </c>
       <c r="E29">
-        <v>-1230.561</v>
+        <v>-1167.604</v>
       </c>
       <c r="F29">
-        <v>1699.839</v>
+        <v>1762.796</v>
       </c>
       <c r="G29">
         <v>764.8</v>
@@ -3784,28 +3784,28 @@
         <v>2205.4</v>
       </c>
       <c r="M29">
-        <v>117.5565956220804</v>
+        <v>121.9105436080833</v>
       </c>
       <c r="N29">
-        <v>2087.843404377919</v>
+        <v>2083.489456391917</v>
       </c>
       <c r="O29">
-        <v>730.7451915322717</v>
+        <v>729.2213097371707</v>
       </c>
       <c r="P29">
-        <v>1357.098212845648</v>
+        <v>1354.268146654746</v>
       </c>
       <c r="Q29">
-        <v>1493.898212845648</v>
+        <v>1491.068146654746</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1078756839595941</v>
+        <v>0.1084945746058567</v>
       </c>
       <c r="T29">
-        <v>0.9032768385325745</v>
+        <v>0.9122824515310125</v>
       </c>
       <c r="U29">
         <v>0.06915748822216712</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.76032551240166</v>
+        <v>18.09031388695875</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09070275657265123</v>
+        <v>0.09051912467180843</v>
       </c>
       <c r="C30">
-        <v>4531.088077529165</v>
+        <v>4472.42994298477</v>
       </c>
       <c r="D30">
-        <v>5529.084077529165</v>
+        <v>5533.38294298477</v>
       </c>
       <c r="E30">
-        <v>-1167.604</v>
+        <v>-1104.647</v>
       </c>
       <c r="F30">
-        <v>1762.796</v>
+        <v>1825.753</v>
       </c>
       <c r="G30">
         <v>764.8</v>
@@ -3866,28 +3866,28 @@
         <v>2205.4</v>
       </c>
       <c r="M30">
-        <v>121.9105436080833</v>
+        <v>126.2644915940863</v>
       </c>
       <c r="N30">
-        <v>2083.489456391917</v>
+        <v>2079.135508405913</v>
       </c>
       <c r="O30">
-        <v>729.2213097371707</v>
+        <v>727.6974279420696</v>
       </c>
       <c r="P30">
-        <v>1354.268146654746</v>
+        <v>1351.438080463844</v>
       </c>
       <c r="Q30">
-        <v>1491.068146654746</v>
+        <v>1488.238080463844</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1084945746058567</v>
+        <v>0.1091308987914506</v>
       </c>
       <c r="T30">
-        <v>0.9122824515310125</v>
+        <v>0.9215417437688432</v>
       </c>
       <c r="U30">
         <v>0.06915748822216712</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>18.09031388695875</v>
+        <v>17.46650995982224</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09051912467180843</v>
+        <v>0.09033549277096564</v>
       </c>
       <c r="C31">
-        <v>4472.429942984771</v>
+        <v>4413.778498381611</v>
       </c>
       <c r="D31">
-        <v>5533.38294298477</v>
+        <v>5537.688498381611</v>
       </c>
       <c r="E31">
-        <v>-1104.647</v>
+        <v>-1041.69</v>
       </c>
       <c r="F31">
-        <v>1825.753</v>
+        <v>1888.71</v>
       </c>
       <c r="G31">
         <v>764.8</v>
@@ -3948,28 +3948,28 @@
         <v>2205.4</v>
       </c>
       <c r="M31">
-        <v>126.2644915940863</v>
+        <v>130.6184395800893</v>
       </c>
       <c r="N31">
-        <v>2079.135508405913</v>
+        <v>2074.78156041991</v>
       </c>
       <c r="O31">
-        <v>727.6974279420696</v>
+        <v>726.1735461469686</v>
       </c>
       <c r="P31">
-        <v>1351.438080463844</v>
+        <v>1348.608014272942</v>
       </c>
       <c r="Q31">
-        <v>1488.238080463844</v>
+        <v>1485.408014272942</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1091308987914506</v>
+        <v>0.1097854036680615</v>
       </c>
       <c r="T31">
-        <v>0.9215417437688432</v>
+        <v>0.9310655872134691</v>
       </c>
       <c r="U31">
         <v>0.06915748822216712</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.46650995982224</v>
+        <v>16.8842929611615</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09033549277096564</v>
+        <v>0.09015186087012286</v>
       </c>
       <c r="C32">
-        <v>4413.778498381611</v>
+        <v>4355.133759348288</v>
       </c>
       <c r="D32">
-        <v>5537.688498381611</v>
+        <v>5542.000759348288</v>
       </c>
       <c r="E32">
-        <v>-1041.69</v>
+        <v>-978.7329999999999</v>
       </c>
       <c r="F32">
-        <v>1888.71</v>
+        <v>1951.667</v>
       </c>
       <c r="G32">
         <v>764.8</v>
@@ -4030,28 +4030,28 @@
         <v>2205.4</v>
       </c>
       <c r="M32">
-        <v>130.6184395800893</v>
+        <v>134.9723875660922</v>
       </c>
       <c r="N32">
-        <v>2074.78156041991</v>
+        <v>2070.427612433908</v>
       </c>
       <c r="O32">
-        <v>726.1735461469686</v>
+        <v>724.6496643518676</v>
       </c>
       <c r="P32">
-        <v>1348.608014272942</v>
+        <v>1345.77794808204</v>
       </c>
       <c r="Q32">
-        <v>1485.408014272942</v>
+        <v>1482.57794808204</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1097854036680615</v>
+        <v>0.1104588797005162</v>
       </c>
       <c r="T32">
-        <v>0.9310655872134691</v>
+        <v>0.9408654840912727</v>
       </c>
       <c r="U32">
         <v>0.06915748822216712</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.8842929611615</v>
+        <v>16.33963834951113</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09015186087012286</v>
+        <v>0.08996822896928008</v>
       </c>
       <c r="C33">
-        <v>4355.133759348288</v>
+        <v>4296.495741562117</v>
       </c>
       <c r="D33">
-        <v>5542.000759348288</v>
+        <v>5546.319741562118</v>
       </c>
       <c r="E33">
-        <v>-978.7329999999999</v>
+        <v>-915.7759999999998</v>
       </c>
       <c r="F33">
-        <v>1951.667</v>
+        <v>2014.624</v>
       </c>
       <c r="G33">
         <v>764.8</v>
@@ -4112,28 +4112,28 @@
         <v>2205.4</v>
       </c>
       <c r="M33">
-        <v>134.9723875660922</v>
+        <v>139.3263355520952</v>
       </c>
       <c r="N33">
-        <v>2070.427612433908</v>
+        <v>2066.073664447904</v>
       </c>
       <c r="O33">
-        <v>724.6496643518676</v>
+        <v>723.1257825567665</v>
       </c>
       <c r="P33">
-        <v>1345.77794808204</v>
+        <v>1342.947881891138</v>
       </c>
       <c r="Q33">
-        <v>1482.57794808204</v>
+        <v>1479.747881891138</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1104588797005162</v>
+        <v>0.1111521638515725</v>
       </c>
       <c r="T33">
-        <v>0.9408654840912727</v>
+        <v>0.9509536132301881</v>
       </c>
       <c r="U33">
         <v>0.06915748822216712</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.33963834951113</v>
+        <v>15.8290246510889</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08996822896928008</v>
+        <v>0.08978459706843728</v>
       </c>
       <c r="C34">
-        <v>4296.495741562117</v>
+        <v>4237.864460749332</v>
       </c>
       <c r="D34">
-        <v>5546.319741562118</v>
+        <v>5550.645460749332</v>
       </c>
       <c r="E34">
-        <v>-915.7759999999998</v>
+        <v>-852.819</v>
       </c>
       <c r="F34">
-        <v>2014.624</v>
+        <v>2077.581</v>
       </c>
       <c r="G34">
         <v>764.8</v>
@@ -4194,28 +4194,28 @@
         <v>2205.4</v>
       </c>
       <c r="M34">
-        <v>139.3263355520952</v>
+        <v>143.6802835380982</v>
       </c>
       <c r="N34">
-        <v>2066.073664447904</v>
+        <v>2061.719716461901</v>
       </c>
       <c r="O34">
-        <v>723.1257825567665</v>
+        <v>721.6019007616654</v>
       </c>
       <c r="P34">
-        <v>1342.947881891138</v>
+        <v>1340.117815700236</v>
       </c>
       <c r="Q34">
-        <v>1479.747881891138</v>
+        <v>1476.917815700236</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1111521638515725</v>
+        <v>0.1118661430519141</v>
       </c>
       <c r="T34">
-        <v>0.9509536132301881</v>
+        <v>0.9613428805523546</v>
       </c>
       <c r="U34">
         <v>0.06915748822216712</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.8290246510889</v>
+        <v>15.34935723741954</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08978459706843728</v>
+        <v>0.0896009651675945</v>
       </c>
       <c r="C35">
-        <v>4237.864460749332</v>
+        <v>4179.239932685251</v>
       </c>
       <c r="D35">
-        <v>5550.645460749332</v>
+        <v>5554.977932685251</v>
       </c>
       <c r="E35">
-        <v>-852.819</v>
+        <v>-789.8619999999996</v>
       </c>
       <c r="F35">
-        <v>2077.581</v>
+        <v>2140.538</v>
       </c>
       <c r="G35">
         <v>764.8</v>
@@ -4276,28 +4276,28 @@
         <v>2205.4</v>
       </c>
       <c r="M35">
-        <v>143.6802835380982</v>
+        <v>148.0342315241012</v>
       </c>
       <c r="N35">
-        <v>2061.719716461901</v>
+        <v>2057.365768475898</v>
       </c>
       <c r="O35">
-        <v>721.6019007616654</v>
+        <v>720.0780189665643</v>
       </c>
       <c r="P35">
-        <v>1340.117815700236</v>
+        <v>1337.287749509334</v>
       </c>
       <c r="Q35">
-        <v>1476.917815700236</v>
+        <v>1474.087749509334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1118661430519141</v>
+        <v>0.1126017579855993</v>
       </c>
       <c r="T35">
-        <v>0.9613428805523546</v>
+        <v>0.9720469741570111</v>
       </c>
       <c r="U35">
         <v>0.06915748822216712</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.34935723741954</v>
+        <v>14.89790555396602</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0896009651675945</v>
+        <v>0.08941733326675172</v>
       </c>
       <c r="C36">
-        <v>4179.239932685251</v>
+        <v>4120.622173194497</v>
       </c>
       <c r="D36">
-        <v>5554.977932685251</v>
+        <v>5559.317173194497</v>
       </c>
       <c r="E36">
-        <v>-789.8619999999996</v>
+        <v>-726.9049999999997</v>
       </c>
       <c r="F36">
-        <v>2140.538</v>
+        <v>2203.495</v>
       </c>
       <c r="G36">
         <v>764.8</v>
@@ -4358,28 +4358,28 @@
         <v>2205.4</v>
       </c>
       <c r="M36">
-        <v>148.0342315241012</v>
+        <v>152.3881795101042</v>
       </c>
       <c r="N36">
-        <v>2057.365768475898</v>
+        <v>2053.011820489895</v>
       </c>
       <c r="O36">
-        <v>720.0780189665643</v>
+        <v>718.5541371714634</v>
       </c>
       <c r="P36">
-        <v>1337.287749509334</v>
+        <v>1334.457683318432</v>
       </c>
       <c r="Q36">
-        <v>1474.087749509334</v>
+        <v>1471.257683318432</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1126017579855993</v>
+        <v>0.1133600072249365</v>
       </c>
       <c r="T36">
-        <v>0.9720469741570111</v>
+        <v>0.9830804244879647</v>
       </c>
       <c r="U36">
         <v>0.06915748822216712</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.89790555396602</v>
+        <v>14.472251109567</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08941733326675172</v>
+        <v>0.08923370136590891</v>
       </c>
       <c r="C37">
-        <v>4120.622173194497</v>
+        <v>4062.01119815117</v>
       </c>
       <c r="D37">
-        <v>5559.317173194497</v>
+        <v>5563.66319815117</v>
       </c>
       <c r="E37">
-        <v>-726.9049999999997</v>
+        <v>-663.9479999999994</v>
       </c>
       <c r="F37">
-        <v>2203.495</v>
+        <v>2266.452000000001</v>
       </c>
       <c r="G37">
         <v>764.8</v>
@@ -4440,28 +4440,28 @@
         <v>2205.4</v>
       </c>
       <c r="M37">
-        <v>152.3881795101042</v>
+        <v>156.7421274961072</v>
       </c>
       <c r="N37">
-        <v>2053.011820489895</v>
+        <v>2048.657872503893</v>
       </c>
       <c r="O37">
-        <v>718.5541371714634</v>
+        <v>717.0302553763623</v>
       </c>
       <c r="P37">
-        <v>1334.457683318432</v>
+        <v>1331.62761712753</v>
       </c>
       <c r="Q37">
-        <v>1471.257683318432</v>
+        <v>1468.42761712753</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1133600072249365</v>
+        <v>0.1141419517530028</v>
       </c>
       <c r="T37">
-        <v>0.9830804244879647</v>
+        <v>0.9944586701417606</v>
       </c>
       <c r="U37">
         <v>0.06915748822216712</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.472251109567</v>
+        <v>14.07024413430124</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08923370136590893</v>
+        <v>0.08905006946506615</v>
       </c>
       <c r="C38">
-        <v>4062.01119815117</v>
+        <v>4003.407023479047</v>
       </c>
       <c r="D38">
-        <v>5563.66319815117</v>
+        <v>5568.016023479047</v>
       </c>
       <c r="E38">
-        <v>-663.9479999999999</v>
+        <v>-600.991</v>
       </c>
       <c r="F38">
-        <v>2266.452</v>
+        <v>2329.409</v>
       </c>
       <c r="G38">
         <v>764.8</v>
@@ -4522,28 +4522,28 @@
         <v>2205.4</v>
       </c>
       <c r="M38">
-        <v>156.7421274961071</v>
+        <v>161.0960754821101</v>
       </c>
       <c r="N38">
-        <v>2048.657872503893</v>
+        <v>2044.30392451789</v>
       </c>
       <c r="O38">
-        <v>717.0302553763623</v>
+        <v>715.5063735812613</v>
       </c>
       <c r="P38">
-        <v>1331.62761712753</v>
+        <v>1328.797550936628</v>
       </c>
       <c r="Q38">
-        <v>1468.42761712753</v>
+        <v>1465.597550936628</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1141419517530028</v>
+        <v>0.1149487199168809</v>
       </c>
       <c r="T38">
-        <v>0.9944586701417606</v>
+        <v>1.006198129943296</v>
       </c>
       <c r="U38">
         <v>0.06915748822216712</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>14.07024413430125</v>
+        <v>13.68996726580662</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08905006946506615</v>
+        <v>0.08886643756422337</v>
       </c>
       <c r="C39">
-        <v>4003.407023479047</v>
+        <v>3944.809665151784</v>
       </c>
       <c r="D39">
-        <v>5568.016023479047</v>
+        <v>5572.375665151784</v>
       </c>
       <c r="E39">
-        <v>-600.991</v>
+        <v>-538.0339999999997</v>
       </c>
       <c r="F39">
-        <v>2329.409</v>
+        <v>2392.366</v>
       </c>
       <c r="G39">
         <v>764.8</v>
@@ -4604,28 +4604,28 @@
         <v>2205.4</v>
       </c>
       <c r="M39">
-        <v>161.0960754821101</v>
+        <v>165.4500234681131</v>
       </c>
       <c r="N39">
-        <v>2044.30392451789</v>
+        <v>2039.949976531886</v>
       </c>
       <c r="O39">
-        <v>715.5063735812613</v>
+        <v>713.9824917861603</v>
       </c>
       <c r="P39">
-        <v>1328.797550936628</v>
+        <v>1325.967484745726</v>
       </c>
       <c r="Q39">
-        <v>1465.597550936628</v>
+        <v>1462.767484745726</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1149487199168809</v>
+        <v>0.1157815128602389</v>
       </c>
       <c r="T39">
-        <v>1.006198129943296</v>
+        <v>1.018316281996494</v>
       </c>
       <c r="U39">
         <v>0.06915748822216712</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.68996726580662</v>
+        <v>13.32970496933802</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08886643756422337</v>
+        <v>0.08868280566338058</v>
       </c>
       <c r="C40">
-        <v>3944.809665151784</v>
+        <v>3886.219139193096</v>
       </c>
       <c r="D40">
-        <v>5572.375665151784</v>
+        <v>5576.742139193097</v>
       </c>
       <c r="E40">
-        <v>-538.0339999999997</v>
+        <v>-475.0769999999998</v>
       </c>
       <c r="F40">
-        <v>2392.366</v>
+        <v>2455.323</v>
       </c>
       <c r="G40">
         <v>764.8</v>
@@ -4686,28 +4686,28 @@
         <v>2205.4</v>
       </c>
       <c r="M40">
-        <v>165.4500234681131</v>
+        <v>169.8039714541161</v>
       </c>
       <c r="N40">
-        <v>2039.949976531886</v>
+        <v>2035.596028545884</v>
       </c>
       <c r="O40">
-        <v>713.9824917861603</v>
+        <v>712.4586099910592</v>
       </c>
       <c r="P40">
-        <v>1325.967484745726</v>
+        <v>1323.137418554824</v>
       </c>
       <c r="Q40">
-        <v>1462.767484745726</v>
+        <v>1459.937418554824</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1157815128602389</v>
+        <v>0.1166416104902643</v>
       </c>
       <c r="T40">
-        <v>1.018316281996494</v>
+        <v>1.030831750510453</v>
       </c>
       <c r="U40">
         <v>0.06915748822216712</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.32970496933802</v>
+        <v>12.98791766243192</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08868280566338058</v>
+        <v>0.08888917376253778</v>
       </c>
       <c r="C41">
-        <v>3886.219139193096</v>
+        <v>3818.355510246231</v>
       </c>
       <c r="D41">
-        <v>5576.742139193097</v>
+        <v>5571.835510246232</v>
       </c>
       <c r="E41">
-        <v>-475.0769999999998</v>
+        <v>-412.1199999999994</v>
       </c>
       <c r="F41">
-        <v>2455.323</v>
+        <v>2518.280000000001</v>
       </c>
       <c r="G41">
         <v>764.8</v>
@@ -4768,45 +4768,45 @@
         <v>2205.4</v>
       </c>
       <c r="M41">
-        <v>169.8039714541161</v>
+        <v>177.935339440119</v>
       </c>
       <c r="N41">
-        <v>2035.596028545884</v>
+        <v>2027.46466055988</v>
       </c>
       <c r="O41">
-        <v>712.4586099910592</v>
+        <v>709.6126311959581</v>
       </c>
       <c r="P41">
-        <v>1323.137418554824</v>
+        <v>1317.852029363922</v>
       </c>
       <c r="Q41">
-        <v>1459.937418554824</v>
+        <v>1454.652029363922</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1166416104902643</v>
+        <v>0.1175303780412906</v>
       </c>
       <c r="T41">
-        <v>1.030831750510453</v>
+        <v>1.043764401308209</v>
       </c>
       <c r="U41">
-        <v>0.06915748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V41">
         <v>0.35</v>
       </c>
       <c r="W41">
-        <v>0.04495236734440863</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y41">
-        <v>12.98791766243192</v>
+        <v>12.39439004606607</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08888917376253778</v>
+        <v>0.08871529186169499</v>
       </c>
       <c r="C42">
-        <v>3818.355510246231</v>
+        <v>3759.532171004503</v>
       </c>
       <c r="D42">
-        <v>5571.835510246232</v>
+        <v>5575.969171004504</v>
       </c>
       <c r="E42">
-        <v>-412.1199999999994</v>
+        <v>-349.1629999999996</v>
       </c>
       <c r="F42">
-        <v>2518.280000000001</v>
+        <v>2581.237000000001</v>
       </c>
       <c r="G42">
         <v>764.8</v>
@@ -4850,28 +4850,28 @@
         <v>2205.4</v>
       </c>
       <c r="M42">
-        <v>177.935339440119</v>
+        <v>182.383722926122</v>
       </c>
       <c r="N42">
-        <v>2027.46466055988</v>
+        <v>2023.016277073878</v>
       </c>
       <c r="O42">
-        <v>709.6126311959581</v>
+        <v>708.0556969758571</v>
       </c>
       <c r="P42">
-        <v>1317.852029363922</v>
+        <v>1314.96058009802</v>
       </c>
       <c r="Q42">
-        <v>1454.652029363922</v>
+        <v>1451.76058009802</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1175303780412906</v>
+        <v>0.118449273305911</v>
       </c>
       <c r="T42">
-        <v>1.043764401308209</v>
+        <v>1.057135447048263</v>
       </c>
       <c r="U42">
         <v>0.07065748822216711</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.39439004606607</v>
+        <v>12.09208784982056</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08871529186169499</v>
+        <v>0.08854140996085222</v>
       </c>
       <c r="C43">
-        <v>3759.532171004503</v>
+        <v>3700.714969717616</v>
       </c>
       <c r="D43">
-        <v>5575.969171004504</v>
+        <v>5580.108969717616</v>
       </c>
       <c r="E43">
-        <v>-349.1629999999996</v>
+        <v>-286.2059999999997</v>
       </c>
       <c r="F43">
-        <v>2581.237000000001</v>
+        <v>2644.194</v>
       </c>
       <c r="G43">
         <v>764.8</v>
@@ -4932,28 +4932,28 @@
         <v>2205.4</v>
       </c>
       <c r="M43">
-        <v>182.383722926122</v>
+        <v>186.832106412125</v>
       </c>
       <c r="N43">
-        <v>2023.016277073878</v>
+        <v>2018.567893587875</v>
       </c>
       <c r="O43">
-        <v>708.0556969758571</v>
+        <v>706.498762755756</v>
       </c>
       <c r="P43">
-        <v>1314.96058009802</v>
+        <v>1312.069130832118</v>
       </c>
       <c r="Q43">
-        <v>1451.76058009802</v>
+        <v>1448.869130832118</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.118449273305911</v>
+        <v>0.119399854614139</v>
       </c>
       <c r="T43">
-        <v>1.057135447048263</v>
+        <v>1.070967563331078</v>
       </c>
       <c r="U43">
         <v>0.07065748822216711</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>12.09208784982056</v>
+        <v>11.80418099625341</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08854140996085223</v>
+        <v>0.08836752806000941</v>
       </c>
       <c r="C44">
-        <v>3700.714969717616</v>
+        <v>3641.90392006684</v>
       </c>
       <c r="D44">
-        <v>5580.108969717616</v>
+        <v>5584.25492006684</v>
       </c>
       <c r="E44">
-        <v>-286.2059999999997</v>
+        <v>-223.2489999999998</v>
       </c>
       <c r="F44">
-        <v>2644.194</v>
+        <v>2707.151</v>
       </c>
       <c r="G44">
         <v>764.8</v>
@@ -5014,28 +5014,28 @@
         <v>2205.4</v>
       </c>
       <c r="M44">
-        <v>186.832106412125</v>
+        <v>191.2804898981279</v>
       </c>
       <c r="N44">
-        <v>2018.567893587875</v>
+        <v>2014.119510101872</v>
       </c>
       <c r="O44">
-        <v>706.498762755756</v>
+        <v>704.941828535655</v>
       </c>
       <c r="P44">
-        <v>1312.069130832118</v>
+        <v>1309.177681566217</v>
       </c>
       <c r="Q44">
-        <v>1448.869130832118</v>
+        <v>1445.977681566216</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.119399854614139</v>
+        <v>0.1203837896524802</v>
       </c>
       <c r="T44">
-        <v>1.070967563331078</v>
+        <v>1.085285017027324</v>
       </c>
       <c r="U44">
         <v>0.07065748822216711</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.80418099625341</v>
+        <v>11.52966515913123</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08836752806000941</v>
+        <v>0.08819364615916664</v>
       </c>
       <c r="C45">
-        <v>3641.90392006684</v>
+        <v>3583.099035774133</v>
       </c>
       <c r="D45">
-        <v>5584.25492006684</v>
+        <v>5588.407035774133</v>
       </c>
       <c r="E45">
-        <v>-223.2489999999998</v>
+        <v>-160.2919999999999</v>
       </c>
       <c r="F45">
-        <v>2707.151</v>
+        <v>2770.108</v>
       </c>
       <c r="G45">
         <v>764.8</v>
@@ -5096,28 +5096,28 @@
         <v>2205.4</v>
       </c>
       <c r="M45">
-        <v>191.2804898981279</v>
+        <v>195.7288733841309</v>
       </c>
       <c r="N45">
-        <v>2014.119510101872</v>
+        <v>2009.671126615869</v>
       </c>
       <c r="O45">
-        <v>704.941828535655</v>
+        <v>703.384894315554</v>
       </c>
       <c r="P45">
-        <v>1309.177681566217</v>
+        <v>1306.286232300315</v>
       </c>
       <c r="Q45">
-        <v>1445.977681566216</v>
+        <v>1443.086232300315</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1203837896524802</v>
+        <v>0.1214028652279051</v>
       </c>
       <c r="T45">
-        <v>1.085285017027324</v>
+        <v>1.100113808355579</v>
       </c>
       <c r="U45">
         <v>0.07065748822216711</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.52966515913123</v>
+        <v>11.26762731460552</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08819364615916664</v>
+        <v>0.08801976425832385</v>
       </c>
       <c r="C46">
-        <v>3583.099035774133</v>
+        <v>3524.300330602297</v>
       </c>
       <c r="D46">
-        <v>5588.407035774133</v>
+        <v>5592.565330602297</v>
       </c>
       <c r="E46">
-        <v>-160.2919999999999</v>
+        <v>-97.33499999999958</v>
       </c>
       <c r="F46">
-        <v>2770.108</v>
+        <v>2833.065000000001</v>
       </c>
       <c r="G46">
         <v>764.8</v>
@@ -5178,28 +5178,28 @@
         <v>2205.4</v>
       </c>
       <c r="M46">
-        <v>195.7288733841309</v>
+        <v>200.1772568701339</v>
       </c>
       <c r="N46">
-        <v>2009.671126615869</v>
+        <v>2005.222743129866</v>
       </c>
       <c r="O46">
-        <v>703.384894315554</v>
+        <v>701.8279600954529</v>
       </c>
       <c r="P46">
-        <v>1306.286232300315</v>
+        <v>1303.394783034413</v>
       </c>
       <c r="Q46">
-        <v>1443.086232300315</v>
+        <v>1440.194783034413</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1214028652279051</v>
+        <v>0.1224589980969818</v>
       </c>
       <c r="T46">
-        <v>1.100113808355579</v>
+        <v>1.115481828459408</v>
       </c>
       <c r="U46">
         <v>0.07065748822216711</v>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.26762731460552</v>
+        <v>11.01723559650318</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08801976425832385</v>
+        <v>0.08784588235748107</v>
       </c>
       <c r="C47">
-        <v>3524.300330602297</v>
+        <v>3465.507818355123</v>
       </c>
       <c r="D47">
-        <v>5592.565330602297</v>
+        <v>5596.729818355123</v>
       </c>
       <c r="E47">
-        <v>-97.33499999999958</v>
+        <v>-34.3779999999997</v>
       </c>
       <c r="F47">
-        <v>2833.065000000001</v>
+        <v>2896.022</v>
       </c>
       <c r="G47">
         <v>764.8</v>
@@ -5260,28 +5260,28 @@
         <v>2205.4</v>
       </c>
       <c r="M47">
-        <v>200.1772568701339</v>
+        <v>204.6256403561369</v>
       </c>
       <c r="N47">
-        <v>2005.222743129866</v>
+        <v>2000.774359643863</v>
       </c>
       <c r="O47">
-        <v>701.8279600954529</v>
+        <v>700.2710258753519</v>
       </c>
       <c r="P47">
-        <v>1303.394783034413</v>
+        <v>1300.503333768511</v>
       </c>
       <c r="Q47">
-        <v>1440.194783034413</v>
+        <v>1437.303333768511</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1224589980969818</v>
+        <v>0.1235542469982465</v>
       </c>
       <c r="T47">
-        <v>1.115481828459408</v>
+        <v>1.131419034493008</v>
       </c>
       <c r="U47">
         <v>0.07065748822216711</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.01723559650318</v>
+        <v>10.77773047484007</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08784588235748107</v>
+        <v>0.08767200045663828</v>
       </c>
       <c r="C48">
-        <v>3465.507818355123</v>
+        <v>3406.721512877552</v>
       </c>
       <c r="D48">
-        <v>5596.729818355123</v>
+        <v>5600.900512877553</v>
       </c>
       <c r="E48">
-        <v>-34.3779999999997</v>
+        <v>28.57900000000063</v>
       </c>
       <c r="F48">
-        <v>2896.022</v>
+        <v>2958.979000000001</v>
       </c>
       <c r="G48">
         <v>764.8</v>
@@ -5342,28 +5342,28 @@
         <v>2205.4</v>
       </c>
       <c r="M48">
-        <v>204.6256403561369</v>
+        <v>209.0740238421399</v>
       </c>
       <c r="N48">
-        <v>2000.774359643863</v>
+        <v>1996.32597615786</v>
       </c>
       <c r="O48">
-        <v>700.2710258753519</v>
+        <v>698.7140916552509</v>
       </c>
       <c r="P48">
-        <v>1300.503333768511</v>
+        <v>1297.611884502609</v>
       </c>
       <c r="Q48">
-        <v>1437.303333768511</v>
+        <v>1434.411884502609</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1235542469982465</v>
+        <v>0.1246908260467287</v>
       </c>
       <c r="T48">
-        <v>1.131419034493008</v>
+        <v>1.147957644527875</v>
       </c>
       <c r="U48">
         <v>0.07065748822216711</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.77773047484007</v>
+        <v>10.54841706048177</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08767200045663828</v>
+        <v>0.08749811855579551</v>
       </c>
       <c r="C49">
-        <v>3406.721512877552</v>
+        <v>3347.941428055827</v>
       </c>
       <c r="D49">
-        <v>5600.900512877553</v>
+        <v>5605.077428055827</v>
       </c>
       <c r="E49">
-        <v>28.57900000000063</v>
+        <v>91.53600000000051</v>
       </c>
       <c r="F49">
-        <v>2958.979000000001</v>
+        <v>3021.936000000001</v>
       </c>
       <c r="G49">
         <v>764.8</v>
@@ -5424,28 +5424,28 @@
         <v>2205.4</v>
       </c>
       <c r="M49">
-        <v>209.0740238421399</v>
+        <v>213.5224073281428</v>
       </c>
       <c r="N49">
-        <v>1996.32597615786</v>
+        <v>1991.877592671857</v>
       </c>
       <c r="O49">
-        <v>698.7140916552509</v>
+        <v>697.1571574351498</v>
       </c>
       <c r="P49">
-        <v>1297.611884502609</v>
+        <v>1294.720435236707</v>
       </c>
       <c r="Q49">
-        <v>1434.411884502609</v>
+        <v>1431.520435236707</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1246908260467287</v>
+        <v>0.1258711196739988</v>
       </c>
       <c r="T49">
-        <v>1.147957644527875</v>
+        <v>1.165132354948699</v>
       </c>
       <c r="U49">
         <v>0.07065748822216711</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.54841706048177</v>
+        <v>10.32865837172173</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08749811855579551</v>
+        <v>0.0873242366549527</v>
       </c>
       <c r="C50">
-        <v>3347.941428055827</v>
+        <v>3289.167577817642</v>
       </c>
       <c r="D50">
-        <v>5605.077428055827</v>
+        <v>5609.260577817642</v>
       </c>
       <c r="E50">
-        <v>91.53600000000006</v>
+        <v>154.4930000000004</v>
       </c>
       <c r="F50">
-        <v>3021.936</v>
+        <v>3084.893</v>
       </c>
       <c r="G50">
         <v>764.8</v>
@@ -5506,28 +5506,28 @@
         <v>2205.4</v>
       </c>
       <c r="M50">
-        <v>213.5224073281428</v>
+        <v>217.9707908141458</v>
       </c>
       <c r="N50">
-        <v>1991.877592671857</v>
+        <v>1987.429209185854</v>
       </c>
       <c r="O50">
-        <v>697.1571574351498</v>
+        <v>695.6002232150488</v>
       </c>
       <c r="P50">
-        <v>1294.720435236707</v>
+        <v>1291.828985970805</v>
       </c>
       <c r="Q50">
-        <v>1431.520435236707</v>
+        <v>1428.628985970805</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1258711196739988</v>
+        <v>0.1270976993258676</v>
       </c>
       <c r="T50">
-        <v>1.165132354948699</v>
+        <v>1.182980583425241</v>
       </c>
       <c r="U50">
         <v>0.07065748822216711</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.32865837172173</v>
+        <v>10.11786942536006</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0873242366549527</v>
+        <v>0.08715035475410993</v>
       </c>
       <c r="C51">
-        <v>3289.167577817642</v>
+        <v>3230.399976132297</v>
       </c>
       <c r="D51">
-        <v>5609.260577817642</v>
+        <v>5613.449976132297</v>
       </c>
       <c r="E51">
-        <v>154.4930000000004</v>
+        <v>217.4500000000003</v>
       </c>
       <c r="F51">
-        <v>3084.893</v>
+        <v>3147.85</v>
       </c>
       <c r="G51">
         <v>764.8</v>
@@ -5588,28 +5588,28 @@
         <v>2205.4</v>
       </c>
       <c r="M51">
-        <v>217.9707908141458</v>
+        <v>222.4191743001488</v>
       </c>
       <c r="N51">
-        <v>1987.429209185854</v>
+        <v>1982.980825699851</v>
       </c>
       <c r="O51">
-        <v>695.6002232150488</v>
+        <v>694.0432889949477</v>
       </c>
       <c r="P51">
-        <v>1291.828985970805</v>
+        <v>1288.937536704903</v>
       </c>
       <c r="Q51">
-        <v>1428.628985970805</v>
+        <v>1425.737536704903</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1270976993258676</v>
+        <v>0.1283733421638112</v>
       </c>
       <c r="T51">
-        <v>1.182980583425241</v>
+        <v>1.201542741040846</v>
       </c>
       <c r="U51">
         <v>0.07065748822216711</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.11786942536006</v>
+        <v>9.91551203685286</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08715035475410993</v>
+        <v>0.08754002285326715</v>
       </c>
       <c r="C52">
-        <v>3230.399976132297</v>
+        <v>3158.063251627013</v>
       </c>
       <c r="D52">
-        <v>5613.449976132297</v>
+        <v>5604.070251627013</v>
       </c>
       <c r="E52">
-        <v>217.4500000000003</v>
+        <v>280.4070000000002</v>
       </c>
       <c r="F52">
-        <v>3147.85</v>
+        <v>3210.807</v>
       </c>
       <c r="G52">
         <v>764.8</v>
@@ -5670,45 +5670,45 @@
         <v>2205.4</v>
       </c>
       <c r="M52">
-        <v>222.4191743001488</v>
+        <v>232.3259296861517</v>
       </c>
       <c r="N52">
-        <v>1982.980825699851</v>
+        <v>1973.074070313848</v>
       </c>
       <c r="O52">
-        <v>694.0432889949477</v>
+        <v>690.5759246098468</v>
       </c>
       <c r="P52">
-        <v>1288.937536704903</v>
+        <v>1282.498145704001</v>
       </c>
       <c r="Q52">
-        <v>1425.737536704903</v>
+        <v>1419.298145704001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1283733421638112</v>
+        <v>0.1297010520563648</v>
       </c>
       <c r="T52">
-        <v>1.201542741040846</v>
+        <v>1.220862537742801</v>
       </c>
       <c r="U52">
-        <v>0.07065748822216711</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V52">
         <v>0.35</v>
       </c>
       <c r="W52">
-        <v>0.04592736734440862</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>9.91551203685286</v>
+        <v>9.492698481737559</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08754002285326715</v>
+        <v>0.08737719095242436</v>
       </c>
       <c r="C53">
-        <v>3158.063251627013</v>
+        <v>3099.021973025047</v>
       </c>
       <c r="D53">
-        <v>5604.070251627013</v>
+        <v>5607.985973025047</v>
       </c>
       <c r="E53">
-        <v>280.4070000000002</v>
+        <v>343.3640000000005</v>
       </c>
       <c r="F53">
-        <v>3210.807</v>
+        <v>3273.764000000001</v>
       </c>
       <c r="G53">
         <v>764.8</v>
@@ -5752,28 +5752,28 @@
         <v>2205.4</v>
       </c>
       <c r="M53">
-        <v>232.3259296861517</v>
+        <v>236.8813400721548</v>
       </c>
       <c r="N53">
-        <v>1973.074070313848</v>
+        <v>1968.518659927845</v>
       </c>
       <c r="O53">
-        <v>690.5759246098468</v>
+        <v>688.9815309747457</v>
       </c>
       <c r="P53">
-        <v>1282.498145704001</v>
+        <v>1279.537128953099</v>
       </c>
       <c r="Q53">
-        <v>1419.298145704001</v>
+        <v>1416.337128953099</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1297010520563648</v>
+        <v>0.1310840831944414</v>
       </c>
       <c r="T53">
-        <v>1.220862537742801</v>
+        <v>1.240987325974005</v>
       </c>
       <c r="U53">
         <v>0.07235748822216712</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.492698481737559</v>
+        <v>9.310146587857989</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08737719095242436</v>
+        <v>0.08721435905158158</v>
       </c>
       <c r="C54">
-        <v>3099.021973025047</v>
+        <v>3039.986170298426</v>
       </c>
       <c r="D54">
-        <v>5607.985973025047</v>
+        <v>5611.907170298427</v>
       </c>
       <c r="E54">
-        <v>343.3640000000005</v>
+        <v>406.3210000000004</v>
       </c>
       <c r="F54">
-        <v>3273.764000000001</v>
+        <v>3336.721</v>
       </c>
       <c r="G54">
         <v>764.8</v>
@@ -5834,28 +5834,28 @@
         <v>2205.4</v>
       </c>
       <c r="M54">
-        <v>236.8813400721548</v>
+        <v>241.4367504581577</v>
       </c>
       <c r="N54">
-        <v>1968.518659927845</v>
+        <v>1963.963249541842</v>
       </c>
       <c r="O54">
-        <v>688.9815309747457</v>
+        <v>687.3871373396446</v>
       </c>
       <c r="P54">
-        <v>1279.537128953099</v>
+        <v>1276.576112202197</v>
       </c>
       <c r="Q54">
-        <v>1416.337128953099</v>
+        <v>1413.376112202197</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1310840831944414</v>
+        <v>0.1325259667213723</v>
       </c>
       <c r="T54">
-        <v>1.240987325974005</v>
+        <v>1.261968488172494</v>
       </c>
       <c r="U54">
         <v>0.07235748822216712</v>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.310146587857989</v>
+        <v>9.134483444690858</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08721435905158158</v>
+        <v>0.08705152715073879</v>
       </c>
       <c r="C55">
-        <v>3039.986170298426</v>
+        <v>2980.955854941662</v>
       </c>
       <c r="D55">
-        <v>5611.907170298427</v>
+        <v>5615.833854941662</v>
       </c>
       <c r="E55">
-        <v>406.3210000000004</v>
+        <v>469.2780000000007</v>
       </c>
       <c r="F55">
-        <v>3336.721</v>
+        <v>3399.678000000001</v>
       </c>
       <c r="G55">
         <v>764.8</v>
@@ -5916,28 +5916,28 @@
         <v>2205.4</v>
       </c>
       <c r="M55">
-        <v>241.4367504581577</v>
+        <v>245.9921608441607</v>
       </c>
       <c r="N55">
-        <v>1963.963249541842</v>
+        <v>1959.407839155839</v>
       </c>
       <c r="O55">
-        <v>687.3871373396446</v>
+        <v>685.7927437045436</v>
       </c>
       <c r="P55">
-        <v>1276.576112202197</v>
+        <v>1273.615095451295</v>
       </c>
       <c r="Q55">
-        <v>1413.376112202197</v>
+        <v>1410.415095451295</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1325259667213723</v>
+        <v>0.1340305408364307</v>
       </c>
       <c r="T55">
-        <v>1.261968488172494</v>
+        <v>1.283861874814395</v>
       </c>
       <c r="U55">
         <v>0.07235748822216712</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>9.134483444690858</v>
+        <v>8.96532634386325</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08705152715073879</v>
+        <v>0.08688869524989601</v>
       </c>
       <c r="C56">
-        <v>2980.955854941662</v>
+        <v>2921.931038481451</v>
       </c>
       <c r="D56">
-        <v>5615.833854941662</v>
+        <v>5619.766038481452</v>
       </c>
       <c r="E56">
-        <v>469.2780000000007</v>
+        <v>532.2350000000006</v>
       </c>
       <c r="F56">
-        <v>3399.678000000001</v>
+        <v>3462.635000000001</v>
       </c>
       <c r="G56">
         <v>764.8</v>
@@ -5998,28 +5998,28 @@
         <v>2205.4</v>
       </c>
       <c r="M56">
-        <v>245.9921608441607</v>
+        <v>250.5475712301637</v>
       </c>
       <c r="N56">
-        <v>1959.407839155839</v>
+        <v>1954.852428769836</v>
       </c>
       <c r="O56">
-        <v>685.7927437045436</v>
+        <v>684.1983500694425</v>
       </c>
       <c r="P56">
-        <v>1273.615095451295</v>
+        <v>1270.654078700393</v>
       </c>
       <c r="Q56">
-        <v>1410.415095451295</v>
+        <v>1407.454078700393</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1340305408364307</v>
+        <v>0.1356019849121584</v>
       </c>
       <c r="T56">
-        <v>1.283861874814395</v>
+        <v>1.306728300862603</v>
       </c>
       <c r="U56">
         <v>0.07235748822216712</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.96532634386325</v>
+        <v>8.802320410338464</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08688869524989601</v>
+        <v>0.0867258633490532</v>
       </c>
       <c r="C57">
-        <v>2921.931038481451</v>
+        <v>2862.911732476804</v>
       </c>
       <c r="D57">
-        <v>5619.766038481452</v>
+        <v>5623.703732476804</v>
       </c>
       <c r="E57">
-        <v>532.2350000000006</v>
+        <v>595.1920000000005</v>
       </c>
       <c r="F57">
-        <v>3462.635000000001</v>
+        <v>3525.592000000001</v>
       </c>
       <c r="G57">
         <v>764.8</v>
@@ -6080,28 +6080,28 @@
         <v>2205.4</v>
       </c>
       <c r="M57">
-        <v>250.5475712301637</v>
+        <v>255.1029816161667</v>
       </c>
       <c r="N57">
-        <v>1954.852428769836</v>
+        <v>1950.297018383833</v>
       </c>
       <c r="O57">
-        <v>684.1983500694425</v>
+        <v>682.6039564343415</v>
       </c>
       <c r="P57">
-        <v>1270.654078700393</v>
+        <v>1267.693061949491</v>
       </c>
       <c r="Q57">
-        <v>1407.454078700393</v>
+        <v>1404.493061949491</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1356019849121584</v>
+        <v>0.1372448582640554</v>
       </c>
       <c r="T57">
-        <v>1.306728300862603</v>
+        <v>1.330634109913003</v>
       </c>
       <c r="U57">
         <v>0.07235748822216712</v>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.802320410338464</v>
+        <v>8.645136117296705</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0867258633490532</v>
+        <v>0.08656303144821043</v>
       </c>
       <c r="C58">
-        <v>2862.911732476804</v>
+        <v>2803.897948519146</v>
       </c>
       <c r="D58">
-        <v>5623.703732476804</v>
+        <v>5627.646948519146</v>
       </c>
       <c r="E58">
-        <v>595.1920000000005</v>
+        <v>658.1490000000008</v>
       </c>
       <c r="F58">
-        <v>3525.592000000001</v>
+        <v>3588.549000000001</v>
       </c>
       <c r="G58">
         <v>764.8</v>
@@ -6162,28 +6162,28 @@
         <v>2205.4</v>
       </c>
       <c r="M58">
-        <v>255.1029816161667</v>
+        <v>259.6583920021696</v>
       </c>
       <c r="N58">
-        <v>1950.297018383833</v>
+        <v>1945.74160799783</v>
       </c>
       <c r="O58">
-        <v>682.6039564343415</v>
+        <v>681.0095627992405</v>
       </c>
       <c r="P58">
-        <v>1267.693061949491</v>
+        <v>1264.73204519859</v>
       </c>
       <c r="Q58">
-        <v>1404.493061949491</v>
+        <v>1401.532045198589</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1372448582640554</v>
+        <v>0.1389641443299942</v>
       </c>
       <c r="T58">
-        <v>1.330634109913003</v>
+        <v>1.35565181705877</v>
       </c>
       <c r="U58">
         <v>0.07235748822216712</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.645136117296705</v>
+        <v>8.493467062607287</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08656303144821043</v>
+        <v>0.08640019954736763</v>
       </c>
       <c r="C59">
-        <v>2803.897948519146</v>
+        <v>2744.889698232438</v>
       </c>
       <c r="D59">
-        <v>5627.646948519146</v>
+        <v>5631.595698232439</v>
       </c>
       <c r="E59">
-        <v>658.1490000000008</v>
+        <v>721.1060000000007</v>
       </c>
       <c r="F59">
-        <v>3588.549000000001</v>
+        <v>3651.506000000001</v>
       </c>
       <c r="G59">
         <v>764.8</v>
@@ -6244,28 +6244,28 @@
         <v>2205.4</v>
       </c>
       <c r="M59">
-        <v>259.6583920021696</v>
+        <v>264.2138023881726</v>
       </c>
       <c r="N59">
-        <v>1945.74160799783</v>
+        <v>1941.186197611827</v>
       </c>
       <c r="O59">
-        <v>681.0095627992405</v>
+        <v>679.4151691641395</v>
       </c>
       <c r="P59">
-        <v>1264.73204519859</v>
+        <v>1261.771028447688</v>
       </c>
       <c r="Q59">
-        <v>1401.532045198589</v>
+        <v>1398.571028447687</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1389641443299942</v>
+        <v>0.1407653011609777</v>
       </c>
       <c r="T59">
-        <v>1.35565181705877</v>
+        <v>1.38186084359243</v>
       </c>
       <c r="U59">
         <v>0.07235748822216712</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.493467062607287</v>
+        <v>8.347027975320955</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08640019954736763</v>
+        <v>0.08623736764652484</v>
       </c>
       <c r="C60">
-        <v>2744.889698232439</v>
+        <v>2685.886993273287</v>
       </c>
       <c r="D60">
-        <v>5631.595698232439</v>
+        <v>5635.549993273287</v>
       </c>
       <c r="E60">
-        <v>721.1060000000002</v>
+        <v>784.0630000000001</v>
       </c>
       <c r="F60">
-        <v>3651.506</v>
+        <v>3714.463</v>
       </c>
       <c r="G60">
         <v>764.8</v>
@@ -6326,28 +6326,28 @@
         <v>2205.4</v>
       </c>
       <c r="M60">
-        <v>264.2138023881726</v>
+        <v>268.7692127741756</v>
       </c>
       <c r="N60">
-        <v>1941.186197611827</v>
+        <v>1936.630787225824</v>
       </c>
       <c r="O60">
-        <v>679.4151691641395</v>
+        <v>677.8207755290383</v>
       </c>
       <c r="P60">
-        <v>1261.771028447688</v>
+        <v>1258.810011696786</v>
       </c>
       <c r="Q60">
-        <v>1398.571028447687</v>
+        <v>1395.610011696786</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1407653011609777</v>
+        <v>0.1426543193007896</v>
       </c>
       <c r="T60">
-        <v>1.38186084359243</v>
+        <v>1.409348359225293</v>
       </c>
       <c r="U60">
         <v>0.07235748822216712</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.347027975320959</v>
+        <v>8.205552924891787</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08623736764652484</v>
+        <v>0.08607453574568207</v>
       </c>
       <c r="C61">
-        <v>2685.886993273287</v>
+        <v>2626.889845331064</v>
       </c>
       <c r="D61">
-        <v>5635.549993273287</v>
+        <v>5639.509845331064</v>
       </c>
       <c r="E61">
-        <v>784.0630000000001</v>
+        <v>847.02</v>
       </c>
       <c r="F61">
-        <v>3714.463</v>
+        <v>3777.42</v>
       </c>
       <c r="G61">
         <v>764.8</v>
@@ -6408,28 +6408,28 @@
         <v>2205.4</v>
       </c>
       <c r="M61">
-        <v>268.7692127741756</v>
+        <v>273.3246231601785</v>
       </c>
       <c r="N61">
-        <v>1936.630787225824</v>
+        <v>1932.075376839821</v>
       </c>
       <c r="O61">
-        <v>677.8207755290383</v>
+        <v>676.2263818939373</v>
       </c>
       <c r="P61">
-        <v>1258.810011696786</v>
+        <v>1255.848994945884</v>
       </c>
       <c r="Q61">
-        <v>1395.610011696786</v>
+        <v>1392.648994945884</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1426543193007896</v>
+        <v>0.1446377883475922</v>
       </c>
       <c r="T61">
-        <v>1.409348359225293</v>
+        <v>1.4382102506398</v>
       </c>
       <c r="U61">
         <v>0.07235748822216712</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.205552924891787</v>
+        <v>8.068793709476925</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08607453574568207</v>
+        <v>0.08591170384483929</v>
       </c>
       <c r="C62">
-        <v>2626.889845331064</v>
+        <v>2567.898266128015</v>
       </c>
       <c r="D62">
-        <v>5639.509845331064</v>
+        <v>5643.475266128015</v>
       </c>
       <c r="E62">
-        <v>847.02</v>
+        <v>909.9770000000003</v>
       </c>
       <c r="F62">
-        <v>3777.42</v>
+        <v>3840.377</v>
       </c>
       <c r="G62">
         <v>764.8</v>
@@ -6490,28 +6490,28 @@
         <v>2205.4</v>
       </c>
       <c r="M62">
-        <v>273.3246231601785</v>
+        <v>277.8800335461815</v>
       </c>
       <c r="N62">
-        <v>1932.075376839821</v>
+        <v>1927.519966453818</v>
       </c>
       <c r="O62">
-        <v>676.2263818939373</v>
+        <v>674.6319882588363</v>
       </c>
       <c r="P62">
-        <v>1255.848994945884</v>
+        <v>1252.887978194982</v>
       </c>
       <c r="Q62">
-        <v>1392.648994945884</v>
+        <v>1389.687978194982</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1446377883475922</v>
+        <v>0.1467229737557693</v>
       </c>
       <c r="T62">
-        <v>1.4382102506398</v>
+        <v>1.468552239049923</v>
       </c>
       <c r="U62">
         <v>0.07235748822216712</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.068793709476925</v>
+        <v>7.93651840276419</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08591170384483929</v>
+        <v>0.0857488719439965</v>
       </c>
       <c r="C63">
-        <v>2567.898266128015</v>
+        <v>2508.912267419384</v>
       </c>
       <c r="D63">
-        <v>5643.475266128015</v>
+        <v>5647.446267419384</v>
       </c>
       <c r="E63">
-        <v>909.9770000000003</v>
+        <v>972.9340000000002</v>
       </c>
       <c r="F63">
-        <v>3840.377</v>
+        <v>3903.334</v>
       </c>
       <c r="G63">
         <v>764.8</v>
@@ -6572,28 +6572,28 @@
         <v>2205.4</v>
       </c>
       <c r="M63">
-        <v>277.8800335461815</v>
+        <v>282.4354439321845</v>
       </c>
       <c r="N63">
-        <v>1927.519966453818</v>
+        <v>1922.964556067815</v>
       </c>
       <c r="O63">
-        <v>674.6319882588363</v>
+        <v>673.0375946237353</v>
       </c>
       <c r="P63">
-        <v>1252.887978194982</v>
+        <v>1249.92696144408</v>
       </c>
       <c r="Q63">
-        <v>1389.687978194982</v>
+        <v>1386.72696144408</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1467229737557693</v>
+        <v>0.1489179057643767</v>
       </c>
       <c r="T63">
-        <v>1.468552239049923</v>
+        <v>1.500491174218473</v>
       </c>
       <c r="U63">
         <v>0.07235748822216712</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.93651840276419</v>
+        <v>7.808510041429283</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0857488719439965</v>
+        <v>0.0855860400431537</v>
       </c>
       <c r="C64">
-        <v>2508.912267419384</v>
+        <v>2449.931860993518</v>
       </c>
       <c r="D64">
-        <v>5647.446267419384</v>
+        <v>5651.422860993518</v>
       </c>
       <c r="E64">
-        <v>972.9340000000002</v>
+        <v>1035.891000000001</v>
       </c>
       <c r="F64">
-        <v>3903.334</v>
+        <v>3966.291000000001</v>
       </c>
       <c r="G64">
         <v>764.8</v>
@@ -6654,28 +6654,28 @@
         <v>2205.4</v>
       </c>
       <c r="M64">
-        <v>282.4354439321845</v>
+        <v>286.9908543181875</v>
       </c>
       <c r="N64">
-        <v>1922.964556067815</v>
+        <v>1918.409145681812</v>
       </c>
       <c r="O64">
-        <v>673.0375946237353</v>
+        <v>671.4432009886342</v>
       </c>
       <c r="P64">
-        <v>1249.92696144408</v>
+        <v>1246.965944693178</v>
       </c>
       <c r="Q64">
-        <v>1386.72696144408</v>
+        <v>1383.765944693178</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1489179057643767</v>
+        <v>0.1512314827464223</v>
       </c>
       <c r="T64">
-        <v>1.500491174218473</v>
+        <v>1.534156538315052</v>
       </c>
       <c r="U64">
         <v>0.07235748822216712</v>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.808510041429283</v>
+        <v>7.684565437597071</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0855860400431537</v>
+        <v>0.08575600814231092</v>
       </c>
       <c r="C65">
-        <v>2449.931860993518</v>
+        <v>2382.82411900071</v>
       </c>
       <c r="D65">
-        <v>5651.422860993518</v>
+        <v>5647.272119000711</v>
       </c>
       <c r="E65">
-        <v>1035.891000000001</v>
+        <v>1098.848</v>
       </c>
       <c r="F65">
-        <v>3966.291000000001</v>
+        <v>4029.248000000001</v>
       </c>
       <c r="G65">
         <v>764.8</v>
@@ -6736,45 +6736,45 @@
         <v>2205.4</v>
       </c>
       <c r="M65">
-        <v>286.9908543181875</v>
+        <v>294.7696631041904</v>
       </c>
       <c r="N65">
-        <v>1918.409145681812</v>
+        <v>1910.630336895809</v>
       </c>
       <c r="O65">
-        <v>671.4432009886342</v>
+        <v>668.7206179135331</v>
       </c>
       <c r="P65">
-        <v>1246.965944693178</v>
+        <v>1241.909718982276</v>
       </c>
       <c r="Q65">
-        <v>1383.765944693178</v>
+        <v>1378.709718982276</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1512314827464223</v>
+        <v>0.1536735917830261</v>
       </c>
       <c r="T65">
-        <v>1.534156538315052</v>
+        <v>1.569692200416997</v>
       </c>
       <c r="U65">
-        <v>0.07235748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V65">
         <v>0.35</v>
       </c>
       <c r="W65">
-        <v>0.04703236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y65">
-        <v>7.684565437597071</v>
+        <v>7.48177399524479</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08575600814231092</v>
+        <v>0.08559837624146814</v>
       </c>
       <c r="C66">
-        <v>2382.82411900071</v>
+        <v>2323.716396904586</v>
       </c>
       <c r="D66">
-        <v>5647.272119000711</v>
+        <v>5651.121396904587</v>
       </c>
       <c r="E66">
-        <v>1098.848</v>
+        <v>1161.805000000001</v>
       </c>
       <c r="F66">
-        <v>4029.248000000001</v>
+        <v>4092.205000000001</v>
       </c>
       <c r="G66">
         <v>764.8</v>
@@ -6818,28 +6818,28 @@
         <v>2205.4</v>
       </c>
       <c r="M66">
-        <v>294.7696631041904</v>
+        <v>299.3754390901934</v>
       </c>
       <c r="N66">
-        <v>1910.630336895809</v>
+        <v>1906.024560909806</v>
       </c>
       <c r="O66">
-        <v>668.7206179135331</v>
+        <v>667.1085963184322</v>
       </c>
       <c r="P66">
-        <v>1241.909718982276</v>
+        <v>1238.915964591374</v>
       </c>
       <c r="Q66">
-        <v>1378.709718982276</v>
+        <v>1375.715964591374</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1536735917830261</v>
+        <v>0.1562552499074358</v>
       </c>
       <c r="T66">
-        <v>1.569692200416997</v>
+        <v>1.607258471781911</v>
       </c>
       <c r="U66">
         <v>0.07315748822216711</v>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.48177399524479</v>
+        <v>7.366669779933331</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08559837624146814</v>
+        <v>0.08544074434062535</v>
       </c>
       <c r="C67">
-        <v>2323.716396904586</v>
+        <v>2264.613925855851</v>
       </c>
       <c r="D67">
-        <v>5651.121396904587</v>
+        <v>5654.975925855851</v>
       </c>
       <c r="E67">
-        <v>1161.805000000001</v>
+        <v>1224.762</v>
       </c>
       <c r="F67">
-        <v>4092.205000000001</v>
+        <v>4155.162</v>
       </c>
       <c r="G67">
         <v>764.8</v>
@@ -6900,28 +6900,28 @@
         <v>2205.4</v>
       </c>
       <c r="M67">
-        <v>299.3754390901934</v>
+        <v>303.9812150761963</v>
       </c>
       <c r="N67">
-        <v>1906.024560909806</v>
+        <v>1901.418784923803</v>
       </c>
       <c r="O67">
-        <v>667.1085963184322</v>
+        <v>665.4965747233312</v>
       </c>
       <c r="P67">
-        <v>1238.915964591374</v>
+        <v>1235.922210200472</v>
       </c>
       <c r="Q67">
-        <v>1375.715964591374</v>
+        <v>1372.722210200472</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1562552499074358</v>
+        <v>0.1589887702744578</v>
       </c>
       <c r="T67">
-        <v>1.607258471781911</v>
+        <v>1.647034523815348</v>
       </c>
       <c r="U67">
         <v>0.07315748822216711</v>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.366669779933331</v>
+        <v>7.255053571146464</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08544074434062535</v>
+        <v>0.08528311243978257</v>
       </c>
       <c r="C68">
-        <v>2264.613925855851</v>
+        <v>2205.51671660677</v>
       </c>
       <c r="D68">
-        <v>5654.975925855851</v>
+        <v>5658.835716606771</v>
       </c>
       <c r="E68">
-        <v>1224.762</v>
+        <v>1287.719000000001</v>
       </c>
       <c r="F68">
-        <v>4155.162</v>
+        <v>4218.119000000001</v>
       </c>
       <c r="G68">
         <v>764.8</v>
@@ -6982,28 +6982,28 @@
         <v>2205.4</v>
       </c>
       <c r="M68">
-        <v>303.9812150761963</v>
+        <v>308.5869910621993</v>
       </c>
       <c r="N68">
-        <v>1901.418784923803</v>
+        <v>1896.8130089378</v>
       </c>
       <c r="O68">
-        <v>665.4965747233312</v>
+        <v>663.8845531282301</v>
       </c>
       <c r="P68">
-        <v>1235.922210200472</v>
+        <v>1232.92845580957</v>
       </c>
       <c r="Q68">
-        <v>1372.722210200472</v>
+        <v>1369.72845580957</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1589887702744578</v>
+        <v>0.1618879585425115</v>
       </c>
       <c r="T68">
-        <v>1.647034523815348</v>
+        <v>1.689221245668995</v>
       </c>
       <c r="U68">
         <v>0.07315748822216711</v>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.255053571146464</v>
+        <v>7.146769189487562</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08528311243978257</v>
+        <v>0.08512548053893979</v>
       </c>
       <c r="C69">
-        <v>2205.51671660677</v>
+        <v>2146.424779938995</v>
       </c>
       <c r="D69">
-        <v>5658.835716606771</v>
+        <v>5662.700779938996</v>
       </c>
       <c r="E69">
-        <v>1287.719000000001</v>
+        <v>1350.676000000001</v>
       </c>
       <c r="F69">
-        <v>4218.119000000001</v>
+        <v>4281.076000000001</v>
       </c>
       <c r="G69">
         <v>764.8</v>
@@ -7064,28 +7064,28 @@
         <v>2205.4</v>
       </c>
       <c r="M69">
-        <v>308.5869910621993</v>
+        <v>313.1927670482024</v>
       </c>
       <c r="N69">
-        <v>1896.8130089378</v>
+        <v>1892.207232951797</v>
       </c>
       <c r="O69">
-        <v>663.8845531282301</v>
+        <v>662.272531533129</v>
       </c>
       <c r="P69">
-        <v>1232.92845580957</v>
+        <v>1229.934701418668</v>
       </c>
       <c r="Q69">
-        <v>1369.72845580957</v>
+        <v>1366.734701418668</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1618879585425115</v>
+        <v>0.1649683460773185</v>
       </c>
       <c r="T69">
-        <v>1.689221245668995</v>
+        <v>1.734044637638494</v>
       </c>
       <c r="U69">
         <v>0.07315748822216711</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.146769189487562</v>
+        <v>7.041669642583331</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08512548053893979</v>
+        <v>0.08496784863809698</v>
       </c>
       <c r="C70">
-        <v>2146.424779938995</v>
+        <v>2087.338126663647</v>
       </c>
       <c r="D70">
-        <v>5662.700779938996</v>
+        <v>5666.571126663648</v>
       </c>
       <c r="E70">
-        <v>1350.676000000001</v>
+        <v>1413.633000000001</v>
       </c>
       <c r="F70">
-        <v>4281.076000000001</v>
+        <v>4344.033000000001</v>
       </c>
       <c r="G70">
         <v>764.8</v>
@@ -7146,28 +7146,28 @@
         <v>2205.4</v>
       </c>
       <c r="M70">
-        <v>313.1927670482024</v>
+        <v>317.7985430342054</v>
       </c>
       <c r="N70">
-        <v>1892.207232951797</v>
+        <v>1887.601456965794</v>
       </c>
       <c r="O70">
-        <v>662.272531533129</v>
+        <v>660.660509938028</v>
       </c>
       <c r="P70">
-        <v>1229.934701418668</v>
+        <v>1226.940947027766</v>
       </c>
       <c r="Q70">
-        <v>1366.734701418668</v>
+        <v>1363.740947027766</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1649683460773185</v>
+        <v>0.1682474682917905</v>
       </c>
       <c r="T70">
-        <v>1.734044637638494</v>
+        <v>1.78175986134796</v>
       </c>
       <c r="U70">
         <v>0.07315748822216711</v>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.041669642583331</v>
+        <v>6.939616459357485</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08496784863809698</v>
+        <v>0.08481021673725421</v>
       </c>
       <c r="C71">
-        <v>2087.338126663647</v>
+        <v>2028.256767621426</v>
       </c>
       <c r="D71">
-        <v>5666.571126663648</v>
+        <v>5670.446767621426</v>
       </c>
       <c r="E71">
-        <v>1413.633000000001</v>
+        <v>1476.590000000001</v>
       </c>
       <c r="F71">
-        <v>4344.033000000001</v>
+        <v>4406.990000000001</v>
       </c>
       <c r="G71">
         <v>764.8</v>
@@ -7228,28 +7228,28 @@
         <v>2205.4</v>
       </c>
       <c r="M71">
-        <v>317.7985430342054</v>
+        <v>322.4043190202083</v>
       </c>
       <c r="N71">
-        <v>1887.601456965794</v>
+        <v>1882.995680979791</v>
       </c>
       <c r="O71">
-        <v>660.660509938028</v>
+        <v>659.0484883429269</v>
       </c>
       <c r="P71">
-        <v>1226.940947027766</v>
+        <v>1223.947192636864</v>
       </c>
       <c r="Q71">
-        <v>1363.740947027766</v>
+        <v>1360.747192636864</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1682474682917905</v>
+        <v>0.1717451986538939</v>
       </c>
       <c r="T71">
-        <v>1.78175986134796</v>
+        <v>1.832656099971391</v>
       </c>
       <c r="U71">
         <v>0.07315748822216711</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.939616459357485</v>
+        <v>6.840479081366666</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08481021673725421</v>
+        <v>0.08465258483641142</v>
       </c>
       <c r="C72">
-        <v>2028.256767621426</v>
+        <v>1969.180713682709</v>
       </c>
       <c r="D72">
-        <v>5670.446767621426</v>
+        <v>5674.32771368271</v>
       </c>
       <c r="E72">
-        <v>1476.590000000001</v>
+        <v>1539.547000000001</v>
       </c>
       <c r="F72">
-        <v>4406.990000000001</v>
+        <v>4469.947000000001</v>
       </c>
       <c r="G72">
         <v>764.8</v>
@@ -7310,28 +7310,28 @@
         <v>2205.4</v>
       </c>
       <c r="M72">
-        <v>322.4043190202083</v>
+        <v>327.0100950062113</v>
       </c>
       <c r="N72">
-        <v>1882.995680979791</v>
+        <v>1878.389904993788</v>
       </c>
       <c r="O72">
-        <v>659.0484883429269</v>
+        <v>657.4364667478259</v>
       </c>
       <c r="P72">
-        <v>1223.947192636864</v>
+        <v>1220.953438245962</v>
       </c>
       <c r="Q72">
-        <v>1360.747192636864</v>
+        <v>1357.753438245962</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1717451986538939</v>
+        <v>0.1754841517995907</v>
       </c>
       <c r="T72">
-        <v>1.832656099971391</v>
+        <v>1.887062424017128</v>
       </c>
       <c r="U72">
         <v>0.07315748822216711</v>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.840479081366666</v>
+        <v>6.744134305572769</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08465258483641142</v>
+        <v>0.08449495293556863</v>
       </c>
       <c r="C73">
-        <v>1969.18071368271</v>
+        <v>1910.109975747656</v>
       </c>
       <c r="D73">
-        <v>5674.32771368271</v>
+        <v>5678.213975747656</v>
       </c>
       <c r="E73">
-        <v>1539.547</v>
+        <v>1602.504</v>
       </c>
       <c r="F73">
-        <v>4469.947</v>
+        <v>4532.904</v>
       </c>
       <c r="G73">
         <v>764.8</v>
@@ -7392,28 +7392,28 @@
         <v>2205.4</v>
       </c>
       <c r="M73">
-        <v>327.0100950062112</v>
+        <v>331.6158709922142</v>
       </c>
       <c r="N73">
-        <v>1878.389904993788</v>
+        <v>1873.784129007785</v>
       </c>
       <c r="O73">
-        <v>657.4364667478259</v>
+        <v>655.8244451527248</v>
       </c>
       <c r="P73">
-        <v>1220.953438245962</v>
+        <v>1217.959683855061</v>
       </c>
       <c r="Q73">
-        <v>1357.753438245962</v>
+        <v>1354.759683855061</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1754841517995907</v>
+        <v>0.1794901730271229</v>
       </c>
       <c r="T73">
-        <v>1.887062424017128</v>
+        <v>1.945354914066131</v>
       </c>
       <c r="U73">
         <v>0.07315748822216711</v>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.74413430557277</v>
+        <v>6.650465773550924</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08449495293556863</v>
+        <v>0.08433732103472584</v>
       </c>
       <c r="C74">
-        <v>1910.109975747656</v>
+        <v>1851.044564746304</v>
       </c>
       <c r="D74">
-        <v>5678.213975747656</v>
+        <v>5682.105564746304</v>
       </c>
       <c r="E74">
-        <v>1602.504</v>
+        <v>1665.461000000001</v>
       </c>
       <c r="F74">
-        <v>4532.904</v>
+        <v>4595.861000000001</v>
       </c>
       <c r="G74">
         <v>764.8</v>
@@ -7474,28 +7474,28 @@
         <v>2205.4</v>
       </c>
       <c r="M74">
-        <v>331.6158709922142</v>
+        <v>336.2216469782172</v>
       </c>
       <c r="N74">
-        <v>1873.784129007785</v>
+        <v>1869.178353021782</v>
       </c>
       <c r="O74">
-        <v>655.8244451527248</v>
+        <v>654.2124235576238</v>
       </c>
       <c r="P74">
-        <v>1217.959683855061</v>
+        <v>1214.965929464159</v>
       </c>
       <c r="Q74">
-        <v>1354.759683855061</v>
+        <v>1351.765929464159</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1794901730271229</v>
+        <v>0.1837929365678057</v>
       </c>
       <c r="T74">
-        <v>1.945354914066131</v>
+        <v>2.007965366340986</v>
       </c>
       <c r="U74">
         <v>0.07315748822216711</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.650465773550924</v>
+        <v>6.559363502680363</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08433732103472584</v>
+        <v>0.08417968913388306</v>
       </c>
       <c r="C75">
-        <v>1851.044564746304</v>
+        <v>1791.984491638678</v>
       </c>
       <c r="D75">
-        <v>5682.105564746304</v>
+        <v>5686.002491638678</v>
       </c>
       <c r="E75">
-        <v>1665.461000000001</v>
+        <v>1728.418</v>
       </c>
       <c r="F75">
-        <v>4595.861000000001</v>
+        <v>4658.818</v>
       </c>
       <c r="G75">
         <v>764.8</v>
@@ -7556,28 +7556,28 @@
         <v>2205.4</v>
       </c>
       <c r="M75">
-        <v>336.2216469782172</v>
+        <v>340.8274229642201</v>
       </c>
       <c r="N75">
-        <v>1869.178353021782</v>
+        <v>1864.572577035779</v>
       </c>
       <c r="O75">
-        <v>654.2124235576238</v>
+        <v>652.6004019625227</v>
       </c>
       <c r="P75">
-        <v>1214.965929464159</v>
+        <v>1211.972175073257</v>
       </c>
       <c r="Q75">
-        <v>1351.765929464159</v>
+        <v>1348.772175073257</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1837929365678057</v>
+        <v>0.1884266819193103</v>
       </c>
       <c r="T75">
-        <v>2.007965366340986</v>
+        <v>2.07539200725237</v>
       </c>
       <c r="U75">
         <v>0.07315748822216711</v>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.559363502680363</v>
+        <v>6.470723455346846</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08417968913388306</v>
+        <v>0.08402205723304028</v>
       </c>
       <c r="C76">
-        <v>1791.984491638678</v>
+        <v>1732.92976741489</v>
       </c>
       <c r="D76">
-        <v>5686.002491638678</v>
+        <v>5689.904767414891</v>
       </c>
       <c r="E76">
-        <v>1728.418</v>
+        <v>1791.375</v>
       </c>
       <c r="F76">
-        <v>4658.818</v>
+        <v>4721.775000000001</v>
       </c>
       <c r="G76">
         <v>764.8</v>
@@ -7638,28 +7638,28 @@
         <v>2205.4</v>
       </c>
       <c r="M76">
-        <v>340.8274229642201</v>
+        <v>345.4331989502231</v>
       </c>
       <c r="N76">
-        <v>1864.572577035779</v>
+        <v>1859.966801049776</v>
       </c>
       <c r="O76">
-        <v>652.6004019625227</v>
+        <v>650.9883803674218</v>
       </c>
       <c r="P76">
-        <v>1211.972175073257</v>
+        <v>1208.978420682355</v>
       </c>
       <c r="Q76">
-        <v>1348.772175073257</v>
+        <v>1345.778420682355</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1884266819193103</v>
+        <v>0.1934311268989352</v>
       </c>
       <c r="T76">
-        <v>2.07539200725237</v>
+        <v>2.148212779436664</v>
       </c>
       <c r="U76">
         <v>0.07315748822216711</v>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.470723455346846</v>
+        <v>6.384447142608888</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08402205723304028</v>
+        <v>0.08386442533219748</v>
       </c>
       <c r="C77">
-        <v>1732.92976741489</v>
+        <v>1673.880403095241</v>
       </c>
       <c r="D77">
-        <v>5689.904767414891</v>
+        <v>5693.812403095241</v>
       </c>
       <c r="E77">
-        <v>1791.375</v>
+        <v>1854.332000000001</v>
       </c>
       <c r="F77">
-        <v>4721.775000000001</v>
+        <v>4784.732000000001</v>
       </c>
       <c r="G77">
         <v>764.8</v>
@@ -7720,28 +7720,28 @@
         <v>2205.4</v>
       </c>
       <c r="M77">
-        <v>345.4331989502231</v>
+        <v>350.0389749362262</v>
       </c>
       <c r="N77">
-        <v>1859.966801049776</v>
+        <v>1855.361025063773</v>
       </c>
       <c r="O77">
-        <v>650.9883803674218</v>
+        <v>649.3763587723207</v>
       </c>
       <c r="P77">
-        <v>1208.978420682355</v>
+        <v>1205.984666291453</v>
       </c>
       <c r="Q77">
-        <v>1345.778420682355</v>
+        <v>1342.784666291453</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1934311268989352</v>
+        <v>0.1988526089601956</v>
       </c>
       <c r="T77">
-        <v>2.148212779436664</v>
+        <v>2.227101949302982</v>
       </c>
       <c r="U77">
         <v>0.07315748822216711</v>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.384447142608888</v>
+        <v>6.300441259153507</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08386442533219748</v>
+        <v>0.0837067934313547</v>
       </c>
       <c r="C78">
-        <v>1673.880403095241</v>
+        <v>1614.836409730327</v>
       </c>
       <c r="D78">
-        <v>5693.812403095241</v>
+        <v>5697.725409730328</v>
       </c>
       <c r="E78">
-        <v>1854.332000000001</v>
+        <v>1917.289</v>
       </c>
       <c r="F78">
-        <v>4784.732000000001</v>
+        <v>4847.689</v>
       </c>
       <c r="G78">
         <v>764.8</v>
@@ -7802,28 +7802,28 @@
         <v>2205.4</v>
       </c>
       <c r="M78">
-        <v>350.0389749362262</v>
+        <v>354.6447509222291</v>
       </c>
       <c r="N78">
-        <v>1855.361025063773</v>
+        <v>1850.75524907777</v>
       </c>
       <c r="O78">
-        <v>649.3763587723207</v>
+        <v>647.7643371772197</v>
       </c>
       <c r="P78">
-        <v>1205.984666291453</v>
+        <v>1202.990911900551</v>
       </c>
       <c r="Q78">
-        <v>1342.784666291453</v>
+        <v>1339.790911900551</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1988526089601956</v>
+        <v>0.2047455242441742</v>
       </c>
       <c r="T78">
-        <v>2.227101949302982</v>
+        <v>2.312851046983762</v>
       </c>
       <c r="U78">
         <v>0.07315748822216711</v>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.300441259153507</v>
+        <v>6.218617346696969</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0837067934313547</v>
+        <v>0.08354916153051191</v>
       </c>
       <c r="C79">
-        <v>1614.836409730327</v>
+        <v>1555.797798401145</v>
       </c>
       <c r="D79">
-        <v>5697.725409730328</v>
+        <v>5701.643798401145</v>
       </c>
       <c r="E79">
-        <v>1917.289</v>
+        <v>1980.246000000001</v>
       </c>
       <c r="F79">
-        <v>4847.689</v>
+        <v>4910.646000000001</v>
       </c>
       <c r="G79">
         <v>764.8</v>
@@ -7884,28 +7884,28 @@
         <v>2205.4</v>
       </c>
       <c r="M79">
-        <v>354.6447509222291</v>
+        <v>359.2505269082321</v>
       </c>
       <c r="N79">
-        <v>1850.75524907777</v>
+        <v>1846.149473091768</v>
       </c>
       <c r="O79">
-        <v>647.7643371772197</v>
+        <v>646.1523155821186</v>
       </c>
       <c r="P79">
-        <v>1202.990911900551</v>
+        <v>1199.997157509649</v>
       </c>
       <c r="Q79">
-        <v>1339.790911900551</v>
+        <v>1336.797157509649</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2047455242441742</v>
+        <v>0.2111741590994236</v>
       </c>
       <c r="T79">
-        <v>2.312851046983762</v>
+        <v>2.406395517180977</v>
       </c>
       <c r="U79">
         <v>0.07315748822216711</v>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.218617346696969</v>
+        <v>6.138891483277776</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08354916153051191</v>
+        <v>0.08390502962966913</v>
       </c>
       <c r="C80">
-        <v>1555.797798401145</v>
+        <v>1484.002324675789</v>
       </c>
       <c r="D80">
-        <v>5701.643798401145</v>
+        <v>5692.80532467579</v>
       </c>
       <c r="E80">
-        <v>1980.246000000001</v>
+        <v>2043.203000000001</v>
       </c>
       <c r="F80">
-        <v>4910.646000000001</v>
+        <v>4973.603000000001</v>
       </c>
       <c r="G80">
         <v>764.8</v>
@@ -7966,45 +7966,45 @@
         <v>2205.4</v>
       </c>
       <c r="M80">
-        <v>359.2505269082321</v>
+        <v>368.8299058942351</v>
       </c>
       <c r="N80">
-        <v>1846.149473091768</v>
+        <v>1836.570094105765</v>
       </c>
       <c r="O80">
-        <v>646.1523155821186</v>
+        <v>642.7995329370176</v>
       </c>
       <c r="P80">
-        <v>1199.997157509649</v>
+        <v>1193.770561168747</v>
       </c>
       <c r="Q80">
-        <v>1336.797157509649</v>
+        <v>1330.570561168747</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2111741590994236</v>
+        <v>0.2182150448932682</v>
       </c>
       <c r="T80">
-        <v>2.406395517180977</v>
+        <v>2.508848984539833</v>
       </c>
       <c r="U80">
-        <v>0.07315748822216711</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V80">
         <v>0.35</v>
       </c>
       <c r="W80">
-        <v>0.04755236734440862</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>6.138891483277776</v>
+        <v>5.979450052058457</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08390502962966913</v>
+        <v>0.08375389772882634</v>
       </c>
       <c r="C81">
-        <v>1484.002324675789</v>
+        <v>1424.795543553599</v>
       </c>
       <c r="D81">
-        <v>5692.80532467579</v>
+        <v>5696.5555435536</v>
       </c>
       <c r="E81">
-        <v>2043.203000000001</v>
+        <v>2106.160000000001</v>
       </c>
       <c r="F81">
-        <v>4973.603000000001</v>
+        <v>5036.560000000001</v>
       </c>
       <c r="G81">
         <v>764.8</v>
@@ -8048,28 +8048,28 @@
         <v>2205.4</v>
       </c>
       <c r="M81">
-        <v>368.8299058942351</v>
+        <v>373.4986388802381</v>
       </c>
       <c r="N81">
-        <v>1836.570094105765</v>
+        <v>1831.901361119762</v>
       </c>
       <c r="O81">
-        <v>642.7995329370176</v>
+        <v>641.1654763919165</v>
       </c>
       <c r="P81">
-        <v>1193.770561168747</v>
+        <v>1190.735884727845</v>
       </c>
       <c r="Q81">
-        <v>1330.570561168747</v>
+        <v>1327.535884727845</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2182150448932682</v>
+        <v>0.2259600192664973</v>
       </c>
       <c r="T81">
-        <v>2.508848984539833</v>
+        <v>2.621547798634573</v>
       </c>
       <c r="U81">
         <v>0.07415748822216711</v>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.979450052058457</v>
+        <v>5.904706926407726</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08375389772882634</v>
+        <v>0.08360276582798357</v>
       </c>
       <c r="C82">
-        <v>1424.795543553599</v>
+        <v>1365.593706711738</v>
       </c>
       <c r="D82">
-        <v>5696.5555435536</v>
+        <v>5700.310706711739</v>
       </c>
       <c r="E82">
-        <v>2106.160000000001</v>
+        <v>2169.117000000001</v>
       </c>
       <c r="F82">
-        <v>5036.560000000001</v>
+        <v>5099.517000000001</v>
       </c>
       <c r="G82">
         <v>764.8</v>
@@ -8130,28 +8130,28 @@
         <v>2205.4</v>
       </c>
       <c r="M82">
-        <v>373.4986388802381</v>
+        <v>378.167371866241</v>
       </c>
       <c r="N82">
-        <v>1831.901361119762</v>
+        <v>1827.232628133759</v>
       </c>
       <c r="O82">
-        <v>641.1654763919165</v>
+        <v>639.5314198468155</v>
       </c>
       <c r="P82">
-        <v>1190.735884727845</v>
+        <v>1187.701208286943</v>
       </c>
       <c r="Q82">
-        <v>1327.535884727845</v>
+        <v>1324.501208286943</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2259600192664973</v>
+        <v>0.2345202541000662</v>
       </c>
       <c r="T82">
-        <v>2.621547798634573</v>
+        <v>2.746109645791918</v>
       </c>
       <c r="U82">
         <v>0.07415748822216711</v>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.904706926407726</v>
+        <v>5.831809310032322</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08360276582798357</v>
+        <v>0.08345163392714076</v>
       </c>
       <c r="C83">
-        <v>1365.593706711738</v>
+        <v>1306.396823934452</v>
       </c>
       <c r="D83">
-        <v>5700.310706711739</v>
+        <v>5704.070823934453</v>
       </c>
       <c r="E83">
-        <v>2169.117000000001</v>
+        <v>2232.074000000001</v>
       </c>
       <c r="F83">
-        <v>5099.517000000001</v>
+        <v>5162.474000000001</v>
       </c>
       <c r="G83">
         <v>764.8</v>
@@ -8212,28 +8212,28 @@
         <v>2205.4</v>
       </c>
       <c r="M83">
-        <v>378.167371866241</v>
+        <v>382.836104852244</v>
       </c>
       <c r="N83">
-        <v>1827.232628133759</v>
+        <v>1822.563895147756</v>
       </c>
       <c r="O83">
-        <v>639.5314198468155</v>
+        <v>637.8973633017144</v>
       </c>
       <c r="P83">
-        <v>1187.701208286943</v>
+        <v>1184.666531846041</v>
       </c>
       <c r="Q83">
-        <v>1324.501208286943</v>
+        <v>1321.466531846041</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2345202541000662</v>
+        <v>0.244031626137365</v>
       </c>
       <c r="T83">
-        <v>2.746109645791918</v>
+        <v>2.884511698188967</v>
       </c>
       <c r="U83">
         <v>0.07415748822216711</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.831809310032322</v>
+        <v>5.76068968430022</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08345163392714076</v>
+        <v>0.08330050202629799</v>
       </c>
       <c r="C84">
-        <v>1306.396823934452</v>
+        <v>1247.204905031815</v>
       </c>
       <c r="D84">
-        <v>5704.070823934453</v>
+        <v>5707.835905031816</v>
       </c>
       <c r="E84">
-        <v>2232.074000000001</v>
+        <v>2295.031000000001</v>
       </c>
       <c r="F84">
-        <v>5162.474000000001</v>
+        <v>5225.431000000001</v>
       </c>
       <c r="G84">
         <v>764.8</v>
@@ -8294,28 +8294,28 @@
         <v>2205.4</v>
       </c>
       <c r="M84">
-        <v>382.836104852244</v>
+        <v>387.504837838247</v>
       </c>
       <c r="N84">
-        <v>1822.563895147756</v>
+        <v>1817.895162161753</v>
       </c>
       <c r="O84">
-        <v>637.8973633017144</v>
+        <v>636.2633067566134</v>
       </c>
       <c r="P84">
-        <v>1184.666531846041</v>
+        <v>1181.631855405139</v>
       </c>
       <c r="Q84">
-        <v>1321.466531846041</v>
+        <v>1318.431855405139</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.244031626137365</v>
+        <v>0.2546619831202285</v>
       </c>
       <c r="T84">
-        <v>2.884511698188967</v>
+        <v>3.03919634498567</v>
       </c>
       <c r="U84">
         <v>0.07415748822216711</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.76068968430022</v>
+        <v>5.691283784489374</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08330050202629799</v>
+        <v>0.0831493701254552</v>
       </c>
       <c r="C85">
-        <v>1247.204905031815</v>
+        <v>1188.01795983982</v>
       </c>
       <c r="D85">
-        <v>5707.835905031816</v>
+        <v>5711.605959839821</v>
       </c>
       <c r="E85">
-        <v>2295.031000000001</v>
+        <v>2357.988000000001</v>
       </c>
       <c r="F85">
-        <v>5225.431000000001</v>
+        <v>5288.388000000001</v>
       </c>
       <c r="G85">
         <v>764.8</v>
@@ -8376,28 +8376,28 @@
         <v>2205.4</v>
       </c>
       <c r="M85">
-        <v>387.504837838247</v>
+        <v>392.17357082425</v>
       </c>
       <c r="N85">
-        <v>1817.895162161753</v>
+        <v>1813.22642917575</v>
       </c>
       <c r="O85">
-        <v>636.2633067566134</v>
+        <v>634.6292502115124</v>
       </c>
       <c r="P85">
-        <v>1181.631855405139</v>
+        <v>1178.597178964237</v>
       </c>
       <c r="Q85">
-        <v>1318.431855405139</v>
+        <v>1315.397178964237</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2546619831202285</v>
+        <v>0.2666211347259498</v>
       </c>
       <c r="T85">
-        <v>3.03919634498567</v>
+        <v>3.21321657263196</v>
       </c>
       <c r="U85">
         <v>0.07415748822216711</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.691283784489374</v>
+        <v>5.623530406102596</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0831493701254552</v>
+        <v>0.08299823822461241</v>
       </c>
       <c r="C86">
-        <v>1188.01795983982</v>
+        <v>1128.835998220467</v>
       </c>
       <c r="D86">
-        <v>5711.605959839821</v>
+        <v>5715.380998220467</v>
       </c>
       <c r="E86">
-        <v>2357.988000000001</v>
+        <v>2420.945</v>
       </c>
       <c r="F86">
-        <v>5288.388000000001</v>
+        <v>5351.345</v>
       </c>
       <c r="G86">
         <v>764.8</v>
@@ -8458,28 +8458,28 @@
         <v>2205.4</v>
       </c>
       <c r="M86">
-        <v>392.17357082425</v>
+        <v>396.8423038102529</v>
       </c>
       <c r="N86">
-        <v>1813.22642917575</v>
+        <v>1808.557696189747</v>
       </c>
       <c r="O86">
-        <v>634.6292502115124</v>
+        <v>632.9951936664113</v>
       </c>
       <c r="P86">
-        <v>1178.597178964237</v>
+        <v>1175.562502523336</v>
       </c>
       <c r="Q86">
-        <v>1315.397178964237</v>
+        <v>1312.362502523335</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2666211347259497</v>
+        <v>0.2801748398791006</v>
       </c>
       <c r="T86">
-        <v>3.213216572631958</v>
+        <v>3.410439497297754</v>
       </c>
       <c r="U86">
         <v>0.07415748822216711</v>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.623530406102596</v>
+        <v>5.557371224854331</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08299823822461241</v>
+        <v>0.08284710632376963</v>
       </c>
       <c r="C87">
-        <v>1128.835998220467</v>
+        <v>1069.659030061839</v>
       </c>
       <c r="D87">
-        <v>5715.380998220467</v>
+        <v>5719.161030061839</v>
       </c>
       <c r="E87">
-        <v>2420.945</v>
+        <v>2483.902</v>
       </c>
       <c r="F87">
-        <v>5351.345</v>
+        <v>5414.302000000001</v>
       </c>
       <c r="G87">
         <v>764.8</v>
@@ -8540,28 +8540,28 @@
         <v>2205.4</v>
       </c>
       <c r="M87">
-        <v>396.8423038102529</v>
+        <v>401.5110367962559</v>
       </c>
       <c r="N87">
-        <v>1808.557696189747</v>
+        <v>1803.888963203744</v>
       </c>
       <c r="O87">
-        <v>632.9951936664113</v>
+        <v>631.3611371213103</v>
       </c>
       <c r="P87">
-        <v>1175.562502523336</v>
+        <v>1172.527826082433</v>
       </c>
       <c r="Q87">
-        <v>1312.362502523335</v>
+        <v>1309.327826082433</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2801748398791006</v>
+        <v>0.2956647886255586</v>
       </c>
       <c r="T87">
-        <v>3.410439497297754</v>
+        <v>3.635837125487234</v>
       </c>
       <c r="U87">
         <v>0.07415748822216711</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.557371224854331</v>
+        <v>5.49275062921649</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08284710632376963</v>
+        <v>0.08269597442292684</v>
       </c>
       <c r="C88">
-        <v>1069.659030061839</v>
+        <v>1010.487065278206</v>
       </c>
       <c r="D88">
-        <v>5719.161030061839</v>
+        <v>5722.946065278206</v>
       </c>
       <c r="E88">
-        <v>2483.902</v>
+        <v>2546.859000000001</v>
       </c>
       <c r="F88">
-        <v>5414.302000000001</v>
+        <v>5477.259000000001</v>
       </c>
       <c r="G88">
         <v>764.8</v>
@@ -8622,28 +8622,28 @@
         <v>2205.4</v>
       </c>
       <c r="M88">
-        <v>401.5110367962559</v>
+        <v>406.1797697822589</v>
       </c>
       <c r="N88">
-        <v>1803.888963203744</v>
+        <v>1799.220230217741</v>
       </c>
       <c r="O88">
-        <v>631.3611371213103</v>
+        <v>629.7270805762092</v>
       </c>
       <c r="P88">
-        <v>1172.527826082433</v>
+        <v>1169.493149641532</v>
       </c>
       <c r="Q88">
-        <v>1309.327826082433</v>
+        <v>1306.293149641531</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2956647886255586</v>
+        <v>0.3135378064099333</v>
       </c>
       <c r="T88">
-        <v>3.635837125487234</v>
+        <v>3.895911311859712</v>
       </c>
       <c r="U88">
         <v>0.07415748822216711</v>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.49275062921649</v>
+        <v>5.429615564512852</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08269597442292684</v>
+        <v>0.08254484252208405</v>
       </c>
       <c r="C89">
-        <v>1010.487065278206</v>
+        <v>951.320113810094</v>
       </c>
       <c r="D89">
-        <v>5722.946065278206</v>
+        <v>5726.736113810094</v>
       </c>
       <c r="E89">
-        <v>2546.859000000001</v>
+        <v>2609.816</v>
       </c>
       <c r="F89">
-        <v>5477.259000000001</v>
+        <v>5540.216</v>
       </c>
       <c r="G89">
         <v>764.8</v>
@@ -8704,28 +8704,28 @@
         <v>2205.4</v>
       </c>
       <c r="M89">
-        <v>406.1797697822589</v>
+        <v>410.8485027682618</v>
       </c>
       <c r="N89">
-        <v>1799.220230217741</v>
+        <v>1794.551497231738</v>
       </c>
       <c r="O89">
-        <v>629.7270805762092</v>
+        <v>628.0930240311081</v>
       </c>
       <c r="P89">
-        <v>1169.493149641532</v>
+        <v>1166.45847320063</v>
       </c>
       <c r="Q89">
-        <v>1306.293149641531</v>
+        <v>1303.25847320063</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3135378064099333</v>
+        <v>0.3343896604917039</v>
       </c>
       <c r="T89">
-        <v>3.895911311859712</v>
+        <v>4.199331195960936</v>
       </c>
       <c r="U89">
         <v>0.07415748822216711</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.429615564512852</v>
+        <v>5.367915387643388</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08254484252208405</v>
+        <v>0.08239371062124126</v>
       </c>
       <c r="C90">
-        <v>951.320113810094</v>
+        <v>892.1581856243774</v>
       </c>
       <c r="D90">
-        <v>5726.736113810094</v>
+        <v>5730.531185624378</v>
       </c>
       <c r="E90">
-        <v>2609.816</v>
+        <v>2672.773000000001</v>
       </c>
       <c r="F90">
-        <v>5540.216</v>
+        <v>5603.173000000001</v>
       </c>
       <c r="G90">
         <v>764.8</v>
@@ -8786,28 +8786,28 @@
         <v>2205.4</v>
       </c>
       <c r="M90">
-        <v>410.8485027682618</v>
+        <v>415.5172357542648</v>
       </c>
       <c r="N90">
-        <v>1794.551497231738</v>
+        <v>1789.882764245735</v>
       </c>
       <c r="O90">
-        <v>628.0930240311081</v>
+        <v>626.4589674860072</v>
       </c>
       <c r="P90">
-        <v>1166.45847320063</v>
+        <v>1163.423796759728</v>
       </c>
       <c r="Q90">
-        <v>1303.25847320063</v>
+        <v>1300.223796759728</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3343896604917039</v>
+        <v>0.35903276077016</v>
       </c>
       <c r="T90">
-        <v>4.199331195960936</v>
+        <v>4.557918331716928</v>
       </c>
       <c r="U90">
         <v>0.07415748822216711</v>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.367915387643388</v>
+        <v>5.307601731602452</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08239371062124126</v>
+        <v>0.08224257872039847</v>
       </c>
       <c r="C91">
-        <v>892.1581856243774</v>
+        <v>833.0012907143746</v>
       </c>
       <c r="D91">
-        <v>5730.531185624378</v>
+        <v>5734.331290714375</v>
       </c>
       <c r="E91">
-        <v>2672.773000000001</v>
+        <v>2735.730000000001</v>
       </c>
       <c r="F91">
-        <v>5603.173000000001</v>
+        <v>5666.130000000001</v>
       </c>
       <c r="G91">
         <v>764.8</v>
@@ -8868,28 +8868,28 @@
         <v>2205.4</v>
       </c>
       <c r="M91">
-        <v>415.5172357542648</v>
+        <v>420.1859687402678</v>
       </c>
       <c r="N91">
-        <v>1789.882764245735</v>
+        <v>1785.214031259732</v>
       </c>
       <c r="O91">
-        <v>626.4589674860072</v>
+        <v>624.8249109409061</v>
       </c>
       <c r="P91">
-        <v>1163.423796759728</v>
+        <v>1160.389120318826</v>
       </c>
       <c r="Q91">
-        <v>1300.223796759728</v>
+        <v>1297.189120318826</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.35903276077016</v>
+        <v>0.3886044811043073</v>
       </c>
       <c r="T91">
-        <v>4.557918331716928</v>
+        <v>4.988222894624118</v>
       </c>
       <c r="U91">
         <v>0.07415748822216711</v>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.307601731602452</v>
+        <v>5.24862837902909</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08224257872039847</v>
+        <v>0.08209144681955569</v>
       </c>
       <c r="C92">
-        <v>833.0012907143746</v>
+        <v>773.849439099924</v>
       </c>
       <c r="D92">
-        <v>5734.331290714375</v>
+        <v>5738.136439099924</v>
       </c>
       <c r="E92">
-        <v>2735.730000000001</v>
+        <v>2798.687</v>
       </c>
       <c r="F92">
-        <v>5666.130000000001</v>
+        <v>5729.087</v>
       </c>
       <c r="G92">
         <v>764.8</v>
@@ -8950,28 +8950,28 @@
         <v>2205.4</v>
       </c>
       <c r="M92">
-        <v>420.1859687402678</v>
+        <v>424.8547017262707</v>
       </c>
       <c r="N92">
-        <v>1785.214031259732</v>
+        <v>1780.545298273729</v>
       </c>
       <c r="O92">
-        <v>624.8249109409061</v>
+        <v>623.190854395805</v>
       </c>
       <c r="P92">
-        <v>1160.389120318826</v>
+        <v>1157.354443877924</v>
       </c>
       <c r="Q92">
-        <v>1297.189120318826</v>
+        <v>1294.154443877924</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3886044811043073</v>
+        <v>0.4247476948460429</v>
       </c>
       <c r="T92">
-        <v>4.988222894624118</v>
+        <v>5.514150693732907</v>
       </c>
       <c r="U92">
         <v>0.07415748822216711</v>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.24862837902909</v>
+        <v>5.190951144094705</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08209144681955569</v>
+        <v>0.08194031491871291</v>
       </c>
       <c r="C93">
-        <v>773.849439099924</v>
+        <v>714.7026408274796</v>
       </c>
       <c r="D93">
-        <v>5738.136439099924</v>
+        <v>5741.94664082748</v>
       </c>
       <c r="E93">
-        <v>2798.687</v>
+        <v>2861.644000000001</v>
       </c>
       <c r="F93">
-        <v>5729.087</v>
+        <v>5792.044000000001</v>
       </c>
       <c r="G93">
         <v>764.8</v>
@@ -9032,28 +9032,28 @@
         <v>2205.4</v>
       </c>
       <c r="M93">
-        <v>424.8547017262707</v>
+        <v>429.5234347122737</v>
       </c>
       <c r="N93">
-        <v>1780.545298273729</v>
+        <v>1775.876565287726</v>
       </c>
       <c r="O93">
-        <v>623.190854395805</v>
+        <v>621.556797850704</v>
       </c>
       <c r="P93">
-        <v>1157.354443877924</v>
+        <v>1154.319767437022</v>
       </c>
       <c r="Q93">
-        <v>1294.154443877924</v>
+        <v>1291.119767437022</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4247476948460429</v>
+        <v>0.4699267120232125</v>
       </c>
       <c r="T93">
-        <v>5.514150693732907</v>
+        <v>6.171560442618893</v>
       </c>
       <c r="U93">
         <v>0.07415748822216711</v>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.190951144094705</v>
+        <v>5.134527762093676</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08194031491871291</v>
+        <v>0.08178918301787011</v>
       </c>
       <c r="C94">
-        <v>714.7026408274796</v>
+        <v>655.5609059701965</v>
       </c>
       <c r="D94">
-        <v>5741.94664082748</v>
+        <v>5745.761905970197</v>
       </c>
       <c r="E94">
-        <v>2861.644000000001</v>
+        <v>2924.601000000001</v>
       </c>
       <c r="F94">
-        <v>5792.044000000001</v>
+        <v>5855.001000000001</v>
       </c>
       <c r="G94">
         <v>764.8</v>
@@ -9114,28 +9114,28 @@
         <v>2205.4</v>
       </c>
       <c r="M94">
-        <v>429.5234347122737</v>
+        <v>434.1921676982768</v>
       </c>
       <c r="N94">
-        <v>1775.876565287726</v>
+        <v>1771.207832301723</v>
       </c>
       <c r="O94">
-        <v>621.556797850704</v>
+        <v>619.9227413056029</v>
       </c>
       <c r="P94">
-        <v>1154.319767437022</v>
+        <v>1151.28509099612</v>
       </c>
       <c r="Q94">
-        <v>1291.119767437022</v>
+        <v>1288.08509099612</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4699267120232125</v>
+        <v>0.5280140198224303</v>
       </c>
       <c r="T94">
-        <v>6.171560442618893</v>
+        <v>7.016801548329445</v>
       </c>
       <c r="U94">
         <v>0.07415748822216711</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.134527762093676</v>
+        <v>5.079317786157183</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08178918301787011</v>
+        <v>0.08163805111702734</v>
       </c>
       <c r="C95">
-        <v>655.5609059701965</v>
+        <v>596.4242446280196</v>
       </c>
       <c r="D95">
-        <v>5745.761905970197</v>
+        <v>5749.582244628021</v>
       </c>
       <c r="E95">
-        <v>2924.601000000001</v>
+        <v>2987.558000000001</v>
       </c>
       <c r="F95">
-        <v>5855.001000000001</v>
+        <v>5917.958000000001</v>
       </c>
       <c r="G95">
         <v>764.8</v>
@@ -9196,28 +9196,28 @@
         <v>2205.4</v>
       </c>
       <c r="M95">
-        <v>434.1921676982768</v>
+        <v>438.8609006842797</v>
       </c>
       <c r="N95">
-        <v>1771.207832301723</v>
+        <v>1766.53909931572</v>
       </c>
       <c r="O95">
-        <v>619.9227413056029</v>
+        <v>618.2886847605018</v>
       </c>
       <c r="P95">
-        <v>1151.28509099612</v>
+        <v>1148.250414555218</v>
       </c>
       <c r="Q95">
-        <v>1288.08509099612</v>
+        <v>1285.050414555218</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5280140198224303</v>
+        <v>0.605463763554721</v>
       </c>
       <c r="T95">
-        <v>7.016801548329445</v>
+        <v>8.143789689276851</v>
       </c>
       <c r="U95">
         <v>0.07415748822216711</v>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.079317786157183</v>
+        <v>5.025282490559767</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08163805111702734</v>
+        <v>0.08148691921618455</v>
       </c>
       <c r="C96">
-        <v>596.4242446280196</v>
+        <v>537.2926669277758</v>
       </c>
       <c r="D96">
-        <v>5749.582244628021</v>
+        <v>5753.407666927777</v>
       </c>
       <c r="E96">
-        <v>2987.558000000001</v>
+        <v>3050.515000000001</v>
       </c>
       <c r="F96">
-        <v>5917.958000000001</v>
+        <v>5980.915000000001</v>
       </c>
       <c r="G96">
         <v>764.8</v>
@@ -9278,28 +9278,28 @@
         <v>2205.4</v>
       </c>
       <c r="M96">
-        <v>438.8609006842797</v>
+        <v>443.5296336702827</v>
       </c>
       <c r="N96">
-        <v>1766.53909931572</v>
+        <v>1761.870366329717</v>
       </c>
       <c r="O96">
-        <v>618.2886847605018</v>
+        <v>616.6546282154009</v>
       </c>
       <c r="P96">
-        <v>1148.250414555218</v>
+        <v>1145.215738114316</v>
       </c>
       <c r="Q96">
-        <v>1285.050414555218</v>
+        <v>1282.015738114316</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.605463763554721</v>
+        <v>0.713893404779928</v>
       </c>
       <c r="T96">
-        <v>8.143789689276851</v>
+        <v>9.72157308660322</v>
       </c>
       <c r="U96">
         <v>0.07415748822216711</v>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.025282490559767</v>
+        <v>4.972384780132822</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08148691921618455</v>
+        <v>0.08133578731534176</v>
       </c>
       <c r="C97">
-        <v>537.2926669277758</v>
+        <v>478.166183023257</v>
       </c>
       <c r="D97">
-        <v>5753.407666927777</v>
+        <v>5757.238183023258</v>
       </c>
       <c r="E97">
-        <v>3050.515000000001</v>
+        <v>3113.472000000001</v>
       </c>
       <c r="F97">
-        <v>5980.915000000001</v>
+        <v>6043.872000000001</v>
       </c>
       <c r="G97">
         <v>764.8</v>
@@ -9360,28 +9360,28 @@
         <v>2205.4</v>
       </c>
       <c r="M97">
-        <v>443.5296336702827</v>
+        <v>448.1983666562857</v>
       </c>
       <c r="N97">
-        <v>1761.870366329717</v>
+        <v>1757.201633343714</v>
       </c>
       <c r="O97">
-        <v>616.6546282154009</v>
+        <v>615.0205716702999</v>
       </c>
       <c r="P97">
-        <v>1145.215738114316</v>
+        <v>1142.181061673414</v>
       </c>
       <c r="Q97">
-        <v>1282.015738114316</v>
+        <v>1278.981061673414</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.713893404779928</v>
+        <v>0.8765378666177386</v>
       </c>
       <c r="T97">
-        <v>9.72157308660322</v>
+        <v>12.08824818259277</v>
       </c>
       <c r="U97">
         <v>0.07415748822216711</v>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.972384780132822</v>
+        <v>4.920589105339772</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08133578731534177</v>
+        <v>0.08118465541449899</v>
       </c>
       <c r="C98">
-        <v>478.1661830232579</v>
+        <v>419.0448030953157</v>
       </c>
       <c r="D98">
-        <v>5757.238183023258</v>
+        <v>5761.073803095316</v>
       </c>
       <c r="E98">
-        <v>3113.472</v>
+        <v>3176.429000000001</v>
       </c>
       <c r="F98">
-        <v>6043.872</v>
+        <v>6106.829000000001</v>
       </c>
       <c r="G98">
         <v>764.8</v>
@@ -9442,28 +9442,28 @@
         <v>2205.4</v>
       </c>
       <c r="M98">
-        <v>448.1983666562856</v>
+        <v>452.8670996422886</v>
       </c>
       <c r="N98">
-        <v>1757.201633343714</v>
+        <v>1752.532900357711</v>
       </c>
       <c r="O98">
-        <v>615.0205716702999</v>
+        <v>613.3865151251988</v>
       </c>
       <c r="P98">
-        <v>1142.181061673414</v>
+        <v>1139.146385232512</v>
       </c>
       <c r="Q98">
-        <v>1278.981061673414</v>
+        <v>1275.946385232512</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8765378666177365</v>
+        <v>1.147611969680753</v>
       </c>
       <c r="T98">
-        <v>12.08824818259274</v>
+        <v>16.03270667590865</v>
       </c>
       <c r="U98">
         <v>0.07415748822216711</v>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.920589105339772</v>
+        <v>4.86986138260431</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08118465541449899</v>
+        <v>0.0810335235136562</v>
       </c>
       <c r="C99">
-        <v>419.0448030953157</v>
+        <v>359.9285373519569</v>
       </c>
       <c r="D99">
-        <v>5761.073803095316</v>
+        <v>5764.914537351958</v>
       </c>
       <c r="E99">
-        <v>3176.429000000001</v>
+        <v>3239.386000000001</v>
       </c>
       <c r="F99">
-        <v>6106.829000000001</v>
+        <v>6169.786000000001</v>
       </c>
       <c r="G99">
         <v>764.8</v>
@@ -9524,28 +9524,28 @@
         <v>2205.4</v>
       </c>
       <c r="M99">
-        <v>452.8670996422886</v>
+        <v>457.5358326282916</v>
       </c>
       <c r="N99">
-        <v>1752.532900357711</v>
+        <v>1747.864167371708</v>
       </c>
       <c r="O99">
-        <v>613.3865151251988</v>
+        <v>611.7524585800977</v>
       </c>
       <c r="P99">
-        <v>1139.146385232512</v>
+        <v>1136.11170879161</v>
       </c>
       <c r="Q99">
-        <v>1275.946385232512</v>
+        <v>1272.91170879161</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.147611969680753</v>
+        <v>1.689760175806786</v>
       </c>
       <c r="T99">
-        <v>16.03270667590865</v>
+        <v>23.92162366254045</v>
       </c>
       <c r="U99">
         <v>0.07415748822216711</v>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.86986138260431</v>
+        <v>4.820168919516512</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0810335235136562</v>
+        <v>0.08088239161281341</v>
       </c>
       <c r="C100">
-        <v>359.9285373519569</v>
+        <v>300.8173960284203</v>
       </c>
       <c r="D100">
-        <v>5764.914537351958</v>
+        <v>5768.76039602842</v>
       </c>
       <c r="E100">
-        <v>3239.386000000001</v>
+        <v>3302.343</v>
       </c>
       <c r="F100">
-        <v>6169.786000000001</v>
+        <v>6232.743</v>
       </c>
       <c r="G100">
         <v>764.8</v>
@@ -9606,28 +9606,28 @@
         <v>2205.4</v>
       </c>
       <c r="M100">
-        <v>457.5358326282916</v>
+        <v>462.2045656142946</v>
       </c>
       <c r="N100">
-        <v>1747.864167371708</v>
+        <v>1743.195434385705</v>
       </c>
       <c r="O100">
-        <v>611.7524585800977</v>
+        <v>610.1184020349967</v>
       </c>
       <c r="P100">
-        <v>1136.11170879161</v>
+        <v>1133.077032350708</v>
       </c>
       <c r="Q100">
-        <v>1272.91170879161</v>
+        <v>1269.877032350708</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.689760175806786</v>
+        <v>3.316204794184884</v>
       </c>
       <c r="T100">
-        <v>23.92162366254045</v>
+        <v>47.58837462243589</v>
       </c>
       <c r="U100">
         <v>0.07415748822216711</v>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.820168919516512</v>
+        <v>4.7714803445719</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08088239161281341</v>
-      </c>
-      <c r="C101">
-        <v>300.8173960284203</v>
-      </c>
-      <c r="D101">
-        <v>5768.76039602842</v>
-      </c>
-      <c r="E101">
-        <v>3302.343</v>
-      </c>
-      <c r="F101">
-        <v>6232.743</v>
-      </c>
-      <c r="G101">
-        <v>764.8</v>
-      </c>
-      <c r="H101">
-        <v>3365.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2342.2</v>
-      </c>
-      <c r="K101">
-        <v>136.8</v>
-      </c>
-      <c r="L101">
-        <v>2205.4</v>
-      </c>
-      <c r="M101">
-        <v>462.2045656142946</v>
-      </c>
-      <c r="N101">
-        <v>1743.195434385705</v>
-      </c>
-      <c r="O101">
-        <v>610.1184020349967</v>
-      </c>
-      <c r="P101">
-        <v>1133.077032350708</v>
-      </c>
-      <c r="Q101">
-        <v>1269.877032350708</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.316204794184884</v>
-      </c>
-      <c r="T101">
-        <v>47.58837462243589</v>
-      </c>
-      <c r="U101">
-        <v>0.07415748822216711</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.04820236734440862</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.7714803445719</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
